--- a/artfynd/A 28050-2026 artfynd.xlsx
+++ b/artfynd/A 28050-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135849953</v>
       </c>
       <c r="B2" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135849954</v>
       </c>
       <c r="B3" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135849955</v>
       </c>
       <c r="B4" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135849956</v>
       </c>
       <c r="B5" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135849957</v>
       </c>
       <c r="B6" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135849958</v>
       </c>
       <c r="B7" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135849959</v>
       </c>
       <c r="B8" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135850027</v>
       </c>
       <c r="B18" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>135850012</v>
       </c>
       <c r="B19" t="n">
-        <v>99173</v>
+        <v>99175</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>135850029</v>
       </c>
       <c r="B20" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135849834</v>
       </c>
       <c r="B21" t="n">
-        <v>99298</v>
+        <v>99300</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>135849835</v>
       </c>
       <c r="B22" t="n">
-        <v>99298</v>
+        <v>99300</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>135849836</v>
       </c>
       <c r="B23" t="n">
-        <v>99298</v>
+        <v>99300</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>135849837</v>
       </c>
       <c r="B24" t="n">
-        <v>99298</v>
+        <v>99300</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>135849838</v>
       </c>
       <c r="B25" t="n">
-        <v>99298</v>
+        <v>99300</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>135849839</v>
       </c>
       <c r="B26" t="n">
-        <v>99298</v>
+        <v>99300</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>135849840</v>
       </c>
       <c r="B27" t="n">
-        <v>99298</v>
+        <v>99300</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>135849841</v>
       </c>
       <c r="B28" t="n">
-        <v>99298</v>
+        <v>99300</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>135849936</v>
       </c>
       <c r="B29" t="n">
-        <v>99612</v>
+        <v>99614</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>135849937</v>
       </c>
       <c r="B30" t="n">
-        <v>99612</v>
+        <v>99614</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>135850030</v>
       </c>
       <c r="B31" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>135850031</v>
       </c>
       <c r="B32" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>135850032</v>
       </c>
       <c r="B33" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>135850033</v>
       </c>
       <c r="B34" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>135850034</v>
       </c>
       <c r="B35" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>135850035</v>
       </c>
       <c r="B36" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>135849917</v>
       </c>
       <c r="B37" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>135849918</v>
       </c>
       <c r="B38" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>135849919</v>
       </c>
       <c r="B39" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>135849920</v>
       </c>
       <c r="B40" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>135849921</v>
       </c>
       <c r="B41" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>135849922</v>
       </c>
       <c r="B42" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>135849923</v>
       </c>
       <c r="B43" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>135849909</v>
       </c>
       <c r="B44" t="n">
-        <v>111242</v>
+        <v>111244</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>135849910</v>
       </c>
       <c r="B45" t="n">
-        <v>111242</v>
+        <v>111244</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>135849974</v>
       </c>
       <c r="B46" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>135849975</v>
       </c>
       <c r="B47" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>135849976</v>
       </c>
       <c r="B48" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>135849977</v>
       </c>
       <c r="B49" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>135849978</v>
       </c>
       <c r="B50" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>135849979</v>
       </c>
       <c r="B51" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>135849862</v>
       </c>
       <c r="B52" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>135849863</v>
       </c>
       <c r="B53" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>135849864</v>
       </c>
       <c r="B54" t="n">
-        <v>110012</v>
+        <v>110014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>135849876</v>
       </c>
       <c r="B55" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>135850039</v>
       </c>
       <c r="B56" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>135850040</v>
       </c>
       <c r="B57" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>135850042</v>
       </c>
       <c r="B58" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>135850043</v>
       </c>
       <c r="B59" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>135850044</v>
       </c>
       <c r="B60" t="n">
-        <v>101483</v>
+        <v>101485</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>135849915</v>
       </c>
       <c r="B61" t="n">
-        <v>99551</v>
+        <v>99553</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>135849889</v>
       </c>
       <c r="B62" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>135849996</v>
       </c>
       <c r="B63" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>135849997</v>
       </c>
       <c r="B64" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>135849998</v>
       </c>
       <c r="B65" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>135849893</v>
       </c>
       <c r="B66" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>135849894</v>
       </c>
       <c r="B67" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>135849895</v>
       </c>
       <c r="B68" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>135849896</v>
       </c>
       <c r="B69" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>135849897</v>
       </c>
       <c r="B70" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>135849898</v>
       </c>
       <c r="B71" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>135849899</v>
       </c>
       <c r="B72" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>135849900</v>
       </c>
       <c r="B73" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>135849901</v>
       </c>
       <c r="B74" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>135849902</v>
       </c>
       <c r="B75" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>135849903</v>
       </c>
       <c r="B76" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 28050-2026 artfynd.xlsx
+++ b/artfynd/A 28050-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ76"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1464,7 +1464,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135850014</v>
+        <v>135850018</v>
       </c>
       <c r="B9" t="n">
         <v>79441</v>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500484</v>
+        <v>500425</v>
       </c>
       <c r="R9" t="n">
-        <v>7003356</v>
+        <v>7003323</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,6 +1540,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1552,7 +1557,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1584,54 +1589,63 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850014</t>
+          <t>https://artportalen.se/Sighting/135850018</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135850015</v>
+        <v>135849842</v>
       </c>
       <c r="B10" t="n">
-        <v>79441</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500586</v>
+        <v>500404</v>
       </c>
       <c r="R10" t="n">
-        <v>7003162</v>
+        <v>7003270</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1682,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i granskog.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran med spår av rikligt med kådaflöde.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1677,13 +1691,12 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1698,12 +1711,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1720,43 +1733,48 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850015</t>
+          <t>https://artportalen.se/Sighting/135849842</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135850016</v>
+        <v>135849843</v>
       </c>
       <c r="B11" t="n">
-        <v>79441</v>
+        <v>57980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1764,10 +1782,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500552</v>
+        <v>500404</v>
       </c>
       <c r="R11" t="n">
-        <v>7003131</v>
+        <v>7003271</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,19 +1820,23 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1827,9 +1849,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1846,54 +1873,63 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850016</t>
+          <t>https://artportalen.se/Sighting/135849843</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135850017</v>
+        <v>135849844</v>
       </c>
       <c r="B12" t="n">
-        <v>79441</v>
+        <v>57980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500505</v>
+        <v>500403</v>
       </c>
       <c r="R12" t="n">
-        <v>7003184</v>
+        <v>7003276</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1930,7 +1966,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i granskog.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1939,13 +1975,12 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -1958,9 +1993,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1977,54 +2017,63 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850017</t>
+          <t>https://artportalen.se/Sighting/135849844</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135850018</v>
+        <v>135849845</v>
       </c>
       <c r="B13" t="n">
-        <v>79441</v>
+        <v>57980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500425</v>
+        <v>500377</v>
       </c>
       <c r="R13" t="n">
-        <v>7003323</v>
+        <v>7003317</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2061,7 +2110,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2070,7 +2119,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2089,9 +2137,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2108,63 +2161,67 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850018</t>
+          <t>https://artportalen.se/Sighting/135849845</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135849842</v>
+        <v>135849841</v>
       </c>
       <c r="B14" t="n">
-        <v>57980</v>
+        <v>99300</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500404</v>
+        <v>500424</v>
       </c>
       <c r="R14" t="n">
-        <v>7003270</v>
+        <v>7003277</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2201,7 +2258,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran med spår av rikligt med kådaflöde.</t>
+          <t>Minst 3 plantor som växer i ett örtrikt fältskikt på fuktig mark.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2210,32 +2267,13 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2252,48 +2290,48 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849842</t>
+          <t>https://artportalen.se/Sighting/135849841</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135849843</v>
+        <v>135849936</v>
       </c>
       <c r="B15" t="n">
-        <v>57980</v>
+        <v>99614</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2301,10 +2339,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500404</v>
+        <v>500459</v>
       </c>
       <c r="R15" t="n">
-        <v>7003271</v>
+        <v>7003232</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2339,43 +2377,19 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2392,63 +2406,59 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849843</t>
+          <t>https://artportalen.se/Sighting/135849936</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135849844</v>
+        <v>135849937</v>
       </c>
       <c r="B16" t="n">
-        <v>57980</v>
+        <v>99614</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500403</v>
+        <v>500481</v>
       </c>
       <c r="R16" t="n">
-        <v>7003276</v>
+        <v>7003274</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2483,43 +2493,19 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2536,63 +2522,59 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849844</t>
+          <t>https://artportalen.se/Sighting/135849937</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135849845</v>
+        <v>135849917</v>
       </c>
       <c r="B17" t="n">
-        <v>57980</v>
+        <v>108364</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220102</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500377</v>
+        <v>500456</v>
       </c>
       <c r="R17" t="n">
-        <v>7003317</v>
+        <v>7003316</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2627,43 +2609,19 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2680,16 +2638,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849845</t>
+          <t>https://artportalen.se/Sighting/135849917</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135850027</v>
+        <v>135849918</v>
       </c>
       <c r="B18" t="n">
-        <v>99193</v>
+        <v>108364</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2697,21 +2655,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>220102</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2729,10 +2687,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500425</v>
+        <v>500488</v>
       </c>
       <c r="R18" t="n">
-        <v>7003277</v>
+        <v>7003344</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2767,11 +2725,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Växer här i ett stort örtrikt fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2784,7 +2737,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2801,16 +2754,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850027</t>
+          <t>https://artportalen.se/Sighting/135849918</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135850012</v>
+        <v>135849919</v>
       </c>
       <c r="B19" t="n">
-        <v>99175</v>
+        <v>108364</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2818,36 +2771,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219795</v>
+        <v>220102</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -2858,10 +2803,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500521</v>
+        <v>500511</v>
       </c>
       <c r="R19" t="n">
-        <v>7003130</v>
+        <v>7003325</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2925,16 +2870,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850012</t>
+          <t>https://artportalen.se/Sighting/135849919</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135850029</v>
+        <v>135849920</v>
       </c>
       <c r="B20" t="n">
-        <v>99278</v>
+        <v>108364</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2942,33 +2887,25 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219811</v>
+        <v>220102</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -2982,10 +2919,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500389</v>
+        <v>500416</v>
       </c>
       <c r="R20" t="n">
-        <v>7003289</v>
+        <v>7003258</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3032,7 +2969,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3049,16 +2986,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850029</t>
+          <t>https://artportalen.se/Sighting/135849920</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135849834</v>
+        <v>135849921</v>
       </c>
       <c r="B21" t="n">
-        <v>99300</v>
+        <v>108364</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3066,28 +3003,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219847</v>
+        <v>220102</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -3098,10 +3035,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500475</v>
+        <v>500474</v>
       </c>
       <c r="R21" t="n">
-        <v>7003332</v>
+        <v>7003267</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3165,16 +3102,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849834</t>
+          <t>https://artportalen.se/Sighting/135849921</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135849835</v>
+        <v>135849922</v>
       </c>
       <c r="B22" t="n">
-        <v>99300</v>
+        <v>108364</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3182,28 +3119,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219847</v>
+        <v>220102</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -3214,10 +3151,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>500456</v>
+        <v>500448</v>
       </c>
       <c r="R22" t="n">
-        <v>7003229</v>
+        <v>7003286</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3264,7 +3201,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3281,16 +3218,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849835</t>
+          <t>https://artportalen.se/Sighting/135849922</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135849836</v>
+        <v>135849923</v>
       </c>
       <c r="B23" t="n">
-        <v>99300</v>
+        <v>108364</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3298,21 +3235,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>220102</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3330,10 +3267,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500435</v>
+        <v>500415</v>
       </c>
       <c r="R23" t="n">
-        <v>7003231</v>
+        <v>7003291</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3397,16 +3334,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849836</t>
+          <t>https://artportalen.se/Sighting/135849923</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135849837</v>
+        <v>135849909</v>
       </c>
       <c r="B24" t="n">
-        <v>99300</v>
+        <v>111244</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3414,28 +3351,28 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219847</v>
+        <v>220240</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -3446,10 +3383,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>500408</v>
+        <v>500546</v>
       </c>
       <c r="R24" t="n">
-        <v>7003263</v>
+        <v>7003124</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3496,7 +3433,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3513,16 +3450,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849837</t>
+          <t>https://artportalen.se/Sighting/135849909</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135849838</v>
+        <v>135849910</v>
       </c>
       <c r="B25" t="n">
-        <v>99300</v>
+        <v>111244</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3530,28 +3467,28 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219847</v>
+        <v>220240</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -3562,10 +3499,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500394</v>
+        <v>500461</v>
       </c>
       <c r="R25" t="n">
-        <v>7003275</v>
+        <v>7003351</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3629,42 +3566,50 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849838</t>
+          <t>https://artportalen.se/Sighting/135849910</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135849839</v>
+        <v>135849975</v>
       </c>
       <c r="B26" t="n">
-        <v>99300</v>
+        <v>99276</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -3678,10 +3623,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>500397</v>
+        <v>500529</v>
       </c>
       <c r="R26" t="n">
-        <v>7003280</v>
+        <v>7003306</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3716,6 +3661,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minst 30 plantor och 7 överblommade blomställningar inom ca 3 m2 yta i granskog.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3728,12 +3678,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Örtrik barrskog på stor del fuktig mark.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3750,59 +3695,71 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849839</t>
+          <t>https://artportalen.se/Sighting/135849975</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135849840</v>
+        <v>135849976</v>
       </c>
       <c r="B27" t="n">
-        <v>99300</v>
+        <v>99276</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>500478</v>
+        <v>500652</v>
       </c>
       <c r="R27" t="n">
-        <v>7003263</v>
+        <v>7003184</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3837,6 +3794,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Minst 120 plantor varav 30 med överblommade blomställningar inom ca 8 m2 yta i granskog.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3849,7 +3811,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3866,43 +3828,43 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849840</t>
+          <t>https://artportalen.se/Sighting/135849976</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135849841</v>
+        <v>135849977</v>
       </c>
       <c r="B28" t="n">
-        <v>99300</v>
+        <v>99276</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3916,17 +3878,21 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>500424</v>
+        <v>500570</v>
       </c>
       <c r="R28" t="n">
-        <v>7003277</v>
+        <v>7003141</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3963,7 +3929,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Minst 3 plantor som växer i ett örtrikt fältskikt på fuktig mark.</t>
+          <t>Minst 70 plantor och 13 överblommade blomställningar inom ca 1,5 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3978,7 +3944,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3995,59 +3961,71 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849841</t>
+          <t>https://artportalen.se/Sighting/135849977</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135849936</v>
+        <v>135849978</v>
       </c>
       <c r="B29" t="n">
-        <v>99614</v>
+        <v>99276</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500459</v>
+        <v>500507</v>
       </c>
       <c r="R29" t="n">
-        <v>7003232</v>
+        <v>7003191</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4082,6 +4060,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minst 30 plantor och 15 överblommade blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4094,7 +4077,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4111,59 +4094,71 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849936</t>
+          <t>https://artportalen.se/Sighting/135849978</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135849937</v>
+        <v>135849979</v>
       </c>
       <c r="B30" t="n">
-        <v>99614</v>
+        <v>99276</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>500481</v>
+        <v>500400</v>
       </c>
       <c r="R30" t="n">
-        <v>7003274</v>
+        <v>7003285</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4198,6 +4193,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 120 plantor och 20 mestadels överblommade blomställningar inom ca 2 m2 yta på ett moss- och granöverväxt block.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4227,16 +4227,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849937</t>
+          <t>https://artportalen.se/Sighting/135849979</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135850030</v>
+        <v>135849862</v>
       </c>
       <c r="B31" t="n">
-        <v>108294</v>
+        <v>110014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4244,28 +4244,28 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220083</v>
+        <v>221184</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -4276,10 +4276,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500467</v>
+        <v>500497</v>
       </c>
       <c r="R31" t="n">
-        <v>7003353</v>
+        <v>7003367</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4343,16 +4343,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850030</t>
+          <t>https://artportalen.se/Sighting/135849862</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135850031</v>
+        <v>135849863</v>
       </c>
       <c r="B32" t="n">
-        <v>108294</v>
+        <v>110014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4360,21 +4360,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220083</v>
+        <v>221184</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500476</v>
+        <v>500524</v>
       </c>
       <c r="R32" t="n">
-        <v>7003332</v>
+        <v>7003318</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4442,12 +4442,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Örtrik barrskog på kalkrik fuktig mark.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4464,16 +4459,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850031</t>
+          <t>https://artportalen.se/Sighting/135849863</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135850032</v>
+        <v>135849864</v>
       </c>
       <c r="B33" t="n">
-        <v>108294</v>
+        <v>110014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4481,21 +4476,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220083</v>
+        <v>221184</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4513,10 +4508,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500513</v>
+        <v>500480</v>
       </c>
       <c r="R33" t="n">
-        <v>7003327</v>
+        <v>7003262</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4580,16 +4575,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850032</t>
+          <t>https://artportalen.se/Sighting/135849864</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135850033</v>
+        <v>135849915</v>
       </c>
       <c r="B34" t="n">
-        <v>108294</v>
+        <v>99553</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4597,28 +4592,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220083</v>
+        <v>222812</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -4629,7 +4624,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>500572</v>
+        <v>500491</v>
       </c>
       <c r="R34" t="n">
         <v>7003234</v>
@@ -4696,16 +4691,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850033</t>
+          <t>https://artportalen.se/Sighting/135849915</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135850034</v>
+        <v>135849996</v>
       </c>
       <c r="B35" t="n">
-        <v>108294</v>
+        <v>98327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4713,21 +4708,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220083</v>
+        <v>223358</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4745,10 +4740,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>500399</v>
+        <v>500520</v>
       </c>
       <c r="R35" t="n">
-        <v>7003277</v>
+        <v>7003324</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4795,7 +4790,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4812,16 +4807,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850034</t>
+          <t>https://artportalen.se/Sighting/135849996</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135850035</v>
+        <v>135849997</v>
       </c>
       <c r="B36" t="n">
-        <v>108294</v>
+        <v>98327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4829,28 +4824,28 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220083</v>
+        <v>223358</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -4861,10 +4856,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>500389</v>
+        <v>500533</v>
       </c>
       <c r="R36" t="n">
-        <v>7003293</v>
+        <v>7003286</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4911,12 +4906,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Örtrik barrskog på fuktig mark.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4933,16 +4923,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850035</t>
+          <t>https://artportalen.se/Sighting/135849997</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135849917</v>
+        <v>135849998</v>
       </c>
       <c r="B37" t="n">
-        <v>108364</v>
+        <v>98327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4950,28 +4940,28 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220102</v>
+        <v>223358</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -4982,10 +4972,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>500456</v>
+        <v>500474</v>
       </c>
       <c r="R37" t="n">
-        <v>7003316</v>
+        <v>7003265</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5032,7 +5022,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5049,16 +5039,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849917</t>
+          <t>https://artportalen.se/Sighting/135849998</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135849918</v>
+        <v>135849893</v>
       </c>
       <c r="B38" t="n">
-        <v>108364</v>
+        <v>101375</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5066,28 +5056,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220102</v>
+        <v>224885</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5098,10 +5088,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>500488</v>
+        <v>500510</v>
       </c>
       <c r="R38" t="n">
-        <v>7003344</v>
+        <v>7003353</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5165,16 +5155,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849918</t>
+          <t>https://artportalen.se/Sighting/135849893</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135849919</v>
+        <v>135849894</v>
       </c>
       <c r="B39" t="n">
-        <v>108364</v>
+        <v>101375</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5182,21 +5172,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220102</v>
+        <v>224885</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5214,10 +5204,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>500511</v>
+        <v>500470</v>
       </c>
       <c r="R39" t="n">
-        <v>7003325</v>
+        <v>7003356</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5264,7 +5254,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5281,16 +5271,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849919</t>
+          <t>https://artportalen.se/Sighting/135849894</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135849920</v>
+        <v>135849895</v>
       </c>
       <c r="B40" t="n">
-        <v>108364</v>
+        <v>101375</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5298,28 +5288,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220102</v>
+        <v>224885</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -5330,10 +5320,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>500416</v>
+        <v>500496</v>
       </c>
       <c r="R40" t="n">
-        <v>7003258</v>
+        <v>7003339</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5397,16 +5387,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849920</t>
+          <t>https://artportalen.se/Sighting/135849895</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135849921</v>
+        <v>135849896</v>
       </c>
       <c r="B41" t="n">
-        <v>108364</v>
+        <v>101375</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5414,28 +5404,28 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220102</v>
+        <v>224885</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -5446,10 +5436,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>500474</v>
+        <v>500524</v>
       </c>
       <c r="R41" t="n">
-        <v>7003267</v>
+        <v>7003325</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5496,7 +5486,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5513,16 +5503,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849921</t>
+          <t>https://artportalen.se/Sighting/135849896</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135849922</v>
+        <v>135849897</v>
       </c>
       <c r="B42" t="n">
-        <v>108364</v>
+        <v>101375</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5530,28 +5520,28 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220102</v>
+        <v>224885</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -5562,10 +5552,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>500448</v>
+        <v>500461</v>
       </c>
       <c r="R42" t="n">
-        <v>7003286</v>
+        <v>7003234</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5612,7 +5602,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5629,16 +5619,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849922</t>
+          <t>https://artportalen.se/Sighting/135849897</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135849923</v>
+        <v>135849898</v>
       </c>
       <c r="B43" t="n">
-        <v>108364</v>
+        <v>101375</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5646,28 +5636,28 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220102</v>
+        <v>224885</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -5678,10 +5668,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>500415</v>
+        <v>500438</v>
       </c>
       <c r="R43" t="n">
-        <v>7003291</v>
+        <v>7003234</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5745,16 +5735,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849923</t>
+          <t>https://artportalen.se/Sighting/135849898</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135849909</v>
+        <v>135849899</v>
       </c>
       <c r="B44" t="n">
-        <v>111244</v>
+        <v>101375</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5762,21 +5752,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220240</v>
+        <v>224885</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5794,10 +5784,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>500546</v>
+        <v>500480</v>
       </c>
       <c r="R44" t="n">
-        <v>7003124</v>
+        <v>7003325</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5844,7 +5834,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5861,16 +5851,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849909</t>
+          <t>https://artportalen.se/Sighting/135849899</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135849910</v>
+        <v>135849900</v>
       </c>
       <c r="B45" t="n">
-        <v>111244</v>
+        <v>101375</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5878,21 +5868,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220240</v>
+        <v>224885</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5910,10 +5900,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>500461</v>
+        <v>500469</v>
       </c>
       <c r="R45" t="n">
-        <v>7003351</v>
+        <v>7003260</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5977,53 +5967,45 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849910</t>
+          <t>https://artportalen.se/Sighting/135849900</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135849974</v>
+        <v>135849901</v>
       </c>
       <c r="B46" t="n">
-        <v>99276</v>
+        <v>101375</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>224885</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -6034,10 +6016,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>500511</v>
+        <v>500470</v>
       </c>
       <c r="R46" t="n">
-        <v>7003332</v>
+        <v>7003268</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6072,11 +6054,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor och 10 överblommade blomställningar inom ca 2 x 2 m2 yta i granskog.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6106,53 +6083,45 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849974</t>
+          <t>https://artportalen.se/Sighting/135849901</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135849975</v>
+        <v>135849902</v>
       </c>
       <c r="B47" t="n">
-        <v>99276</v>
+        <v>101375</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>224885</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -6163,10 +6132,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>500529</v>
+        <v>500443</v>
       </c>
       <c r="R47" t="n">
-        <v>7003306</v>
+        <v>7003286</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6201,11 +6170,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Minst 30 plantor och 7 överblommade blomställningar inom ca 3 m2 yta i granskog.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6218,7 +6182,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6235,3444 +6199,7 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849975</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>135849976</v>
-      </c>
-      <c r="B48" t="n">
-        <v>99276</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>500652</v>
-      </c>
-      <c r="R48" t="n">
-        <v>7003184</v>
-      </c>
-      <c r="S48" t="n">
-        <v>10</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst 120 plantor varav 30 med överblommade blomställningar inom ca 8 m2 yta i granskog.</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="inlineStr"/>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849976</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>135849977</v>
-      </c>
-      <c r="B49" t="n">
-        <v>99276</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>500570</v>
-      </c>
-      <c r="R49" t="n">
-        <v>7003141</v>
-      </c>
-      <c r="S49" t="n">
-        <v>10</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor och 13 överblommade blomställningar inom ca 1,5 m2 yta i granskog.</t>
-        </is>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF49" t="inlineStr"/>
-      <c r="AG49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849977</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>135849978</v>
-      </c>
-      <c r="B50" t="n">
-        <v>99276</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>500507</v>
-      </c>
-      <c r="R50" t="n">
-        <v>7003191</v>
-      </c>
-      <c r="S50" t="n">
-        <v>10</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Minst 30 plantor och 15 överblommade blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
-        </is>
-      </c>
-      <c r="AD50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="inlineStr"/>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849978</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>135849979</v>
-      </c>
-      <c r="B51" t="n">
-        <v>99276</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>500400</v>
-      </c>
-      <c r="R51" t="n">
-        <v>7003285</v>
-      </c>
-      <c r="S51" t="n">
-        <v>10</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Minst 120 plantor och 20 mestadels överblommade blomställningar inom ca 2 m2 yta på ett moss- och granöverväxt block.</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="inlineStr"/>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849979</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>135849862</v>
-      </c>
-      <c r="B52" t="n">
-        <v>110014</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>221184</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Torta</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Lactuca alpina</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>500497</v>
-      </c>
-      <c r="R52" t="n">
-        <v>7003367</v>
-      </c>
-      <c r="S52" t="n">
-        <v>10</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF52" t="inlineStr"/>
-      <c r="AG52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849862</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>135849863</v>
-      </c>
-      <c r="B53" t="n">
-        <v>110014</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>221184</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Torta</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Lactuca alpina</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q53" t="n">
-        <v>500524</v>
-      </c>
-      <c r="R53" t="n">
-        <v>7003318</v>
-      </c>
-      <c r="S53" t="n">
-        <v>10</v>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="inlineStr"/>
-      <c r="AG53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AW53" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849863</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>135849864</v>
-      </c>
-      <c r="B54" t="n">
-        <v>110014</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>221184</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Torta</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Lactuca alpina</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>500480</v>
-      </c>
-      <c r="R54" t="n">
-        <v>7003262</v>
-      </c>
-      <c r="S54" t="n">
-        <v>10</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF54" t="inlineStr"/>
-      <c r="AG54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849864</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>135849876</v>
-      </c>
-      <c r="B55" t="n">
-        <v>99298</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>500545</v>
-      </c>
-      <c r="R55" t="n">
-        <v>7003269</v>
-      </c>
-      <c r="S55" t="n">
-        <v>10</v>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF55" t="inlineStr"/>
-      <c r="AG55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849876</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>135850039</v>
-      </c>
-      <c r="B56" t="n">
-        <v>101485</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>500509</v>
-      </c>
-      <c r="R56" t="n">
-        <v>7003354</v>
-      </c>
-      <c r="S56" t="n">
-        <v>10</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF56" t="inlineStr"/>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850039</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>135850040</v>
-      </c>
-      <c r="B57" t="n">
-        <v>101485</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>500494</v>
-      </c>
-      <c r="R57" t="n">
-        <v>7003341</v>
-      </c>
-      <c r="S57" t="n">
-        <v>10</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF57" t="inlineStr"/>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850040</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>135850042</v>
-      </c>
-      <c r="B58" t="n">
-        <v>101485</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>500509</v>
-      </c>
-      <c r="R58" t="n">
-        <v>7003330</v>
-      </c>
-      <c r="S58" t="n">
-        <v>10</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF58" t="inlineStr"/>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
-      </c>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850042</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>135850043</v>
-      </c>
-      <c r="B59" t="n">
-        <v>101485</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>500523</v>
-      </c>
-      <c r="R59" t="n">
-        <v>7003129</v>
-      </c>
-      <c r="S59" t="n">
-        <v>10</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF59" t="inlineStr"/>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850043</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>135850044</v>
-      </c>
-      <c r="B60" t="n">
-        <v>101485</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q60" t="n">
-        <v>500450</v>
-      </c>
-      <c r="R60" t="n">
-        <v>7003243</v>
-      </c>
-      <c r="S60" t="n">
-        <v>10</v>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF60" t="inlineStr"/>
-      <c r="AG60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850044</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>135849915</v>
-      </c>
-      <c r="B61" t="n">
-        <v>99553</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>222812</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Liljekonvalj</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Convallaria majalis</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q61" t="n">
-        <v>500491</v>
-      </c>
-      <c r="R61" t="n">
-        <v>7003234</v>
-      </c>
-      <c r="S61" t="n">
-        <v>10</v>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF61" t="inlineStr"/>
-      <c r="AG61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849915</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>135849889</v>
-      </c>
-      <c r="B62" t="n">
-        <v>99082</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>223049</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Ormbär</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Paris quadrifolia</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q62" t="n">
-        <v>500512</v>
-      </c>
-      <c r="R62" t="n">
-        <v>7003140</v>
-      </c>
-      <c r="S62" t="n">
-        <v>10</v>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF62" t="inlineStr"/>
-      <c r="AG62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849889</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>135849996</v>
-      </c>
-      <c r="B63" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>500520</v>
-      </c>
-      <c r="R63" t="n">
-        <v>7003324</v>
-      </c>
-      <c r="S63" t="n">
-        <v>10</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF63" t="inlineStr"/>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849996</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>135849997</v>
-      </c>
-      <c r="B64" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>500533</v>
-      </c>
-      <c r="R64" t="n">
-        <v>7003286</v>
-      </c>
-      <c r="S64" t="n">
-        <v>10</v>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF64" t="inlineStr"/>
-      <c r="AG64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849997</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>135849998</v>
-      </c>
-      <c r="B65" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>500474</v>
-      </c>
-      <c r="R65" t="n">
-        <v>7003265</v>
-      </c>
-      <c r="S65" t="n">
-        <v>10</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF65" t="inlineStr"/>
-      <c r="AG65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT65" t="inlineStr"/>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849998</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>135849893</v>
-      </c>
-      <c r="B66" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>500510</v>
-      </c>
-      <c r="R66" t="n">
-        <v>7003353</v>
-      </c>
-      <c r="S66" t="n">
-        <v>10</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF66" t="inlineStr"/>
-      <c r="AG66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Högörtbarrskog</t>
-        </is>
-      </c>
-      <c r="AT66" t="inlineStr"/>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849893</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>135849894</v>
-      </c>
-      <c r="B67" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q67" t="n">
-        <v>500470</v>
-      </c>
-      <c r="R67" t="n">
-        <v>7003356</v>
-      </c>
-      <c r="S67" t="n">
-        <v>10</v>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF67" t="inlineStr"/>
-      <c r="AG67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Högörtbarrskog</t>
-        </is>
-      </c>
-      <c r="AT67" t="inlineStr"/>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849894</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>135849895</v>
-      </c>
-      <c r="B68" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q68" t="n">
-        <v>500496</v>
-      </c>
-      <c r="R68" t="n">
-        <v>7003339</v>
-      </c>
-      <c r="S68" t="n">
-        <v>10</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF68" t="inlineStr"/>
-      <c r="AG68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Högörtbarrskog</t>
-        </is>
-      </c>
-      <c r="AT68" t="inlineStr"/>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849895</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>135849896</v>
-      </c>
-      <c r="B69" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>500524</v>
-      </c>
-      <c r="R69" t="n">
-        <v>7003325</v>
-      </c>
-      <c r="S69" t="n">
-        <v>10</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF69" t="inlineStr"/>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849896</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>135849897</v>
-      </c>
-      <c r="B70" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>500461</v>
-      </c>
-      <c r="R70" t="n">
-        <v>7003234</v>
-      </c>
-      <c r="S70" t="n">
-        <v>10</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF70" t="inlineStr"/>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849897</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>135849898</v>
-      </c>
-      <c r="B71" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>500438</v>
-      </c>
-      <c r="R71" t="n">
-        <v>7003234</v>
-      </c>
-      <c r="S71" t="n">
-        <v>10</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF71" t="inlineStr"/>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849898</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>135849899</v>
-      </c>
-      <c r="B72" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>500480</v>
-      </c>
-      <c r="R72" t="n">
-        <v>7003325</v>
-      </c>
-      <c r="S72" t="n">
-        <v>10</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF72" t="inlineStr"/>
-      <c r="AG72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT72" t="inlineStr"/>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849899</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>135849900</v>
-      </c>
-      <c r="B73" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>500469</v>
-      </c>
-      <c r="R73" t="n">
-        <v>7003260</v>
-      </c>
-      <c r="S73" t="n">
-        <v>10</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF73" t="inlineStr"/>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849900</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>135849901</v>
-      </c>
-      <c r="B74" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>500470</v>
-      </c>
-      <c r="R74" t="n">
-        <v>7003268</v>
-      </c>
-      <c r="S74" t="n">
-        <v>10</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF74" t="inlineStr"/>
-      <c r="AG74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT74" t="inlineStr"/>
-      <c r="AW74" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849901</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>135849902</v>
-      </c>
-      <c r="B75" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q75" t="n">
-        <v>500443</v>
-      </c>
-      <c r="R75" t="n">
-        <v>7003286</v>
-      </c>
-      <c r="S75" t="n">
-        <v>10</v>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF75" t="inlineStr"/>
-      <c r="AG75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT75" t="inlineStr"/>
-      <c r="AW75" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
-      <c r="AZ75" t="inlineStr">
-        <is>
           <t>https://artportalen.se/Sighting/135849902</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>135849903</v>
-      </c>
-      <c r="B76" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q76" t="n">
-        <v>500429</v>
-      </c>
-      <c r="R76" t="n">
-        <v>7003294</v>
-      </c>
-      <c r="S76" t="n">
-        <v>10</v>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF76" t="inlineStr"/>
-      <c r="AG76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT76" t="inlineStr"/>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849903</t>
         </is>
       </c>
     </row>
@@ -9724,35 +6251,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28050-2026 artfynd.xlsx
+++ b/artfynd/A 28050-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ47"/>
+  <dimension ref="A1:AZ76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1464,7 +1464,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135850018</v>
+        <v>135850014</v>
       </c>
       <c r="B9" t="n">
         <v>79441</v>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500425</v>
+        <v>500484</v>
       </c>
       <c r="R9" t="n">
-        <v>7003323</v>
+        <v>7003356</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,11 +1540,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1557,7 +1552,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1589,63 +1584,54 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850018</t>
+          <t>https://artportalen.se/Sighting/135850014</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135849842</v>
+        <v>135850015</v>
       </c>
       <c r="B10" t="n">
-        <v>57980</v>
+        <v>79441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500404</v>
+        <v>500586</v>
       </c>
       <c r="R10" t="n">
-        <v>7003270</v>
+        <v>7003162</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1682,7 +1668,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran med spår av rikligt med kådaflöde.</t>
+          <t>Långväxta bålar på gran i granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,12 +1677,13 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1711,12 +1698,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1733,48 +1720,43 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849842</t>
+          <t>https://artportalen.se/Sighting/135850015</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135849843</v>
+        <v>135850016</v>
       </c>
       <c r="B11" t="n">
-        <v>57980</v>
+        <v>79441</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1782,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500404</v>
+        <v>500552</v>
       </c>
       <c r="R11" t="n">
-        <v>7003271</v>
+        <v>7003131</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1820,23 +1802,19 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1849,14 +1827,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1873,63 +1846,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849843</t>
+          <t>https://artportalen.se/Sighting/135850016</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135849844</v>
+        <v>135850017</v>
       </c>
       <c r="B12" t="n">
-        <v>57980</v>
+        <v>79441</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500403</v>
+        <v>500505</v>
       </c>
       <c r="R12" t="n">
-        <v>7003276</v>
+        <v>7003184</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1966,7 +1930,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Långväxta bålar på gran i granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1975,12 +1939,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -1993,14 +1958,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2017,63 +1977,54 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849844</t>
+          <t>https://artportalen.se/Sighting/135850017</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135849845</v>
+        <v>135850018</v>
       </c>
       <c r="B13" t="n">
-        <v>57980</v>
+        <v>79441</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500377</v>
+        <v>500425</v>
       </c>
       <c r="R13" t="n">
-        <v>7003317</v>
+        <v>7003323</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2110,7 +2061,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2119,6 +2070,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2137,14 +2089,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2161,67 +2108,63 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849845</t>
+          <t>https://artportalen.se/Sighting/135850018</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135849841</v>
+        <v>135849842</v>
       </c>
       <c r="B14" t="n">
-        <v>99300</v>
+        <v>57980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500424</v>
+        <v>500404</v>
       </c>
       <c r="R14" t="n">
-        <v>7003277</v>
+        <v>7003270</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2258,7 +2201,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Minst 3 plantor som växer i ett örtrikt fältskikt på fuktig mark.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran med spår av rikligt med kådaflöde.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2267,13 +2210,32 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2290,48 +2252,48 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849841</t>
+          <t>https://artportalen.se/Sighting/135849842</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135849936</v>
+        <v>135849843</v>
       </c>
       <c r="B15" t="n">
-        <v>99614</v>
+        <v>57980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2339,10 +2301,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500459</v>
+        <v>500404</v>
       </c>
       <c r="R15" t="n">
-        <v>7003232</v>
+        <v>7003271</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2377,19 +2339,43 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2406,59 +2392,63 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849936</t>
+          <t>https://artportalen.se/Sighting/135849843</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135849937</v>
+        <v>135849844</v>
       </c>
       <c r="B16" t="n">
-        <v>99614</v>
+        <v>57980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500481</v>
+        <v>500403</v>
       </c>
       <c r="R16" t="n">
-        <v>7003274</v>
+        <v>7003276</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2493,19 +2483,43 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2522,59 +2536,63 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849937</t>
+          <t>https://artportalen.se/Sighting/135849844</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135849917</v>
+        <v>135849845</v>
       </c>
       <c r="B17" t="n">
-        <v>108364</v>
+        <v>57980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220102</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500456</v>
+        <v>500377</v>
       </c>
       <c r="R17" t="n">
-        <v>7003316</v>
+        <v>7003317</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2609,19 +2627,43 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2638,16 +2680,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849917</t>
+          <t>https://artportalen.se/Sighting/135849845</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135849918</v>
+        <v>135850027</v>
       </c>
       <c r="B18" t="n">
-        <v>108364</v>
+        <v>99193</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,21 +2697,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220102</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2687,10 +2729,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500488</v>
+        <v>500425</v>
       </c>
       <c r="R18" t="n">
-        <v>7003344</v>
+        <v>7003277</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2725,6 +2767,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Växer här i ett stort örtrikt fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2737,7 +2784,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2754,16 +2801,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849918</t>
+          <t>https://artportalen.se/Sighting/135850027</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135849919</v>
+        <v>135850012</v>
       </c>
       <c r="B19" t="n">
-        <v>108364</v>
+        <v>99175</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,28 +2818,36 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220102</v>
+        <v>219795</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -2803,10 +2858,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500511</v>
+        <v>500521</v>
       </c>
       <c r="R19" t="n">
-        <v>7003325</v>
+        <v>7003130</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2870,16 +2925,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849919</t>
+          <t>https://artportalen.se/Sighting/135850012</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135849920</v>
+        <v>135850029</v>
       </c>
       <c r="B20" t="n">
-        <v>108364</v>
+        <v>99278</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,25 +2942,33 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220102</v>
+        <v>219811</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -2919,10 +2982,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500416</v>
+        <v>500389</v>
       </c>
       <c r="R20" t="n">
-        <v>7003258</v>
+        <v>7003289</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2969,7 +3032,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2986,16 +3049,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849920</t>
+          <t>https://artportalen.se/Sighting/135850029</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135849921</v>
+        <v>135849834</v>
       </c>
       <c r="B21" t="n">
-        <v>108364</v>
+        <v>99300</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,28 +3066,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220102</v>
+        <v>219847</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -3035,10 +3098,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500474</v>
+        <v>500475</v>
       </c>
       <c r="R21" t="n">
-        <v>7003267</v>
+        <v>7003332</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3102,16 +3165,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849921</t>
+          <t>https://artportalen.se/Sighting/135849834</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135849922</v>
+        <v>135849835</v>
       </c>
       <c r="B22" t="n">
-        <v>108364</v>
+        <v>99300</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,28 +3182,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220102</v>
+        <v>219847</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -3151,10 +3214,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>500448</v>
+        <v>500456</v>
       </c>
       <c r="R22" t="n">
-        <v>7003286</v>
+        <v>7003229</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3201,7 +3264,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3218,16 +3281,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849922</t>
+          <t>https://artportalen.se/Sighting/135849835</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135849923</v>
+        <v>135849836</v>
       </c>
       <c r="B23" t="n">
-        <v>108364</v>
+        <v>99300</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,21 +3298,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220102</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3267,10 +3330,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500415</v>
+        <v>500435</v>
       </c>
       <c r="R23" t="n">
-        <v>7003291</v>
+        <v>7003231</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3334,16 +3397,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849923</t>
+          <t>https://artportalen.se/Sighting/135849836</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135849909</v>
+        <v>135849837</v>
       </c>
       <c r="B24" t="n">
-        <v>111244</v>
+        <v>99300</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3351,28 +3414,28 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220240</v>
+        <v>219847</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -3383,10 +3446,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>500546</v>
+        <v>500408</v>
       </c>
       <c r="R24" t="n">
-        <v>7003124</v>
+        <v>7003263</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3433,7 +3496,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3450,16 +3513,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849909</t>
+          <t>https://artportalen.se/Sighting/135849837</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135849910</v>
+        <v>135849838</v>
       </c>
       <c r="B25" t="n">
-        <v>111244</v>
+        <v>99300</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3467,28 +3530,28 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220240</v>
+        <v>219847</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -3499,10 +3562,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500461</v>
+        <v>500394</v>
       </c>
       <c r="R25" t="n">
-        <v>7003351</v>
+        <v>7003275</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3566,50 +3629,42 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849910</t>
+          <t>https://artportalen.se/Sighting/135849838</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135849975</v>
+        <v>135849839</v>
       </c>
       <c r="B26" t="n">
-        <v>99276</v>
+        <v>99300</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -3623,10 +3678,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>500529</v>
+        <v>500397</v>
       </c>
       <c r="R26" t="n">
-        <v>7003306</v>
+        <v>7003280</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3661,11 +3716,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Minst 30 plantor och 7 överblommade blomställningar inom ca 3 m2 yta i granskog.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3678,7 +3728,12 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Örtrik barrskog på stor del fuktig mark.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3695,71 +3750,59 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849975</t>
+          <t>https://artportalen.se/Sighting/135849839</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135849976</v>
+        <v>135849840</v>
       </c>
       <c r="B27" t="n">
-        <v>99276</v>
+        <v>99300</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>500652</v>
+        <v>500478</v>
       </c>
       <c r="R27" t="n">
-        <v>7003184</v>
+        <v>7003263</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3794,11 +3837,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Minst 120 plantor varav 30 med överblommade blomställningar inom ca 8 m2 yta i granskog.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3811,7 +3849,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3828,43 +3866,43 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849976</t>
+          <t>https://artportalen.se/Sighting/135849840</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135849977</v>
+        <v>135849841</v>
       </c>
       <c r="B28" t="n">
-        <v>99276</v>
+        <v>99300</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3878,21 +3916,17 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>500570</v>
+        <v>500424</v>
       </c>
       <c r="R28" t="n">
-        <v>7003141</v>
+        <v>7003277</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3929,7 +3963,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 13 överblommade blomställningar inom ca 1,5 m2 yta i granskog.</t>
+          <t>Minst 3 plantor som växer i ett örtrikt fältskikt på fuktig mark.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3944,7 +3978,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3961,71 +3995,59 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849977</t>
+          <t>https://artportalen.se/Sighting/135849841</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135849978</v>
+        <v>135849936</v>
       </c>
       <c r="B29" t="n">
-        <v>99276</v>
+        <v>99614</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500507</v>
+        <v>500459</v>
       </c>
       <c r="R29" t="n">
-        <v>7003191</v>
+        <v>7003232</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4060,11 +4082,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst 30 plantor och 15 överblommade blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4077,7 +4094,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4094,71 +4111,59 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849978</t>
+          <t>https://artportalen.se/Sighting/135849936</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135849979</v>
+        <v>135849937</v>
       </c>
       <c r="B30" t="n">
-        <v>99276</v>
+        <v>99614</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>500400</v>
+        <v>500481</v>
       </c>
       <c r="R30" t="n">
-        <v>7003285</v>
+        <v>7003274</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4193,11 +4198,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 120 plantor och 20 mestadels överblommade blomställningar inom ca 2 m2 yta på ett moss- och granöverväxt block.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4227,16 +4227,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849979</t>
+          <t>https://artportalen.se/Sighting/135849937</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135849862</v>
+        <v>135850030</v>
       </c>
       <c r="B31" t="n">
-        <v>110014</v>
+        <v>108294</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4244,28 +4244,28 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221184</v>
+        <v>220083</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -4276,10 +4276,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500497</v>
+        <v>500467</v>
       </c>
       <c r="R31" t="n">
-        <v>7003367</v>
+        <v>7003353</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4343,16 +4343,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849862</t>
+          <t>https://artportalen.se/Sighting/135850030</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135849863</v>
+        <v>135850031</v>
       </c>
       <c r="B32" t="n">
-        <v>110014</v>
+        <v>108294</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4360,21 +4360,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221184</v>
+        <v>220083</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500524</v>
+        <v>500476</v>
       </c>
       <c r="R32" t="n">
-        <v>7003318</v>
+        <v>7003332</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4442,7 +4442,12 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Örtrik barrskog på kalkrik fuktig mark.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4459,16 +4464,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849863</t>
+          <t>https://artportalen.se/Sighting/135850031</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135849864</v>
+        <v>135850032</v>
       </c>
       <c r="B33" t="n">
-        <v>110014</v>
+        <v>108294</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4476,21 +4481,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221184</v>
+        <v>220083</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4508,10 +4513,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500480</v>
+        <v>500513</v>
       </c>
       <c r="R33" t="n">
-        <v>7003262</v>
+        <v>7003327</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4575,16 +4580,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849864</t>
+          <t>https://artportalen.se/Sighting/135850032</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135849915</v>
+        <v>135850033</v>
       </c>
       <c r="B34" t="n">
-        <v>99553</v>
+        <v>108294</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4592,28 +4597,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222812</v>
+        <v>220083</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -4624,7 +4629,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>500491</v>
+        <v>500572</v>
       </c>
       <c r="R34" t="n">
         <v>7003234</v>
@@ -4691,16 +4696,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849915</t>
+          <t>https://artportalen.se/Sighting/135850033</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135849996</v>
+        <v>135850034</v>
       </c>
       <c r="B35" t="n">
-        <v>98327</v>
+        <v>108294</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4708,21 +4713,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>223358</v>
+        <v>220083</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4740,10 +4745,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>500520</v>
+        <v>500399</v>
       </c>
       <c r="R35" t="n">
-        <v>7003324</v>
+        <v>7003277</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4790,7 +4795,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4807,16 +4812,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849996</t>
+          <t>https://artportalen.se/Sighting/135850034</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135849997</v>
+        <v>135850035</v>
       </c>
       <c r="B36" t="n">
-        <v>98327</v>
+        <v>108294</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4824,28 +4829,28 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>223358</v>
+        <v>220083</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -4856,10 +4861,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>500533</v>
+        <v>500389</v>
       </c>
       <c r="R36" t="n">
-        <v>7003286</v>
+        <v>7003293</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4906,7 +4911,12 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Örtrik barrskog på fuktig mark.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4923,16 +4933,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849997</t>
+          <t>https://artportalen.se/Sighting/135850035</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135849998</v>
+        <v>135849917</v>
       </c>
       <c r="B37" t="n">
-        <v>98327</v>
+        <v>108364</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4940,28 +4950,28 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>223358</v>
+        <v>220102</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -4972,10 +4982,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>500474</v>
+        <v>500456</v>
       </c>
       <c r="R37" t="n">
-        <v>7003265</v>
+        <v>7003316</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5022,7 +5032,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5039,16 +5049,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849998</t>
+          <t>https://artportalen.se/Sighting/135849917</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135849893</v>
+        <v>135849918</v>
       </c>
       <c r="B38" t="n">
-        <v>101375</v>
+        <v>108364</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5056,28 +5066,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>224885</v>
+        <v>220102</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5088,10 +5098,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>500510</v>
+        <v>500488</v>
       </c>
       <c r="R38" t="n">
-        <v>7003353</v>
+        <v>7003344</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5155,16 +5165,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849893</t>
+          <t>https://artportalen.se/Sighting/135849918</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135849894</v>
+        <v>135849919</v>
       </c>
       <c r="B39" t="n">
-        <v>101375</v>
+        <v>108364</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5172,21 +5182,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>224885</v>
+        <v>220102</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5204,10 +5214,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>500470</v>
+        <v>500511</v>
       </c>
       <c r="R39" t="n">
-        <v>7003356</v>
+        <v>7003325</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5254,7 +5264,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5271,16 +5281,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849894</t>
+          <t>https://artportalen.se/Sighting/135849919</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135849895</v>
+        <v>135849920</v>
       </c>
       <c r="B40" t="n">
-        <v>101375</v>
+        <v>108364</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5288,28 +5298,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>224885</v>
+        <v>220102</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -5320,10 +5330,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>500496</v>
+        <v>500416</v>
       </c>
       <c r="R40" t="n">
-        <v>7003339</v>
+        <v>7003258</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5387,16 +5397,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849895</t>
+          <t>https://artportalen.se/Sighting/135849920</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135849896</v>
+        <v>135849921</v>
       </c>
       <c r="B41" t="n">
-        <v>101375</v>
+        <v>108364</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5404,28 +5414,28 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>224885</v>
+        <v>220102</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -5436,10 +5446,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>500524</v>
+        <v>500474</v>
       </c>
       <c r="R41" t="n">
-        <v>7003325</v>
+        <v>7003267</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5486,7 +5496,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5503,16 +5513,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849896</t>
+          <t>https://artportalen.se/Sighting/135849921</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135849897</v>
+        <v>135849922</v>
       </c>
       <c r="B42" t="n">
-        <v>101375</v>
+        <v>108364</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5520,28 +5530,28 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>224885</v>
+        <v>220102</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -5552,10 +5562,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>500461</v>
+        <v>500448</v>
       </c>
       <c r="R42" t="n">
-        <v>7003234</v>
+        <v>7003286</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5602,7 +5612,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5619,16 +5629,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849897</t>
+          <t>https://artportalen.se/Sighting/135849922</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135849898</v>
+        <v>135849923</v>
       </c>
       <c r="B43" t="n">
-        <v>101375</v>
+        <v>108364</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5636,28 +5646,28 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>224885</v>
+        <v>220102</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -5668,10 +5678,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>500438</v>
+        <v>500415</v>
       </c>
       <c r="R43" t="n">
-        <v>7003234</v>
+        <v>7003291</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5735,16 +5745,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849898</t>
+          <t>https://artportalen.se/Sighting/135849923</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135849899</v>
+        <v>135849909</v>
       </c>
       <c r="B44" t="n">
-        <v>101375</v>
+        <v>111244</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5752,21 +5762,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>224885</v>
+        <v>220240</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5784,10 +5794,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>500480</v>
+        <v>500546</v>
       </c>
       <c r="R44" t="n">
-        <v>7003325</v>
+        <v>7003124</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5834,7 +5844,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5851,16 +5861,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849899</t>
+          <t>https://artportalen.se/Sighting/135849909</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135849900</v>
+        <v>135849910</v>
       </c>
       <c r="B45" t="n">
-        <v>101375</v>
+        <v>111244</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5868,21 +5878,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>224885</v>
+        <v>220240</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5900,10 +5910,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>500469</v>
+        <v>500461</v>
       </c>
       <c r="R45" t="n">
-        <v>7003260</v>
+        <v>7003351</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5967,45 +5977,53 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849900</t>
+          <t>https://artportalen.se/Sighting/135849910</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135849901</v>
+        <v>135849974</v>
       </c>
       <c r="B46" t="n">
-        <v>101375</v>
+        <v>99276</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>224885</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -6016,10 +6034,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>500470</v>
+        <v>500511</v>
       </c>
       <c r="R46" t="n">
-        <v>7003268</v>
+        <v>7003332</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6054,6 +6072,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor och 10 överblommade blomställningar inom ca 2 x 2 m2 yta i granskog.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6083,45 +6106,53 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849901</t>
+          <t>https://artportalen.se/Sighting/135849974</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135849902</v>
+        <v>135849975</v>
       </c>
       <c r="B47" t="n">
-        <v>101375</v>
+        <v>99276</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>224885</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -6132,10 +6163,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>500443</v>
+        <v>500529</v>
       </c>
       <c r="R47" t="n">
-        <v>7003286</v>
+        <v>7003306</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6170,6 +6201,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Minst 30 plantor och 7 överblommade blomställningar inom ca 3 m2 yta i granskog.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6182,7 +6218,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6199,7 +6235,3444 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135849975</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135849976</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>500652</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7003184</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Minst 120 plantor varav 30 med överblommade blomställningar inom ca 8 m2 yta i granskog.</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849976</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135849977</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>500570</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7003141</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor och 13 överblommade blomställningar inom ca 1,5 m2 yta i granskog.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849977</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135849978</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>500507</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7003191</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Minst 30 plantor och 15 överblommade blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849978</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135849979</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>500400</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7003285</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Minst 120 plantor och 20 mestadels överblommade blomställningar inom ca 2 m2 yta på ett moss- och granöverväxt block.</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849979</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135849862</v>
+      </c>
+      <c r="B52" t="n">
+        <v>110014</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>500497</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7003367</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849862</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135849863</v>
+      </c>
+      <c r="B53" t="n">
+        <v>110014</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>500524</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7003318</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849863</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135849864</v>
+      </c>
+      <c r="B54" t="n">
+        <v>110014</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>500480</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7003262</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849864</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135849876</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>500545</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7003269</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849876</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135850039</v>
+      </c>
+      <c r="B56" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>500509</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7003354</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850039</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135850040</v>
+      </c>
+      <c r="B57" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>500494</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7003341</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850040</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135850042</v>
+      </c>
+      <c r="B58" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>500509</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7003330</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850042</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135850043</v>
+      </c>
+      <c r="B59" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>500523</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7003129</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850043</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135850044</v>
+      </c>
+      <c r="B60" t="n">
+        <v>101485</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>500450</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7003243</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850044</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135849915</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99553</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>500491</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7003234</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849915</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135849889</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99082</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>500512</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7003140</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849889</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135849996</v>
+      </c>
+      <c r="B63" t="n">
+        <v>98327</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>500520</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7003324</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849996</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135849997</v>
+      </c>
+      <c r="B64" t="n">
+        <v>98327</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>500533</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7003286</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849997</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135849998</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98327</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>500474</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7003265</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849998</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135849893</v>
+      </c>
+      <c r="B66" t="n">
+        <v>101375</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>500510</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7003353</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Högörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849893</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135849894</v>
+      </c>
+      <c r="B67" t="n">
+        <v>101375</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>500470</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7003356</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Högörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849894</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>135849895</v>
+      </c>
+      <c r="B68" t="n">
+        <v>101375</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>500496</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7003339</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Högörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849895</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135849896</v>
+      </c>
+      <c r="B69" t="n">
+        <v>101375</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>500524</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7003325</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849896</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135849897</v>
+      </c>
+      <c r="B70" t="n">
+        <v>101375</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>500461</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7003234</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849897</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135849898</v>
+      </c>
+      <c r="B71" t="n">
+        <v>101375</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>500438</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7003234</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849898</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135849899</v>
+      </c>
+      <c r="B72" t="n">
+        <v>101375</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>500480</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7003325</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849899</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135849900</v>
+      </c>
+      <c r="B73" t="n">
+        <v>101375</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>500469</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7003260</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849900</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135849901</v>
+      </c>
+      <c r="B74" t="n">
+        <v>101375</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>500470</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7003268</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849901</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135849902</v>
+      </c>
+      <c r="B75" t="n">
+        <v>101375</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>500443</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7003286</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135849902</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135849903</v>
+      </c>
+      <c r="B76" t="n">
+        <v>101375</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>500429</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7003294</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849903</t>
         </is>
       </c>
     </row>
@@ -6251,6 +9724,35 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28050-2026 artfynd.xlsx
+++ b/artfynd/A 28050-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ76"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>135849953</v>
       </c>
       <c r="B2" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135849954</v>
       </c>
       <c r="B3" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135849955</v>
       </c>
       <c r="B4" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135849956</v>
       </c>
       <c r="B5" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135849957</v>
       </c>
       <c r="B6" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135849958</v>
       </c>
       <c r="B7" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135849959</v>
       </c>
       <c r="B8" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135850014</v>
+        <v>135850018</v>
       </c>
       <c r="B9" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500484</v>
+        <v>500425</v>
       </c>
       <c r="R9" t="n">
-        <v>7003356</v>
+        <v>7003323</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,6 +1540,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1552,7 +1557,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1584,54 +1589,63 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850014</t>
+          <t>https://artportalen.se/Sighting/135850018</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135850015</v>
+        <v>135849842</v>
       </c>
       <c r="B10" t="n">
-        <v>79441</v>
+        <v>57982</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500586</v>
+        <v>500404</v>
       </c>
       <c r="R10" t="n">
-        <v>7003162</v>
+        <v>7003270</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1682,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i granskog.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran med spår av rikligt med kådaflöde.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1677,13 +1691,12 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1698,12 +1711,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1720,43 +1733,48 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850015</t>
+          <t>https://artportalen.se/Sighting/135849842</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135850016</v>
+        <v>135849843</v>
       </c>
       <c r="B11" t="n">
-        <v>79441</v>
+        <v>57982</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1764,10 +1782,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500552</v>
+        <v>500404</v>
       </c>
       <c r="R11" t="n">
-        <v>7003131</v>
+        <v>7003271</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,19 +1820,23 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1827,9 +1849,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1846,54 +1873,63 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850016</t>
+          <t>https://artportalen.se/Sighting/135849843</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135850017</v>
+        <v>135849844</v>
       </c>
       <c r="B12" t="n">
-        <v>79441</v>
+        <v>57982</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500505</v>
+        <v>500403</v>
       </c>
       <c r="R12" t="n">
-        <v>7003184</v>
+        <v>7003276</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1930,7 +1966,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i granskog.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1939,13 +1975,12 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -1958,9 +1993,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1977,54 +2017,63 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850017</t>
+          <t>https://artportalen.se/Sighting/135849844</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135850018</v>
+        <v>135849845</v>
       </c>
       <c r="B13" t="n">
-        <v>79441</v>
+        <v>57982</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500425</v>
+        <v>500377</v>
       </c>
       <c r="R13" t="n">
-        <v>7003323</v>
+        <v>7003317</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2061,7 +2110,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2070,7 +2119,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2089,9 +2137,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2108,63 +2161,67 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850018</t>
+          <t>https://artportalen.se/Sighting/135849845</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135849842</v>
+        <v>135849841</v>
       </c>
       <c r="B14" t="n">
-        <v>57980</v>
+        <v>99317</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500404</v>
+        <v>500424</v>
       </c>
       <c r="R14" t="n">
-        <v>7003270</v>
+        <v>7003277</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2201,7 +2258,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran med spår av rikligt med kådaflöde.</t>
+          <t>Minst 3 plantor som växer i ett örtrikt fältskikt på fuktig mark.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2210,32 +2267,13 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2252,48 +2290,48 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849842</t>
+          <t>https://artportalen.se/Sighting/135849841</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135849843</v>
+        <v>135849936</v>
       </c>
       <c r="B15" t="n">
-        <v>57980</v>
+        <v>99631</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2301,10 +2339,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500404</v>
+        <v>500459</v>
       </c>
       <c r="R15" t="n">
-        <v>7003271</v>
+        <v>7003232</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2339,43 +2377,19 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2392,63 +2406,59 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849843</t>
+          <t>https://artportalen.se/Sighting/135849936</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135849844</v>
+        <v>135849937</v>
       </c>
       <c r="B16" t="n">
-        <v>57980</v>
+        <v>99631</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500403</v>
+        <v>500481</v>
       </c>
       <c r="R16" t="n">
-        <v>7003276</v>
+        <v>7003274</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2483,43 +2493,19 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2536,63 +2522,59 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849844</t>
+          <t>https://artportalen.se/Sighting/135849937</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135849845</v>
+        <v>135849917</v>
       </c>
       <c r="B17" t="n">
-        <v>57980</v>
+        <v>108387</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220102</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500377</v>
+        <v>500456</v>
       </c>
       <c r="R17" t="n">
-        <v>7003317</v>
+        <v>7003316</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2627,43 +2609,19 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2680,16 +2638,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849845</t>
+          <t>https://artportalen.se/Sighting/135849917</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135850027</v>
+        <v>135849918</v>
       </c>
       <c r="B18" t="n">
-        <v>99193</v>
+        <v>108387</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2697,21 +2655,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>220102</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2729,10 +2687,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500425</v>
+        <v>500488</v>
       </c>
       <c r="R18" t="n">
-        <v>7003277</v>
+        <v>7003344</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2767,11 +2725,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Växer här i ett stort örtrikt fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2784,7 +2737,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2801,16 +2754,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850027</t>
+          <t>https://artportalen.se/Sighting/135849918</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135850012</v>
+        <v>135849919</v>
       </c>
       <c r="B19" t="n">
-        <v>99175</v>
+        <v>108387</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2818,36 +2771,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219795</v>
+        <v>220102</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -2858,10 +2803,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500521</v>
+        <v>500511</v>
       </c>
       <c r="R19" t="n">
-        <v>7003130</v>
+        <v>7003325</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2925,16 +2870,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850012</t>
+          <t>https://artportalen.se/Sighting/135849919</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135850029</v>
+        <v>135849920</v>
       </c>
       <c r="B20" t="n">
-        <v>99278</v>
+        <v>108387</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2942,33 +2887,25 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219811</v>
+        <v>220102</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -2982,10 +2919,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500389</v>
+        <v>500416</v>
       </c>
       <c r="R20" t="n">
-        <v>7003289</v>
+        <v>7003258</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3032,7 +2969,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3049,16 +2986,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850029</t>
+          <t>https://artportalen.se/Sighting/135849920</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135849834</v>
+        <v>135849921</v>
       </c>
       <c r="B21" t="n">
-        <v>99300</v>
+        <v>108387</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3066,28 +3003,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219847</v>
+        <v>220102</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -3098,10 +3035,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500475</v>
+        <v>500474</v>
       </c>
       <c r="R21" t="n">
-        <v>7003332</v>
+        <v>7003267</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3165,16 +3102,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849834</t>
+          <t>https://artportalen.se/Sighting/135849921</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135849835</v>
+        <v>135849922</v>
       </c>
       <c r="B22" t="n">
-        <v>99300</v>
+        <v>108387</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3182,28 +3119,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219847</v>
+        <v>220102</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -3214,10 +3151,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>500456</v>
+        <v>500448</v>
       </c>
       <c r="R22" t="n">
-        <v>7003229</v>
+        <v>7003286</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3264,7 +3201,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3281,16 +3218,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849835</t>
+          <t>https://artportalen.se/Sighting/135849922</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135849836</v>
+        <v>135849923</v>
       </c>
       <c r="B23" t="n">
-        <v>99300</v>
+        <v>108387</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3298,21 +3235,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>220102</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3330,10 +3267,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500435</v>
+        <v>500415</v>
       </c>
       <c r="R23" t="n">
-        <v>7003231</v>
+        <v>7003291</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3397,16 +3334,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849836</t>
+          <t>https://artportalen.se/Sighting/135849923</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135849837</v>
+        <v>135849909</v>
       </c>
       <c r="B24" t="n">
-        <v>99300</v>
+        <v>111267</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3414,28 +3351,28 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219847</v>
+        <v>220240</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -3446,10 +3383,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>500408</v>
+        <v>500546</v>
       </c>
       <c r="R24" t="n">
-        <v>7003263</v>
+        <v>7003124</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3496,7 +3433,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3513,16 +3450,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849837</t>
+          <t>https://artportalen.se/Sighting/135849909</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135849838</v>
+        <v>135849910</v>
       </c>
       <c r="B25" t="n">
-        <v>99300</v>
+        <v>111267</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3530,28 +3467,28 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219847</v>
+        <v>220240</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -3562,10 +3499,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500394</v>
+        <v>500461</v>
       </c>
       <c r="R25" t="n">
-        <v>7003275</v>
+        <v>7003351</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3629,42 +3566,50 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849838</t>
+          <t>https://artportalen.se/Sighting/135849910</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135849839</v>
+        <v>135849975</v>
       </c>
       <c r="B26" t="n">
-        <v>99300</v>
+        <v>99293</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -3678,10 +3623,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>500397</v>
+        <v>500529</v>
       </c>
       <c r="R26" t="n">
-        <v>7003280</v>
+        <v>7003306</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3716,6 +3661,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minst 30 plantor och 7 överblommade blomställningar inom ca 3 m2 yta i granskog.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3728,12 +3678,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Örtrik barrskog på stor del fuktig mark.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3750,59 +3695,71 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849839</t>
+          <t>https://artportalen.se/Sighting/135849975</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135849840</v>
+        <v>135849976</v>
       </c>
       <c r="B27" t="n">
-        <v>99300</v>
+        <v>99293</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>500478</v>
+        <v>500652</v>
       </c>
       <c r="R27" t="n">
-        <v>7003263</v>
+        <v>7003184</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3837,6 +3794,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Minst 120 plantor varav 30 med överblommade blomställningar inom ca 8 m2 yta i granskog.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3849,7 +3811,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3866,43 +3828,43 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849840</t>
+          <t>https://artportalen.se/Sighting/135849976</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135849841</v>
+        <v>135849977</v>
       </c>
       <c r="B28" t="n">
-        <v>99300</v>
+        <v>99293</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3916,17 +3878,21 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>500424</v>
+        <v>500570</v>
       </c>
       <c r="R28" t="n">
-        <v>7003277</v>
+        <v>7003141</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3963,7 +3929,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Minst 3 plantor som växer i ett örtrikt fältskikt på fuktig mark.</t>
+          <t>Minst 70 plantor och 13 överblommade blomställningar inom ca 1,5 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3978,7 +3944,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3995,59 +3961,71 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849841</t>
+          <t>https://artportalen.se/Sighting/135849977</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135849936</v>
+        <v>135849978</v>
       </c>
       <c r="B29" t="n">
-        <v>99614</v>
+        <v>99293</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500459</v>
+        <v>500507</v>
       </c>
       <c r="R29" t="n">
-        <v>7003232</v>
+        <v>7003191</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4082,6 +4060,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minst 30 plantor och 15 överblommade blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4094,7 +4077,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4111,59 +4094,71 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849936</t>
+          <t>https://artportalen.se/Sighting/135849978</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135849937</v>
+        <v>135849979</v>
       </c>
       <c r="B30" t="n">
-        <v>99614</v>
+        <v>99293</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>500481</v>
+        <v>500400</v>
       </c>
       <c r="R30" t="n">
-        <v>7003274</v>
+        <v>7003285</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4198,6 +4193,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 120 plantor och 20 mestadels överblommade blomställningar inom ca 2 m2 yta på ett moss- och granöverväxt block.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4227,16 +4227,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849937</t>
+          <t>https://artportalen.se/Sighting/135849979</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135850030</v>
+        <v>135849862</v>
       </c>
       <c r="B31" t="n">
-        <v>108294</v>
+        <v>110037</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4244,28 +4244,28 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220083</v>
+        <v>221184</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -4276,10 +4276,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500467</v>
+        <v>500497</v>
       </c>
       <c r="R31" t="n">
-        <v>7003353</v>
+        <v>7003367</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4343,16 +4343,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850030</t>
+          <t>https://artportalen.se/Sighting/135849862</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135850031</v>
+        <v>135849863</v>
       </c>
       <c r="B32" t="n">
-        <v>108294</v>
+        <v>110037</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4360,21 +4360,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220083</v>
+        <v>221184</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500476</v>
+        <v>500524</v>
       </c>
       <c r="R32" t="n">
-        <v>7003332</v>
+        <v>7003318</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4442,12 +4442,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Örtrik barrskog på kalkrik fuktig mark.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4464,16 +4459,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850031</t>
+          <t>https://artportalen.se/Sighting/135849863</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135850032</v>
+        <v>135849864</v>
       </c>
       <c r="B33" t="n">
-        <v>108294</v>
+        <v>110037</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4481,21 +4476,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220083</v>
+        <v>221184</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4513,10 +4508,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500513</v>
+        <v>500480</v>
       </c>
       <c r="R33" t="n">
-        <v>7003327</v>
+        <v>7003262</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4580,16 +4575,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850032</t>
+          <t>https://artportalen.se/Sighting/135849864</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135850033</v>
+        <v>135849915</v>
       </c>
       <c r="B34" t="n">
-        <v>108294</v>
+        <v>99570</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4597,28 +4592,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220083</v>
+        <v>222812</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -4629,7 +4624,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>500572</v>
+        <v>500491</v>
       </c>
       <c r="R34" t="n">
         <v>7003234</v>
@@ -4696,16 +4691,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850033</t>
+          <t>https://artportalen.se/Sighting/135849915</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135850034</v>
+        <v>135849996</v>
       </c>
       <c r="B35" t="n">
-        <v>108294</v>
+        <v>98344</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4713,21 +4708,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220083</v>
+        <v>223358</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4745,10 +4740,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>500399</v>
+        <v>500520</v>
       </c>
       <c r="R35" t="n">
-        <v>7003277</v>
+        <v>7003324</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4795,7 +4790,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4812,16 +4807,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850034</t>
+          <t>https://artportalen.se/Sighting/135849996</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135850035</v>
+        <v>135849997</v>
       </c>
       <c r="B36" t="n">
-        <v>108294</v>
+        <v>98344</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4829,28 +4824,28 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220083</v>
+        <v>223358</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -4861,10 +4856,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>500389</v>
+        <v>500533</v>
       </c>
       <c r="R36" t="n">
-        <v>7003293</v>
+        <v>7003286</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4911,12 +4906,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Örtrik barrskog på fuktig mark.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4933,16 +4923,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850035</t>
+          <t>https://artportalen.se/Sighting/135849997</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135849917</v>
+        <v>135849998</v>
       </c>
       <c r="B37" t="n">
-        <v>108364</v>
+        <v>98344</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4950,28 +4940,28 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220102</v>
+        <v>223358</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -4982,10 +4972,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>500456</v>
+        <v>500474</v>
       </c>
       <c r="R37" t="n">
-        <v>7003316</v>
+        <v>7003265</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5032,7 +5022,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5049,16 +5039,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849917</t>
+          <t>https://artportalen.se/Sighting/135849998</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135849918</v>
+        <v>135849893</v>
       </c>
       <c r="B38" t="n">
-        <v>108364</v>
+        <v>101392</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5066,28 +5056,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220102</v>
+        <v>224885</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5098,10 +5088,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>500488</v>
+        <v>500510</v>
       </c>
       <c r="R38" t="n">
-        <v>7003344</v>
+        <v>7003353</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5165,16 +5155,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849918</t>
+          <t>https://artportalen.se/Sighting/135849893</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135849919</v>
+        <v>135849894</v>
       </c>
       <c r="B39" t="n">
-        <v>108364</v>
+        <v>101392</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5182,21 +5172,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220102</v>
+        <v>224885</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5214,10 +5204,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>500511</v>
+        <v>500470</v>
       </c>
       <c r="R39" t="n">
-        <v>7003325</v>
+        <v>7003356</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5264,7 +5254,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5281,16 +5271,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849919</t>
+          <t>https://artportalen.se/Sighting/135849894</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135849920</v>
+        <v>135849895</v>
       </c>
       <c r="B40" t="n">
-        <v>108364</v>
+        <v>101392</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5298,28 +5288,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220102</v>
+        <v>224885</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -5330,10 +5320,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>500416</v>
+        <v>500496</v>
       </c>
       <c r="R40" t="n">
-        <v>7003258</v>
+        <v>7003339</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5397,16 +5387,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849920</t>
+          <t>https://artportalen.se/Sighting/135849895</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135849921</v>
+        <v>135849896</v>
       </c>
       <c r="B41" t="n">
-        <v>108364</v>
+        <v>101392</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5414,28 +5404,28 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220102</v>
+        <v>224885</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -5446,10 +5436,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>500474</v>
+        <v>500524</v>
       </c>
       <c r="R41" t="n">
-        <v>7003267</v>
+        <v>7003325</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5496,7 +5486,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5513,16 +5503,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849921</t>
+          <t>https://artportalen.se/Sighting/135849896</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135849922</v>
+        <v>135849897</v>
       </c>
       <c r="B42" t="n">
-        <v>108364</v>
+        <v>101392</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5530,28 +5520,28 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220102</v>
+        <v>224885</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -5562,10 +5552,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>500448</v>
+        <v>500461</v>
       </c>
       <c r="R42" t="n">
-        <v>7003286</v>
+        <v>7003234</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5612,7 +5602,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5629,16 +5619,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849922</t>
+          <t>https://artportalen.se/Sighting/135849897</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135849923</v>
+        <v>135849898</v>
       </c>
       <c r="B43" t="n">
-        <v>108364</v>
+        <v>101392</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5646,28 +5636,28 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220102</v>
+        <v>224885</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -5678,10 +5668,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>500415</v>
+        <v>500438</v>
       </c>
       <c r="R43" t="n">
-        <v>7003291</v>
+        <v>7003234</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5745,16 +5735,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849923</t>
+          <t>https://artportalen.se/Sighting/135849898</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135849909</v>
+        <v>135849899</v>
       </c>
       <c r="B44" t="n">
-        <v>111244</v>
+        <v>101392</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5762,21 +5752,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220240</v>
+        <v>224885</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5794,10 +5784,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>500546</v>
+        <v>500480</v>
       </c>
       <c r="R44" t="n">
-        <v>7003124</v>
+        <v>7003325</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5844,7 +5834,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5861,16 +5851,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849909</t>
+          <t>https://artportalen.se/Sighting/135849899</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135849910</v>
+        <v>135849900</v>
       </c>
       <c r="B45" t="n">
-        <v>111244</v>
+        <v>101392</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5878,21 +5868,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220240</v>
+        <v>224885</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5910,10 +5900,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>500461</v>
+        <v>500469</v>
       </c>
       <c r="R45" t="n">
-        <v>7003351</v>
+        <v>7003260</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5977,53 +5967,45 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849910</t>
+          <t>https://artportalen.se/Sighting/135849900</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135849974</v>
+        <v>135849901</v>
       </c>
       <c r="B46" t="n">
-        <v>99276</v>
+        <v>101392</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>224885</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -6034,10 +6016,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>500511</v>
+        <v>500470</v>
       </c>
       <c r="R46" t="n">
-        <v>7003332</v>
+        <v>7003268</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6072,11 +6054,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor och 10 överblommade blomställningar inom ca 2 x 2 m2 yta i granskog.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6106,53 +6083,45 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849974</t>
+          <t>https://artportalen.se/Sighting/135849901</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135849975</v>
+        <v>135849902</v>
       </c>
       <c r="B47" t="n">
-        <v>99276</v>
+        <v>101392</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>224885</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -6163,10 +6132,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>500529</v>
+        <v>500443</v>
       </c>
       <c r="R47" t="n">
-        <v>7003306</v>
+        <v>7003286</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6201,11 +6170,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Minst 30 plantor och 7 överblommade blomställningar inom ca 3 m2 yta i granskog.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6218,7 +6182,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6235,3444 +6199,7 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849975</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>135849976</v>
-      </c>
-      <c r="B48" t="n">
-        <v>99276</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>500652</v>
-      </c>
-      <c r="R48" t="n">
-        <v>7003184</v>
-      </c>
-      <c r="S48" t="n">
-        <v>10</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst 120 plantor varav 30 med överblommade blomställningar inom ca 8 m2 yta i granskog.</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="inlineStr"/>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849976</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>135849977</v>
-      </c>
-      <c r="B49" t="n">
-        <v>99276</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>500570</v>
-      </c>
-      <c r="R49" t="n">
-        <v>7003141</v>
-      </c>
-      <c r="S49" t="n">
-        <v>10</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor och 13 överblommade blomställningar inom ca 1,5 m2 yta i granskog.</t>
-        </is>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF49" t="inlineStr"/>
-      <c r="AG49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849977</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>135849978</v>
-      </c>
-      <c r="B50" t="n">
-        <v>99276</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>500507</v>
-      </c>
-      <c r="R50" t="n">
-        <v>7003191</v>
-      </c>
-      <c r="S50" t="n">
-        <v>10</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Minst 30 plantor och 15 överblommade blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
-        </is>
-      </c>
-      <c r="AD50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="inlineStr"/>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849978</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>135849979</v>
-      </c>
-      <c r="B51" t="n">
-        <v>99276</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>500400</v>
-      </c>
-      <c r="R51" t="n">
-        <v>7003285</v>
-      </c>
-      <c r="S51" t="n">
-        <v>10</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Minst 120 plantor och 20 mestadels överblommade blomställningar inom ca 2 m2 yta på ett moss- och granöverväxt block.</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="inlineStr"/>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849979</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>135849862</v>
-      </c>
-      <c r="B52" t="n">
-        <v>110014</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>221184</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Torta</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Lactuca alpina</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>500497</v>
-      </c>
-      <c r="R52" t="n">
-        <v>7003367</v>
-      </c>
-      <c r="S52" t="n">
-        <v>10</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF52" t="inlineStr"/>
-      <c r="AG52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849862</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>135849863</v>
-      </c>
-      <c r="B53" t="n">
-        <v>110014</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>221184</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Torta</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Lactuca alpina</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q53" t="n">
-        <v>500524</v>
-      </c>
-      <c r="R53" t="n">
-        <v>7003318</v>
-      </c>
-      <c r="S53" t="n">
-        <v>10</v>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="inlineStr"/>
-      <c r="AG53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AW53" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849863</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>135849864</v>
-      </c>
-      <c r="B54" t="n">
-        <v>110014</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>221184</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Torta</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Lactuca alpina</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>500480</v>
-      </c>
-      <c r="R54" t="n">
-        <v>7003262</v>
-      </c>
-      <c r="S54" t="n">
-        <v>10</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF54" t="inlineStr"/>
-      <c r="AG54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849864</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>135849876</v>
-      </c>
-      <c r="B55" t="n">
-        <v>99298</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>500545</v>
-      </c>
-      <c r="R55" t="n">
-        <v>7003269</v>
-      </c>
-      <c r="S55" t="n">
-        <v>10</v>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF55" t="inlineStr"/>
-      <c r="AG55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849876</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>135850039</v>
-      </c>
-      <c r="B56" t="n">
-        <v>101485</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>500509</v>
-      </c>
-      <c r="R56" t="n">
-        <v>7003354</v>
-      </c>
-      <c r="S56" t="n">
-        <v>10</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF56" t="inlineStr"/>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850039</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>135850040</v>
-      </c>
-      <c r="B57" t="n">
-        <v>101485</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>500494</v>
-      </c>
-      <c r="R57" t="n">
-        <v>7003341</v>
-      </c>
-      <c r="S57" t="n">
-        <v>10</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF57" t="inlineStr"/>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850040</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>135850042</v>
-      </c>
-      <c r="B58" t="n">
-        <v>101485</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>500509</v>
-      </c>
-      <c r="R58" t="n">
-        <v>7003330</v>
-      </c>
-      <c r="S58" t="n">
-        <v>10</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF58" t="inlineStr"/>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
-      </c>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850042</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>135850043</v>
-      </c>
-      <c r="B59" t="n">
-        <v>101485</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>500523</v>
-      </c>
-      <c r="R59" t="n">
-        <v>7003129</v>
-      </c>
-      <c r="S59" t="n">
-        <v>10</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF59" t="inlineStr"/>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850043</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>135850044</v>
-      </c>
-      <c r="B60" t="n">
-        <v>101485</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q60" t="n">
-        <v>500450</v>
-      </c>
-      <c r="R60" t="n">
-        <v>7003243</v>
-      </c>
-      <c r="S60" t="n">
-        <v>10</v>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF60" t="inlineStr"/>
-      <c r="AG60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850044</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>135849915</v>
-      </c>
-      <c r="B61" t="n">
-        <v>99553</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>222812</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Liljekonvalj</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Convallaria majalis</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q61" t="n">
-        <v>500491</v>
-      </c>
-      <c r="R61" t="n">
-        <v>7003234</v>
-      </c>
-      <c r="S61" t="n">
-        <v>10</v>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF61" t="inlineStr"/>
-      <c r="AG61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849915</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>135849889</v>
-      </c>
-      <c r="B62" t="n">
-        <v>99082</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>223049</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Ormbär</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Paris quadrifolia</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q62" t="n">
-        <v>500512</v>
-      </c>
-      <c r="R62" t="n">
-        <v>7003140</v>
-      </c>
-      <c r="S62" t="n">
-        <v>10</v>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF62" t="inlineStr"/>
-      <c r="AG62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849889</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>135849996</v>
-      </c>
-      <c r="B63" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>500520</v>
-      </c>
-      <c r="R63" t="n">
-        <v>7003324</v>
-      </c>
-      <c r="S63" t="n">
-        <v>10</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF63" t="inlineStr"/>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849996</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>135849997</v>
-      </c>
-      <c r="B64" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>500533</v>
-      </c>
-      <c r="R64" t="n">
-        <v>7003286</v>
-      </c>
-      <c r="S64" t="n">
-        <v>10</v>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF64" t="inlineStr"/>
-      <c r="AG64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849997</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>135849998</v>
-      </c>
-      <c r="B65" t="n">
-        <v>98327</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>500474</v>
-      </c>
-      <c r="R65" t="n">
-        <v>7003265</v>
-      </c>
-      <c r="S65" t="n">
-        <v>10</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF65" t="inlineStr"/>
-      <c r="AG65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT65" t="inlineStr"/>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849998</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>135849893</v>
-      </c>
-      <c r="B66" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>500510</v>
-      </c>
-      <c r="R66" t="n">
-        <v>7003353</v>
-      </c>
-      <c r="S66" t="n">
-        <v>10</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF66" t="inlineStr"/>
-      <c r="AG66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Högörtbarrskog</t>
-        </is>
-      </c>
-      <c r="AT66" t="inlineStr"/>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849893</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>135849894</v>
-      </c>
-      <c r="B67" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q67" t="n">
-        <v>500470</v>
-      </c>
-      <c r="R67" t="n">
-        <v>7003356</v>
-      </c>
-      <c r="S67" t="n">
-        <v>10</v>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF67" t="inlineStr"/>
-      <c r="AG67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Högörtbarrskog</t>
-        </is>
-      </c>
-      <c r="AT67" t="inlineStr"/>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849894</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>135849895</v>
-      </c>
-      <c r="B68" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q68" t="n">
-        <v>500496</v>
-      </c>
-      <c r="R68" t="n">
-        <v>7003339</v>
-      </c>
-      <c r="S68" t="n">
-        <v>10</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF68" t="inlineStr"/>
-      <c r="AG68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Högörtbarrskog</t>
-        </is>
-      </c>
-      <c r="AT68" t="inlineStr"/>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849895</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>135849896</v>
-      </c>
-      <c r="B69" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>500524</v>
-      </c>
-      <c r="R69" t="n">
-        <v>7003325</v>
-      </c>
-      <c r="S69" t="n">
-        <v>10</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF69" t="inlineStr"/>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849896</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>135849897</v>
-      </c>
-      <c r="B70" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>500461</v>
-      </c>
-      <c r="R70" t="n">
-        <v>7003234</v>
-      </c>
-      <c r="S70" t="n">
-        <v>10</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF70" t="inlineStr"/>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849897</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>135849898</v>
-      </c>
-      <c r="B71" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>500438</v>
-      </c>
-      <c r="R71" t="n">
-        <v>7003234</v>
-      </c>
-      <c r="S71" t="n">
-        <v>10</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF71" t="inlineStr"/>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849898</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>135849899</v>
-      </c>
-      <c r="B72" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>500480</v>
-      </c>
-      <c r="R72" t="n">
-        <v>7003325</v>
-      </c>
-      <c r="S72" t="n">
-        <v>10</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF72" t="inlineStr"/>
-      <c r="AG72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT72" t="inlineStr"/>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849899</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>135849900</v>
-      </c>
-      <c r="B73" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>500469</v>
-      </c>
-      <c r="R73" t="n">
-        <v>7003260</v>
-      </c>
-      <c r="S73" t="n">
-        <v>10</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF73" t="inlineStr"/>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849900</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>135849901</v>
-      </c>
-      <c r="B74" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>500470</v>
-      </c>
-      <c r="R74" t="n">
-        <v>7003268</v>
-      </c>
-      <c r="S74" t="n">
-        <v>10</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF74" t="inlineStr"/>
-      <c r="AG74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT74" t="inlineStr"/>
-      <c r="AW74" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849901</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>135849902</v>
-      </c>
-      <c r="B75" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q75" t="n">
-        <v>500443</v>
-      </c>
-      <c r="R75" t="n">
-        <v>7003286</v>
-      </c>
-      <c r="S75" t="n">
-        <v>10</v>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF75" t="inlineStr"/>
-      <c r="AG75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT75" t="inlineStr"/>
-      <c r="AW75" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
-      <c r="AZ75" t="inlineStr">
-        <is>
           <t>https://artportalen.se/Sighting/135849902</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>135849903</v>
-      </c>
-      <c r="B76" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q76" t="n">
-        <v>500429</v>
-      </c>
-      <c r="R76" t="n">
-        <v>7003294</v>
-      </c>
-      <c r="S76" t="n">
-        <v>10</v>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF76" t="inlineStr"/>
-      <c r="AG76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT76" t="inlineStr"/>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849903</t>
         </is>
       </c>
     </row>
@@ -9724,35 +6251,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28050-2026 artfynd.xlsx
+++ b/artfynd/A 28050-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ47"/>
+  <dimension ref="A1:AZ76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1464,7 +1464,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135850018</v>
+        <v>135850014</v>
       </c>
       <c r="B9" t="n">
         <v>79443</v>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500425</v>
+        <v>500484</v>
       </c>
       <c r="R9" t="n">
-        <v>7003323</v>
+        <v>7003356</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,11 +1540,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1557,7 +1552,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1589,63 +1584,54 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850018</t>
+          <t>https://artportalen.se/Sighting/135850014</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135849842</v>
+        <v>135850015</v>
       </c>
       <c r="B10" t="n">
-        <v>57982</v>
+        <v>79443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500404</v>
+        <v>500586</v>
       </c>
       <c r="R10" t="n">
-        <v>7003270</v>
+        <v>7003162</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1682,7 +1668,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran med spår av rikligt med kådaflöde.</t>
+          <t>Långväxta bålar på gran i granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,12 +1677,13 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1711,12 +1698,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1733,48 +1720,43 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849842</t>
+          <t>https://artportalen.se/Sighting/135850015</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135849843</v>
+        <v>135850016</v>
       </c>
       <c r="B11" t="n">
-        <v>57982</v>
+        <v>79443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1782,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500404</v>
+        <v>500552</v>
       </c>
       <c r="R11" t="n">
-        <v>7003271</v>
+        <v>7003131</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1820,23 +1802,19 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1849,14 +1827,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1873,63 +1846,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849843</t>
+          <t>https://artportalen.se/Sighting/135850016</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135849844</v>
+        <v>135850017</v>
       </c>
       <c r="B12" t="n">
-        <v>57982</v>
+        <v>79443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500403</v>
+        <v>500505</v>
       </c>
       <c r="R12" t="n">
-        <v>7003276</v>
+        <v>7003184</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1966,7 +1930,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Långväxta bålar på gran i granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1975,12 +1939,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -1993,14 +1958,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2017,63 +1977,54 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849844</t>
+          <t>https://artportalen.se/Sighting/135850017</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135849845</v>
+        <v>135850018</v>
       </c>
       <c r="B13" t="n">
-        <v>57982</v>
+        <v>79443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500377</v>
+        <v>500425</v>
       </c>
       <c r="R13" t="n">
-        <v>7003317</v>
+        <v>7003323</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2110,7 +2061,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2119,6 +2070,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2137,14 +2089,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2161,67 +2108,63 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849845</t>
+          <t>https://artportalen.se/Sighting/135850018</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135849841</v>
+        <v>135849842</v>
       </c>
       <c r="B14" t="n">
-        <v>99317</v>
+        <v>57982</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500424</v>
+        <v>500404</v>
       </c>
       <c r="R14" t="n">
-        <v>7003277</v>
+        <v>7003270</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2258,7 +2201,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Minst 3 plantor som växer i ett örtrikt fältskikt på fuktig mark.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran med spår av rikligt med kådaflöde.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2267,13 +2210,32 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2290,48 +2252,48 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849841</t>
+          <t>https://artportalen.se/Sighting/135849842</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135849936</v>
+        <v>135849843</v>
       </c>
       <c r="B15" t="n">
-        <v>99631</v>
+        <v>57982</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2339,10 +2301,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500459</v>
+        <v>500404</v>
       </c>
       <c r="R15" t="n">
-        <v>7003232</v>
+        <v>7003271</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2377,19 +2339,43 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2406,59 +2392,63 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849936</t>
+          <t>https://artportalen.se/Sighting/135849843</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135849937</v>
+        <v>135849844</v>
       </c>
       <c r="B16" t="n">
-        <v>99631</v>
+        <v>57982</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500481</v>
+        <v>500403</v>
       </c>
       <c r="R16" t="n">
-        <v>7003274</v>
+        <v>7003276</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2493,19 +2483,43 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2522,59 +2536,63 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849937</t>
+          <t>https://artportalen.se/Sighting/135849844</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135849917</v>
+        <v>135849845</v>
       </c>
       <c r="B17" t="n">
-        <v>108387</v>
+        <v>57982</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220102</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500456</v>
+        <v>500377</v>
       </c>
       <c r="R17" t="n">
-        <v>7003316</v>
+        <v>7003317</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2609,19 +2627,43 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2638,16 +2680,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849917</t>
+          <t>https://artportalen.se/Sighting/135849845</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135849918</v>
+        <v>135850027</v>
       </c>
       <c r="B18" t="n">
-        <v>108387</v>
+        <v>99210</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,21 +2697,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220102</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2687,10 +2729,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500488</v>
+        <v>500425</v>
       </c>
       <c r="R18" t="n">
-        <v>7003344</v>
+        <v>7003277</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2725,6 +2767,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Växer här i ett stort örtrikt fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2737,7 +2784,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2754,16 +2801,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849918</t>
+          <t>https://artportalen.se/Sighting/135850027</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135849919</v>
+        <v>135850012</v>
       </c>
       <c r="B19" t="n">
-        <v>108387</v>
+        <v>99192</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,28 +2818,36 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220102</v>
+        <v>219795</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -2803,10 +2858,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500511</v>
+        <v>500521</v>
       </c>
       <c r="R19" t="n">
-        <v>7003325</v>
+        <v>7003130</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2870,16 +2925,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849919</t>
+          <t>https://artportalen.se/Sighting/135850012</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135849920</v>
+        <v>135850029</v>
       </c>
       <c r="B20" t="n">
-        <v>108387</v>
+        <v>99295</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,25 +2942,33 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220102</v>
+        <v>219811</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -2919,10 +2982,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500416</v>
+        <v>500389</v>
       </c>
       <c r="R20" t="n">
-        <v>7003258</v>
+        <v>7003289</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2969,7 +3032,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2986,16 +3049,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849920</t>
+          <t>https://artportalen.se/Sighting/135850029</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135849921</v>
+        <v>135849834</v>
       </c>
       <c r="B21" t="n">
-        <v>108387</v>
+        <v>99317</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,28 +3066,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220102</v>
+        <v>219847</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -3035,10 +3098,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500474</v>
+        <v>500475</v>
       </c>
       <c r="R21" t="n">
-        <v>7003267</v>
+        <v>7003332</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3102,16 +3165,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849921</t>
+          <t>https://artportalen.se/Sighting/135849834</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135849922</v>
+        <v>135849835</v>
       </c>
       <c r="B22" t="n">
-        <v>108387</v>
+        <v>99317</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,28 +3182,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220102</v>
+        <v>219847</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -3151,10 +3214,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>500448</v>
+        <v>500456</v>
       </c>
       <c r="R22" t="n">
-        <v>7003286</v>
+        <v>7003229</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3201,7 +3264,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3218,16 +3281,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849922</t>
+          <t>https://artportalen.se/Sighting/135849835</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135849923</v>
+        <v>135849836</v>
       </c>
       <c r="B23" t="n">
-        <v>108387</v>
+        <v>99317</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,21 +3298,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220102</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3267,10 +3330,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500415</v>
+        <v>500435</v>
       </c>
       <c r="R23" t="n">
-        <v>7003291</v>
+        <v>7003231</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3334,16 +3397,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849923</t>
+          <t>https://artportalen.se/Sighting/135849836</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135849909</v>
+        <v>135849837</v>
       </c>
       <c r="B24" t="n">
-        <v>111267</v>
+        <v>99317</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3351,28 +3414,28 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220240</v>
+        <v>219847</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -3383,10 +3446,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>500546</v>
+        <v>500408</v>
       </c>
       <c r="R24" t="n">
-        <v>7003124</v>
+        <v>7003263</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3433,7 +3496,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3450,16 +3513,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849909</t>
+          <t>https://artportalen.se/Sighting/135849837</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135849910</v>
+        <v>135849838</v>
       </c>
       <c r="B25" t="n">
-        <v>111267</v>
+        <v>99317</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3467,28 +3530,28 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220240</v>
+        <v>219847</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -3499,10 +3562,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500461</v>
+        <v>500394</v>
       </c>
       <c r="R25" t="n">
-        <v>7003351</v>
+        <v>7003275</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3566,50 +3629,42 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849910</t>
+          <t>https://artportalen.se/Sighting/135849838</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135849975</v>
+        <v>135849839</v>
       </c>
       <c r="B26" t="n">
-        <v>99293</v>
+        <v>99317</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -3623,10 +3678,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>500529</v>
+        <v>500397</v>
       </c>
       <c r="R26" t="n">
-        <v>7003306</v>
+        <v>7003280</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3661,11 +3716,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Minst 30 plantor och 7 överblommade blomställningar inom ca 3 m2 yta i granskog.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3678,7 +3728,12 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Örtrik barrskog på stor del fuktig mark.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3695,71 +3750,59 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849975</t>
+          <t>https://artportalen.se/Sighting/135849839</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135849976</v>
+        <v>135849840</v>
       </c>
       <c r="B27" t="n">
-        <v>99293</v>
+        <v>99317</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>500652</v>
+        <v>500478</v>
       </c>
       <c r="R27" t="n">
-        <v>7003184</v>
+        <v>7003263</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3794,11 +3837,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Minst 120 plantor varav 30 med överblommade blomställningar inom ca 8 m2 yta i granskog.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3811,7 +3849,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3828,43 +3866,43 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849976</t>
+          <t>https://artportalen.se/Sighting/135849840</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135849977</v>
+        <v>135849841</v>
       </c>
       <c r="B28" t="n">
-        <v>99293</v>
+        <v>99317</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3878,21 +3916,17 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>500570</v>
+        <v>500424</v>
       </c>
       <c r="R28" t="n">
-        <v>7003141</v>
+        <v>7003277</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3929,7 +3963,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 13 överblommade blomställningar inom ca 1,5 m2 yta i granskog.</t>
+          <t>Minst 3 plantor som växer i ett örtrikt fältskikt på fuktig mark.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3944,7 +3978,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3961,71 +3995,59 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849977</t>
+          <t>https://artportalen.se/Sighting/135849841</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135849978</v>
+        <v>135849936</v>
       </c>
       <c r="B29" t="n">
-        <v>99293</v>
+        <v>99631</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500507</v>
+        <v>500459</v>
       </c>
       <c r="R29" t="n">
-        <v>7003191</v>
+        <v>7003232</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4060,11 +4082,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst 30 plantor och 15 överblommade blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4077,7 +4094,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4094,71 +4111,59 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849978</t>
+          <t>https://artportalen.se/Sighting/135849936</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135849979</v>
+        <v>135849937</v>
       </c>
       <c r="B30" t="n">
-        <v>99293</v>
+        <v>99631</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>500400</v>
+        <v>500481</v>
       </c>
       <c r="R30" t="n">
-        <v>7003285</v>
+        <v>7003274</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4193,11 +4198,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 120 plantor och 20 mestadels överblommade blomställningar inom ca 2 m2 yta på ett moss- och granöverväxt block.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4227,16 +4227,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849979</t>
+          <t>https://artportalen.se/Sighting/135849937</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135849862</v>
+        <v>135850030</v>
       </c>
       <c r="B31" t="n">
-        <v>110037</v>
+        <v>108317</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4244,28 +4244,28 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221184</v>
+        <v>220083</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -4276,10 +4276,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500497</v>
+        <v>500467</v>
       </c>
       <c r="R31" t="n">
-        <v>7003367</v>
+        <v>7003353</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4343,16 +4343,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849862</t>
+          <t>https://artportalen.se/Sighting/135850030</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135849863</v>
+        <v>135850031</v>
       </c>
       <c r="B32" t="n">
-        <v>110037</v>
+        <v>108317</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4360,21 +4360,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221184</v>
+        <v>220083</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500524</v>
+        <v>500476</v>
       </c>
       <c r="R32" t="n">
-        <v>7003318</v>
+        <v>7003332</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4442,7 +4442,12 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Örtrik barrskog på kalkrik fuktig mark.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4459,16 +4464,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849863</t>
+          <t>https://artportalen.se/Sighting/135850031</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135849864</v>
+        <v>135850032</v>
       </c>
       <c r="B33" t="n">
-        <v>110037</v>
+        <v>108317</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4476,21 +4481,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221184</v>
+        <v>220083</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4508,10 +4513,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500480</v>
+        <v>500513</v>
       </c>
       <c r="R33" t="n">
-        <v>7003262</v>
+        <v>7003327</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4575,16 +4580,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849864</t>
+          <t>https://artportalen.se/Sighting/135850032</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135849915</v>
+        <v>135850033</v>
       </c>
       <c r="B34" t="n">
-        <v>99570</v>
+        <v>108317</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4592,28 +4597,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222812</v>
+        <v>220083</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -4624,7 +4629,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>500491</v>
+        <v>500572</v>
       </c>
       <c r="R34" t="n">
         <v>7003234</v>
@@ -4691,16 +4696,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849915</t>
+          <t>https://artportalen.se/Sighting/135850033</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135849996</v>
+        <v>135850034</v>
       </c>
       <c r="B35" t="n">
-        <v>98344</v>
+        <v>108317</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4708,21 +4713,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>223358</v>
+        <v>220083</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4740,10 +4745,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>500520</v>
+        <v>500399</v>
       </c>
       <c r="R35" t="n">
-        <v>7003324</v>
+        <v>7003277</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4790,7 +4795,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4807,16 +4812,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849996</t>
+          <t>https://artportalen.se/Sighting/135850034</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135849997</v>
+        <v>135850035</v>
       </c>
       <c r="B36" t="n">
-        <v>98344</v>
+        <v>108317</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4824,28 +4829,28 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>223358</v>
+        <v>220083</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -4856,10 +4861,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>500533</v>
+        <v>500389</v>
       </c>
       <c r="R36" t="n">
-        <v>7003286</v>
+        <v>7003293</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4906,7 +4911,12 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Örtrik barrskog på fuktig mark.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4923,16 +4933,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849997</t>
+          <t>https://artportalen.se/Sighting/135850035</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135849998</v>
+        <v>135849917</v>
       </c>
       <c r="B37" t="n">
-        <v>98344</v>
+        <v>108387</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4940,28 +4950,28 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>223358</v>
+        <v>220102</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -4972,10 +4982,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>500474</v>
+        <v>500456</v>
       </c>
       <c r="R37" t="n">
-        <v>7003265</v>
+        <v>7003316</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5022,7 +5032,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5039,16 +5049,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849998</t>
+          <t>https://artportalen.se/Sighting/135849917</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135849893</v>
+        <v>135849918</v>
       </c>
       <c r="B38" t="n">
-        <v>101392</v>
+        <v>108387</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5056,28 +5066,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>224885</v>
+        <v>220102</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5088,10 +5098,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>500510</v>
+        <v>500488</v>
       </c>
       <c r="R38" t="n">
-        <v>7003353</v>
+        <v>7003344</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5155,16 +5165,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849893</t>
+          <t>https://artportalen.se/Sighting/135849918</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135849894</v>
+        <v>135849919</v>
       </c>
       <c r="B39" t="n">
-        <v>101392</v>
+        <v>108387</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5172,21 +5182,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>224885</v>
+        <v>220102</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5204,10 +5214,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>500470</v>
+        <v>500511</v>
       </c>
       <c r="R39" t="n">
-        <v>7003356</v>
+        <v>7003325</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5254,7 +5264,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5271,16 +5281,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849894</t>
+          <t>https://artportalen.se/Sighting/135849919</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135849895</v>
+        <v>135849920</v>
       </c>
       <c r="B40" t="n">
-        <v>101392</v>
+        <v>108387</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5288,28 +5298,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>224885</v>
+        <v>220102</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -5320,10 +5330,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>500496</v>
+        <v>500416</v>
       </c>
       <c r="R40" t="n">
-        <v>7003339</v>
+        <v>7003258</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5387,16 +5397,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849895</t>
+          <t>https://artportalen.se/Sighting/135849920</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135849896</v>
+        <v>135849921</v>
       </c>
       <c r="B41" t="n">
-        <v>101392</v>
+        <v>108387</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5404,28 +5414,28 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>224885</v>
+        <v>220102</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -5436,10 +5446,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>500524</v>
+        <v>500474</v>
       </c>
       <c r="R41" t="n">
-        <v>7003325</v>
+        <v>7003267</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5486,7 +5496,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5503,16 +5513,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849896</t>
+          <t>https://artportalen.se/Sighting/135849921</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135849897</v>
+        <v>135849922</v>
       </c>
       <c r="B42" t="n">
-        <v>101392</v>
+        <v>108387</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5520,28 +5530,28 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>224885</v>
+        <v>220102</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -5552,10 +5562,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>500461</v>
+        <v>500448</v>
       </c>
       <c r="R42" t="n">
-        <v>7003234</v>
+        <v>7003286</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5602,7 +5612,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5619,16 +5629,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849897</t>
+          <t>https://artportalen.se/Sighting/135849922</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135849898</v>
+        <v>135849923</v>
       </c>
       <c r="B43" t="n">
-        <v>101392</v>
+        <v>108387</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5636,28 +5646,28 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>224885</v>
+        <v>220102</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -5668,10 +5678,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>500438</v>
+        <v>500415</v>
       </c>
       <c r="R43" t="n">
-        <v>7003234</v>
+        <v>7003291</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5735,16 +5745,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849898</t>
+          <t>https://artportalen.se/Sighting/135849923</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135849899</v>
+        <v>135849909</v>
       </c>
       <c r="B44" t="n">
-        <v>101392</v>
+        <v>111267</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5752,21 +5762,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>224885</v>
+        <v>220240</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5784,10 +5794,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>500480</v>
+        <v>500546</v>
       </c>
       <c r="R44" t="n">
-        <v>7003325</v>
+        <v>7003124</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5834,7 +5844,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5851,16 +5861,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849899</t>
+          <t>https://artportalen.se/Sighting/135849909</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135849900</v>
+        <v>135849910</v>
       </c>
       <c r="B45" t="n">
-        <v>101392</v>
+        <v>111267</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5868,21 +5878,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>224885</v>
+        <v>220240</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5900,10 +5910,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>500469</v>
+        <v>500461</v>
       </c>
       <c r="R45" t="n">
-        <v>7003260</v>
+        <v>7003351</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5967,45 +5977,53 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849900</t>
+          <t>https://artportalen.se/Sighting/135849910</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135849901</v>
+        <v>135849974</v>
       </c>
       <c r="B46" t="n">
-        <v>101392</v>
+        <v>99293</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>224885</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -6016,10 +6034,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>500470</v>
+        <v>500511</v>
       </c>
       <c r="R46" t="n">
-        <v>7003268</v>
+        <v>7003332</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6054,6 +6072,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor och 10 överblommade blomställningar inom ca 2 x 2 m2 yta i granskog.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6083,45 +6106,53 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849901</t>
+          <t>https://artportalen.se/Sighting/135849974</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135849902</v>
+        <v>135849975</v>
       </c>
       <c r="B47" t="n">
-        <v>101392</v>
+        <v>99293</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>224885</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -6132,10 +6163,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>500443</v>
+        <v>500529</v>
       </c>
       <c r="R47" t="n">
-        <v>7003286</v>
+        <v>7003306</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6170,6 +6201,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Minst 30 plantor och 7 överblommade blomställningar inom ca 3 m2 yta i granskog.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6182,7 +6218,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6199,7 +6235,3444 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135849975</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135849976</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>500652</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7003184</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Minst 120 plantor varav 30 med överblommade blomställningar inom ca 8 m2 yta i granskog.</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849976</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135849977</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>500570</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7003141</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor och 13 överblommade blomställningar inom ca 1,5 m2 yta i granskog.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849977</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135849978</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>500507</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7003191</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Minst 30 plantor och 15 överblommade blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849978</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135849979</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>500400</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7003285</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Minst 120 plantor och 20 mestadels överblommade blomställningar inom ca 2 m2 yta på ett moss- och granöverväxt block.</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849979</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135849862</v>
+      </c>
+      <c r="B52" t="n">
+        <v>110037</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>500497</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7003367</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849862</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135849863</v>
+      </c>
+      <c r="B53" t="n">
+        <v>110037</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>500524</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7003318</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849863</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135849864</v>
+      </c>
+      <c r="B54" t="n">
+        <v>110037</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>500480</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7003262</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849864</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135849876</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99315</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>500545</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7003269</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849876</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135850039</v>
+      </c>
+      <c r="B56" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>500509</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7003354</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850039</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135850040</v>
+      </c>
+      <c r="B57" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>500494</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7003341</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850040</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135850042</v>
+      </c>
+      <c r="B58" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>500509</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7003330</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850042</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135850043</v>
+      </c>
+      <c r="B59" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>500523</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7003129</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850043</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135850044</v>
+      </c>
+      <c r="B60" t="n">
+        <v>101502</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>500450</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7003243</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850044</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135849915</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99570</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>500491</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7003234</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849915</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135849889</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99099</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>500512</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7003140</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849889</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135849996</v>
+      </c>
+      <c r="B63" t="n">
+        <v>98344</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>500520</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7003324</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849996</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135849997</v>
+      </c>
+      <c r="B64" t="n">
+        <v>98344</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>500533</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7003286</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849997</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135849998</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98344</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>500474</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7003265</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849998</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135849893</v>
+      </c>
+      <c r="B66" t="n">
+        <v>101392</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>500510</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7003353</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Högörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849893</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135849894</v>
+      </c>
+      <c r="B67" t="n">
+        <v>101392</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>500470</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7003356</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Högörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849894</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>135849895</v>
+      </c>
+      <c r="B68" t="n">
+        <v>101392</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>500496</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7003339</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Högörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849895</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135849896</v>
+      </c>
+      <c r="B69" t="n">
+        <v>101392</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>500524</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7003325</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849896</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135849897</v>
+      </c>
+      <c r="B70" t="n">
+        <v>101392</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>500461</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7003234</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849897</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135849898</v>
+      </c>
+      <c r="B71" t="n">
+        <v>101392</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>500438</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7003234</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849898</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135849899</v>
+      </c>
+      <c r="B72" t="n">
+        <v>101392</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>500480</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7003325</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849899</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135849900</v>
+      </c>
+      <c r="B73" t="n">
+        <v>101392</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>500469</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7003260</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849900</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135849901</v>
+      </c>
+      <c r="B74" t="n">
+        <v>101392</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>500470</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7003268</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849901</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135849902</v>
+      </c>
+      <c r="B75" t="n">
+        <v>101392</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>500443</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7003286</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135849902</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135849903</v>
+      </c>
+      <c r="B76" t="n">
+        <v>101392</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>500429</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7003294</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849903</t>
         </is>
       </c>
     </row>
@@ -6251,6 +9724,35 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28050-2026 artfynd.xlsx
+++ b/artfynd/A 28050-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135849953</v>
       </c>
       <c r="B2" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135849954</v>
       </c>
       <c r="B3" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135849955</v>
       </c>
       <c r="B4" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135849956</v>
       </c>
       <c r="B5" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135849957</v>
       </c>
       <c r="B6" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135849958</v>
       </c>
       <c r="B7" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135849959</v>
       </c>
       <c r="B8" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135850014</v>
       </c>
       <c r="B9" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>135850015</v>
       </c>
       <c r="B10" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>135850016</v>
       </c>
       <c r="B11" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>135850017</v>
       </c>
       <c r="B12" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>135850018</v>
       </c>
       <c r="B13" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135850027</v>
       </c>
       <c r="B18" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>135850012</v>
       </c>
       <c r="B19" t="n">
-        <v>99192</v>
+        <v>99193</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>135850029</v>
       </c>
       <c r="B20" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135849834</v>
       </c>
       <c r="B21" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>135849835</v>
       </c>
       <c r="B22" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>135849836</v>
       </c>
       <c r="B23" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>135849837</v>
       </c>
       <c r="B24" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>135849838</v>
       </c>
       <c r="B25" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>135849839</v>
       </c>
       <c r="B26" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>135849840</v>
       </c>
       <c r="B27" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>135849841</v>
       </c>
       <c r="B28" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>135849936</v>
       </c>
       <c r="B29" t="n">
-        <v>99631</v>
+        <v>99632</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>135849937</v>
       </c>
       <c r="B30" t="n">
-        <v>99631</v>
+        <v>99632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>135850030</v>
       </c>
       <c r="B31" t="n">
-        <v>108317</v>
+        <v>108319</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>135850031</v>
       </c>
       <c r="B32" t="n">
-        <v>108317</v>
+        <v>108319</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>135850032</v>
       </c>
       <c r="B33" t="n">
-        <v>108317</v>
+        <v>108319</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>135850033</v>
       </c>
       <c r="B34" t="n">
-        <v>108317</v>
+        <v>108319</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>135850034</v>
       </c>
       <c r="B35" t="n">
-        <v>108317</v>
+        <v>108319</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>135850035</v>
       </c>
       <c r="B36" t="n">
-        <v>108317</v>
+        <v>108319</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>135849917</v>
       </c>
       <c r="B37" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>135849918</v>
       </c>
       <c r="B38" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>135849919</v>
       </c>
       <c r="B39" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>135849920</v>
       </c>
       <c r="B40" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>135849921</v>
       </c>
       <c r="B41" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>135849922</v>
       </c>
       <c r="B42" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>135849923</v>
       </c>
       <c r="B43" t="n">
-        <v>108387</v>
+        <v>108389</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>135849909</v>
       </c>
       <c r="B44" t="n">
-        <v>111267</v>
+        <v>111269</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>135849910</v>
       </c>
       <c r="B45" t="n">
-        <v>111267</v>
+        <v>111269</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>135849974</v>
       </c>
       <c r="B46" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>135849975</v>
       </c>
       <c r="B47" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>135849976</v>
       </c>
       <c r="B48" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>135849977</v>
       </c>
       <c r="B49" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>135849978</v>
       </c>
       <c r="B50" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>135849979</v>
       </c>
       <c r="B51" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>135849862</v>
       </c>
       <c r="B52" t="n">
-        <v>110037</v>
+        <v>110039</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>135849863</v>
       </c>
       <c r="B53" t="n">
-        <v>110037</v>
+        <v>110039</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>135849864</v>
       </c>
       <c r="B54" t="n">
-        <v>110037</v>
+        <v>110039</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>135849876</v>
       </c>
       <c r="B55" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>135850039</v>
       </c>
       <c r="B56" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>135850040</v>
       </c>
       <c r="B57" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>135850042</v>
       </c>
       <c r="B58" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>135850043</v>
       </c>
       <c r="B59" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>135850044</v>
       </c>
       <c r="B60" t="n">
-        <v>101502</v>
+        <v>101504</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>135849915</v>
       </c>
       <c r="B61" t="n">
-        <v>99570</v>
+        <v>99571</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>135849889</v>
       </c>
       <c r="B62" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>135849996</v>
       </c>
       <c r="B63" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>135849997</v>
       </c>
       <c r="B64" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>135849998</v>
       </c>
       <c r="B65" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>135849893</v>
       </c>
       <c r="B66" t="n">
-        <v>101392</v>
+        <v>101394</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>135849894</v>
       </c>
       <c r="B67" t="n">
-        <v>101392</v>
+        <v>101394</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>135849895</v>
       </c>
       <c r="B68" t="n">
-        <v>101392</v>
+        <v>101394</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>135849896</v>
       </c>
       <c r="B69" t="n">
-        <v>101392</v>
+        <v>101394</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>135849897</v>
       </c>
       <c r="B70" t="n">
-        <v>101392</v>
+        <v>101394</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>135849898</v>
       </c>
       <c r="B71" t="n">
-        <v>101392</v>
+        <v>101394</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>135849899</v>
       </c>
       <c r="B72" t="n">
-        <v>101392</v>
+        <v>101394</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>135849900</v>
       </c>
       <c r="B73" t="n">
-        <v>101392</v>
+        <v>101394</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>135849901</v>
       </c>
       <c r="B74" t="n">
-        <v>101392</v>
+        <v>101394</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>135849902</v>
       </c>
       <c r="B75" t="n">
-        <v>101392</v>
+        <v>101394</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>135849903</v>
       </c>
       <c r="B76" t="n">
-        <v>101392</v>
+        <v>101394</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 28050-2026 artfynd.xlsx
+++ b/artfynd/A 28050-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ76"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1464,7 +1464,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135850014</v>
+        <v>135850018</v>
       </c>
       <c r="B9" t="n">
         <v>79444</v>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500484</v>
+        <v>500425</v>
       </c>
       <c r="R9" t="n">
-        <v>7003356</v>
+        <v>7003323</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,6 +1540,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1552,7 +1557,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1584,54 +1589,63 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850014</t>
+          <t>https://artportalen.se/Sighting/135850018</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135850015</v>
+        <v>135849842</v>
       </c>
       <c r="B10" t="n">
-        <v>79444</v>
+        <v>57982</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500586</v>
+        <v>500404</v>
       </c>
       <c r="R10" t="n">
-        <v>7003162</v>
+        <v>7003270</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1682,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i granskog.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran med spår av rikligt med kådaflöde.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1677,13 +1691,12 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1698,12 +1711,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1720,43 +1733,48 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850015</t>
+          <t>https://artportalen.se/Sighting/135849842</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135850016</v>
+        <v>135849843</v>
       </c>
       <c r="B11" t="n">
-        <v>79444</v>
+        <v>57982</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1764,10 +1782,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500552</v>
+        <v>500404</v>
       </c>
       <c r="R11" t="n">
-        <v>7003131</v>
+        <v>7003271</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,19 +1820,23 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1827,9 +1849,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1846,54 +1873,63 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850016</t>
+          <t>https://artportalen.se/Sighting/135849843</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135850017</v>
+        <v>135849844</v>
       </c>
       <c r="B12" t="n">
-        <v>79444</v>
+        <v>57982</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500505</v>
+        <v>500403</v>
       </c>
       <c r="R12" t="n">
-        <v>7003184</v>
+        <v>7003276</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1930,7 +1966,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran i granskog.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1939,13 +1975,12 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -1958,9 +1993,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1977,54 +2017,63 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850017</t>
+          <t>https://artportalen.se/Sighting/135849844</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135850018</v>
+        <v>135849845</v>
       </c>
       <c r="B13" t="n">
-        <v>79444</v>
+        <v>57982</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500425</v>
+        <v>500377</v>
       </c>
       <c r="R13" t="n">
-        <v>7003323</v>
+        <v>7003317</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2061,7 +2110,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2070,7 +2119,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2089,9 +2137,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2108,63 +2161,67 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850018</t>
+          <t>https://artportalen.se/Sighting/135849845</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135849842</v>
+        <v>135849841</v>
       </c>
       <c r="B14" t="n">
-        <v>57982</v>
+        <v>99318</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>219847</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500404</v>
+        <v>500424</v>
       </c>
       <c r="R14" t="n">
-        <v>7003270</v>
+        <v>7003277</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2201,7 +2258,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran med spår av rikligt med kådaflöde.</t>
+          <t>Minst 3 plantor som växer i ett örtrikt fältskikt på fuktig mark.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2210,32 +2267,13 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2252,48 +2290,48 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849842</t>
+          <t>https://artportalen.se/Sighting/135849841</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135849843</v>
+        <v>135849936</v>
       </c>
       <c r="B15" t="n">
-        <v>57982</v>
+        <v>99632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2301,10 +2339,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500404</v>
+        <v>500459</v>
       </c>
       <c r="R15" t="n">
-        <v>7003271</v>
+        <v>7003232</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2339,43 +2377,19 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2392,63 +2406,59 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849843</t>
+          <t>https://artportalen.se/Sighting/135849936</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135849844</v>
+        <v>135849937</v>
       </c>
       <c r="B16" t="n">
-        <v>57982</v>
+        <v>99632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>219880</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500403</v>
+        <v>500481</v>
       </c>
       <c r="R16" t="n">
-        <v>7003276</v>
+        <v>7003274</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2483,43 +2493,19 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2536,63 +2522,59 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849844</t>
+          <t>https://artportalen.se/Sighting/135849937</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135849845</v>
+        <v>135849917</v>
       </c>
       <c r="B17" t="n">
-        <v>57982</v>
+        <v>108389</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220102</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500377</v>
+        <v>500456</v>
       </c>
       <c r="R17" t="n">
-        <v>7003317</v>
+        <v>7003316</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2627,43 +2609,19 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2680,16 +2638,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849845</t>
+          <t>https://artportalen.se/Sighting/135849917</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135850027</v>
+        <v>135849918</v>
       </c>
       <c r="B18" t="n">
-        <v>99211</v>
+        <v>108389</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2697,21 +2655,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>220102</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2729,10 +2687,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500425</v>
+        <v>500488</v>
       </c>
       <c r="R18" t="n">
-        <v>7003277</v>
+        <v>7003344</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2767,11 +2725,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Växer här i ett stort örtrikt fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2784,7 +2737,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2801,16 +2754,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850027</t>
+          <t>https://artportalen.se/Sighting/135849918</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135850012</v>
+        <v>135849919</v>
       </c>
       <c r="B19" t="n">
-        <v>99193</v>
+        <v>108389</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2818,36 +2771,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219795</v>
+        <v>220102</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -2858,10 +2803,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500521</v>
+        <v>500511</v>
       </c>
       <c r="R19" t="n">
-        <v>7003130</v>
+        <v>7003325</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2925,16 +2870,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850012</t>
+          <t>https://artportalen.se/Sighting/135849919</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135850029</v>
+        <v>135849920</v>
       </c>
       <c r="B20" t="n">
-        <v>99296</v>
+        <v>108389</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2942,33 +2887,25 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219811</v>
+        <v>220102</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -2982,10 +2919,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500389</v>
+        <v>500416</v>
       </c>
       <c r="R20" t="n">
-        <v>7003289</v>
+        <v>7003258</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3032,7 +2969,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3049,16 +2986,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850029</t>
+          <t>https://artportalen.se/Sighting/135849920</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135849834</v>
+        <v>135849921</v>
       </c>
       <c r="B21" t="n">
-        <v>99318</v>
+        <v>108389</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3066,28 +3003,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219847</v>
+        <v>220102</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -3098,10 +3035,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500475</v>
+        <v>500474</v>
       </c>
       <c r="R21" t="n">
-        <v>7003332</v>
+        <v>7003267</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3165,16 +3102,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849834</t>
+          <t>https://artportalen.se/Sighting/135849921</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135849835</v>
+        <v>135849922</v>
       </c>
       <c r="B22" t="n">
-        <v>99318</v>
+        <v>108389</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3182,28 +3119,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219847</v>
+        <v>220102</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -3214,10 +3151,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>500456</v>
+        <v>500448</v>
       </c>
       <c r="R22" t="n">
-        <v>7003229</v>
+        <v>7003286</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3264,7 +3201,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3281,16 +3218,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849835</t>
+          <t>https://artportalen.se/Sighting/135849922</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135849836</v>
+        <v>135849923</v>
       </c>
       <c r="B23" t="n">
-        <v>99318</v>
+        <v>108389</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3298,21 +3235,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>220102</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3330,10 +3267,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500435</v>
+        <v>500415</v>
       </c>
       <c r="R23" t="n">
-        <v>7003231</v>
+        <v>7003291</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3397,16 +3334,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849836</t>
+          <t>https://artportalen.se/Sighting/135849923</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135849837</v>
+        <v>135849909</v>
       </c>
       <c r="B24" t="n">
-        <v>99318</v>
+        <v>111269</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3414,28 +3351,28 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219847</v>
+        <v>220240</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -3446,10 +3383,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>500408</v>
+        <v>500546</v>
       </c>
       <c r="R24" t="n">
-        <v>7003263</v>
+        <v>7003124</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3496,7 +3433,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3513,16 +3450,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849837</t>
+          <t>https://artportalen.se/Sighting/135849909</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135849838</v>
+        <v>135849910</v>
       </c>
       <c r="B25" t="n">
-        <v>99318</v>
+        <v>111269</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3530,28 +3467,28 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219847</v>
+        <v>220240</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -3562,10 +3499,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500394</v>
+        <v>500461</v>
       </c>
       <c r="R25" t="n">
-        <v>7003275</v>
+        <v>7003351</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3629,42 +3566,50 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849838</t>
+          <t>https://artportalen.se/Sighting/135849910</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135849839</v>
+        <v>135849975</v>
       </c>
       <c r="B26" t="n">
-        <v>99318</v>
+        <v>99294</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -3678,10 +3623,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>500397</v>
+        <v>500529</v>
       </c>
       <c r="R26" t="n">
-        <v>7003280</v>
+        <v>7003306</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3716,6 +3661,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minst 30 plantor och 7 överblommade blomställningar inom ca 3 m2 yta i granskog.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3728,12 +3678,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Örtrik barrskog på stor del fuktig mark.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3750,59 +3695,71 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849839</t>
+          <t>https://artportalen.se/Sighting/135849975</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135849840</v>
+        <v>135849976</v>
       </c>
       <c r="B27" t="n">
-        <v>99318</v>
+        <v>99294</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>500478</v>
+        <v>500652</v>
       </c>
       <c r="R27" t="n">
-        <v>7003263</v>
+        <v>7003184</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3837,6 +3794,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Minst 120 plantor varav 30 med överblommade blomställningar inom ca 8 m2 yta i granskog.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3849,7 +3811,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3866,43 +3828,43 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849840</t>
+          <t>https://artportalen.se/Sighting/135849976</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135849841</v>
+        <v>135849977</v>
       </c>
       <c r="B28" t="n">
-        <v>99318</v>
+        <v>99294</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3916,17 +3878,21 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>500424</v>
+        <v>500570</v>
       </c>
       <c r="R28" t="n">
-        <v>7003277</v>
+        <v>7003141</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3963,7 +3929,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Minst 3 plantor som växer i ett örtrikt fältskikt på fuktig mark.</t>
+          <t>Minst 70 plantor och 13 överblommade blomställningar inom ca 1,5 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3978,7 +3944,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3995,59 +3961,71 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849841</t>
+          <t>https://artportalen.se/Sighting/135849977</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135849936</v>
+        <v>135849978</v>
       </c>
       <c r="B29" t="n">
-        <v>99632</v>
+        <v>99294</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500459</v>
+        <v>500507</v>
       </c>
       <c r="R29" t="n">
-        <v>7003232</v>
+        <v>7003191</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4082,6 +4060,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minst 30 plantor och 15 överblommade blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4094,7 +4077,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4111,59 +4094,71 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849936</t>
+          <t>https://artportalen.se/Sighting/135849978</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135849937</v>
+        <v>135849979</v>
       </c>
       <c r="B30" t="n">
-        <v>99632</v>
+        <v>99294</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219880</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>500481</v>
+        <v>500400</v>
       </c>
       <c r="R30" t="n">
-        <v>7003274</v>
+        <v>7003285</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4198,6 +4193,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 120 plantor och 20 mestadels överblommade blomställningar inom ca 2 m2 yta på ett moss- och granöverväxt block.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4227,16 +4227,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849937</t>
+          <t>https://artportalen.se/Sighting/135849979</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135850030</v>
+        <v>135849862</v>
       </c>
       <c r="B31" t="n">
-        <v>108319</v>
+        <v>110039</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4244,28 +4244,28 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220083</v>
+        <v>221184</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -4276,10 +4276,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500467</v>
+        <v>500497</v>
       </c>
       <c r="R31" t="n">
-        <v>7003353</v>
+        <v>7003367</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4343,16 +4343,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850030</t>
+          <t>https://artportalen.se/Sighting/135849862</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135850031</v>
+        <v>135849863</v>
       </c>
       <c r="B32" t="n">
-        <v>108319</v>
+        <v>110039</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4360,21 +4360,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220083</v>
+        <v>221184</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500476</v>
+        <v>500524</v>
       </c>
       <c r="R32" t="n">
-        <v>7003332</v>
+        <v>7003318</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4442,12 +4442,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Örtrik barrskog på kalkrik fuktig mark.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4464,16 +4459,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850031</t>
+          <t>https://artportalen.se/Sighting/135849863</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135850032</v>
+        <v>135849864</v>
       </c>
       <c r="B33" t="n">
-        <v>108319</v>
+        <v>110039</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4481,21 +4476,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220083</v>
+        <v>221184</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4513,10 +4508,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500513</v>
+        <v>500480</v>
       </c>
       <c r="R33" t="n">
-        <v>7003327</v>
+        <v>7003262</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4580,16 +4575,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850032</t>
+          <t>https://artportalen.se/Sighting/135849864</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135850033</v>
+        <v>135849915</v>
       </c>
       <c r="B34" t="n">
-        <v>108319</v>
+        <v>99571</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4597,28 +4592,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220083</v>
+        <v>222812</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -4629,7 +4624,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>500572</v>
+        <v>500491</v>
       </c>
       <c r="R34" t="n">
         <v>7003234</v>
@@ -4696,16 +4691,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850033</t>
+          <t>https://artportalen.se/Sighting/135849915</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135850034</v>
+        <v>135849996</v>
       </c>
       <c r="B35" t="n">
-        <v>108319</v>
+        <v>98345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4713,21 +4708,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220083</v>
+        <v>223358</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4745,10 +4740,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>500399</v>
+        <v>500520</v>
       </c>
       <c r="R35" t="n">
-        <v>7003277</v>
+        <v>7003324</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4795,7 +4790,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4812,16 +4807,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850034</t>
+          <t>https://artportalen.se/Sighting/135849996</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135850035</v>
+        <v>135849997</v>
       </c>
       <c r="B36" t="n">
-        <v>108319</v>
+        <v>98345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4829,28 +4824,28 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220083</v>
+        <v>223358</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -4861,10 +4856,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>500389</v>
+        <v>500533</v>
       </c>
       <c r="R36" t="n">
-        <v>7003293</v>
+        <v>7003286</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4911,12 +4906,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Örtrik barrskog på fuktig mark.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4933,16 +4923,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850035</t>
+          <t>https://artportalen.se/Sighting/135849997</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135849917</v>
+        <v>135849998</v>
       </c>
       <c r="B37" t="n">
-        <v>108389</v>
+        <v>98345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4950,28 +4940,28 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220102</v>
+        <v>223358</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -4982,10 +4972,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>500456</v>
+        <v>500474</v>
       </c>
       <c r="R37" t="n">
-        <v>7003316</v>
+        <v>7003265</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5032,7 +5022,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5049,16 +5039,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849917</t>
+          <t>https://artportalen.se/Sighting/135849998</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135849918</v>
+        <v>135849893</v>
       </c>
       <c r="B38" t="n">
-        <v>108389</v>
+        <v>101394</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5066,28 +5056,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220102</v>
+        <v>224885</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5098,10 +5088,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>500488</v>
+        <v>500510</v>
       </c>
       <c r="R38" t="n">
-        <v>7003344</v>
+        <v>7003353</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5165,16 +5155,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849918</t>
+          <t>https://artportalen.se/Sighting/135849893</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135849919</v>
+        <v>135849894</v>
       </c>
       <c r="B39" t="n">
-        <v>108389</v>
+        <v>101394</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5182,21 +5172,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220102</v>
+        <v>224885</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5214,10 +5204,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>500511</v>
+        <v>500470</v>
       </c>
       <c r="R39" t="n">
-        <v>7003325</v>
+        <v>7003356</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5264,7 +5254,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5281,16 +5271,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849919</t>
+          <t>https://artportalen.se/Sighting/135849894</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135849920</v>
+        <v>135849895</v>
       </c>
       <c r="B40" t="n">
-        <v>108389</v>
+        <v>101394</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5298,28 +5288,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220102</v>
+        <v>224885</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -5330,10 +5320,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>500416</v>
+        <v>500496</v>
       </c>
       <c r="R40" t="n">
-        <v>7003258</v>
+        <v>7003339</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5397,16 +5387,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849920</t>
+          <t>https://artportalen.se/Sighting/135849895</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135849921</v>
+        <v>135849896</v>
       </c>
       <c r="B41" t="n">
-        <v>108389</v>
+        <v>101394</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5414,28 +5404,28 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220102</v>
+        <v>224885</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -5446,10 +5436,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>500474</v>
+        <v>500524</v>
       </c>
       <c r="R41" t="n">
-        <v>7003267</v>
+        <v>7003325</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5496,7 +5486,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5513,16 +5503,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849921</t>
+          <t>https://artportalen.se/Sighting/135849896</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135849922</v>
+        <v>135849897</v>
       </c>
       <c r="B42" t="n">
-        <v>108389</v>
+        <v>101394</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5530,28 +5520,28 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220102</v>
+        <v>224885</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -5562,10 +5552,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>500448</v>
+        <v>500461</v>
       </c>
       <c r="R42" t="n">
-        <v>7003286</v>
+        <v>7003234</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5612,7 +5602,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5629,16 +5619,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849922</t>
+          <t>https://artportalen.se/Sighting/135849897</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135849923</v>
+        <v>135849898</v>
       </c>
       <c r="B43" t="n">
-        <v>108389</v>
+        <v>101394</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5646,28 +5636,28 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220102</v>
+        <v>224885</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -5678,10 +5668,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>500415</v>
+        <v>500438</v>
       </c>
       <c r="R43" t="n">
-        <v>7003291</v>
+        <v>7003234</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5745,16 +5735,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849923</t>
+          <t>https://artportalen.se/Sighting/135849898</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135849909</v>
+        <v>135849899</v>
       </c>
       <c r="B44" t="n">
-        <v>111269</v>
+        <v>101394</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5762,21 +5752,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220240</v>
+        <v>224885</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5794,10 +5784,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>500546</v>
+        <v>500480</v>
       </c>
       <c r="R44" t="n">
-        <v>7003124</v>
+        <v>7003325</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5844,7 +5834,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5861,16 +5851,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849909</t>
+          <t>https://artportalen.se/Sighting/135849899</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135849910</v>
+        <v>135849900</v>
       </c>
       <c r="B45" t="n">
-        <v>111269</v>
+        <v>101394</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5878,21 +5868,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220240</v>
+        <v>224885</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5910,10 +5900,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>500461</v>
+        <v>500469</v>
       </c>
       <c r="R45" t="n">
-        <v>7003351</v>
+        <v>7003260</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5977,53 +5967,45 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849910</t>
+          <t>https://artportalen.se/Sighting/135849900</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135849974</v>
+        <v>135849901</v>
       </c>
       <c r="B46" t="n">
-        <v>99294</v>
+        <v>101394</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>224885</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -6034,10 +6016,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>500511</v>
+        <v>500470</v>
       </c>
       <c r="R46" t="n">
-        <v>7003332</v>
+        <v>7003268</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6072,11 +6054,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor och 10 överblommade blomställningar inom ca 2 x 2 m2 yta i granskog.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6106,53 +6083,45 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849974</t>
+          <t>https://artportalen.se/Sighting/135849901</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135849975</v>
+        <v>135849902</v>
       </c>
       <c r="B47" t="n">
-        <v>99294</v>
+        <v>101394</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>224885</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -6163,10 +6132,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>500529</v>
+        <v>500443</v>
       </c>
       <c r="R47" t="n">
-        <v>7003306</v>
+        <v>7003286</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6201,11 +6170,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Minst 30 plantor och 7 överblommade blomställningar inom ca 3 m2 yta i granskog.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6218,7 +6182,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6235,3444 +6199,7 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849975</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>135849976</v>
-      </c>
-      <c r="B48" t="n">
-        <v>99294</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>500652</v>
-      </c>
-      <c r="R48" t="n">
-        <v>7003184</v>
-      </c>
-      <c r="S48" t="n">
-        <v>10</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst 120 plantor varav 30 med överblommade blomställningar inom ca 8 m2 yta i granskog.</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="inlineStr"/>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849976</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>135849977</v>
-      </c>
-      <c r="B49" t="n">
-        <v>99294</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>500570</v>
-      </c>
-      <c r="R49" t="n">
-        <v>7003141</v>
-      </c>
-      <c r="S49" t="n">
-        <v>10</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Minst 70 plantor och 13 överblommade blomställningar inom ca 1,5 m2 yta i granskog.</t>
-        </is>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF49" t="inlineStr"/>
-      <c r="AG49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849977</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>135849978</v>
-      </c>
-      <c r="B50" t="n">
-        <v>99294</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>500507</v>
-      </c>
-      <c r="R50" t="n">
-        <v>7003191</v>
-      </c>
-      <c r="S50" t="n">
-        <v>10</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Minst 30 plantor och 15 överblommade blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
-        </is>
-      </c>
-      <c r="AD50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="inlineStr"/>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849978</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>135849979</v>
-      </c>
-      <c r="B51" t="n">
-        <v>99294</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>500400</v>
-      </c>
-      <c r="R51" t="n">
-        <v>7003285</v>
-      </c>
-      <c r="S51" t="n">
-        <v>10</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Minst 120 plantor och 20 mestadels överblommade blomställningar inom ca 2 m2 yta på ett moss- och granöverväxt block.</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="inlineStr"/>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849979</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>135849862</v>
-      </c>
-      <c r="B52" t="n">
-        <v>110039</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>221184</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Torta</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Lactuca alpina</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>500497</v>
-      </c>
-      <c r="R52" t="n">
-        <v>7003367</v>
-      </c>
-      <c r="S52" t="n">
-        <v>10</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF52" t="inlineStr"/>
-      <c r="AG52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849862</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>135849863</v>
-      </c>
-      <c r="B53" t="n">
-        <v>110039</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>221184</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Torta</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Lactuca alpina</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q53" t="n">
-        <v>500524</v>
-      </c>
-      <c r="R53" t="n">
-        <v>7003318</v>
-      </c>
-      <c r="S53" t="n">
-        <v>10</v>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="inlineStr"/>
-      <c r="AG53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AW53" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849863</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>135849864</v>
-      </c>
-      <c r="B54" t="n">
-        <v>110039</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>221184</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Torta</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Lactuca alpina</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>500480</v>
-      </c>
-      <c r="R54" t="n">
-        <v>7003262</v>
-      </c>
-      <c r="S54" t="n">
-        <v>10</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF54" t="inlineStr"/>
-      <c r="AG54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849864</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>135849876</v>
-      </c>
-      <c r="B55" t="n">
-        <v>99316</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>500545</v>
-      </c>
-      <c r="R55" t="n">
-        <v>7003269</v>
-      </c>
-      <c r="S55" t="n">
-        <v>10</v>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF55" t="inlineStr"/>
-      <c r="AG55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849876</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>135850039</v>
-      </c>
-      <c r="B56" t="n">
-        <v>101504</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>500509</v>
-      </c>
-      <c r="R56" t="n">
-        <v>7003354</v>
-      </c>
-      <c r="S56" t="n">
-        <v>10</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF56" t="inlineStr"/>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850039</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>135850040</v>
-      </c>
-      <c r="B57" t="n">
-        <v>101504</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>500494</v>
-      </c>
-      <c r="R57" t="n">
-        <v>7003341</v>
-      </c>
-      <c r="S57" t="n">
-        <v>10</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF57" t="inlineStr"/>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850040</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>135850042</v>
-      </c>
-      <c r="B58" t="n">
-        <v>101504</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>500509</v>
-      </c>
-      <c r="R58" t="n">
-        <v>7003330</v>
-      </c>
-      <c r="S58" t="n">
-        <v>10</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF58" t="inlineStr"/>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
-      </c>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850042</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>135850043</v>
-      </c>
-      <c r="B59" t="n">
-        <v>101504</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>500523</v>
-      </c>
-      <c r="R59" t="n">
-        <v>7003129</v>
-      </c>
-      <c r="S59" t="n">
-        <v>10</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF59" t="inlineStr"/>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850043</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>135850044</v>
-      </c>
-      <c r="B60" t="n">
-        <v>101504</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q60" t="n">
-        <v>500450</v>
-      </c>
-      <c r="R60" t="n">
-        <v>7003243</v>
-      </c>
-      <c r="S60" t="n">
-        <v>10</v>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF60" t="inlineStr"/>
-      <c r="AG60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135850044</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>135849915</v>
-      </c>
-      <c r="B61" t="n">
-        <v>99571</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>222812</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Liljekonvalj</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Convallaria majalis</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q61" t="n">
-        <v>500491</v>
-      </c>
-      <c r="R61" t="n">
-        <v>7003234</v>
-      </c>
-      <c r="S61" t="n">
-        <v>10</v>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF61" t="inlineStr"/>
-      <c r="AG61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849915</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>135849889</v>
-      </c>
-      <c r="B62" t="n">
-        <v>99100</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>223049</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Ormbär</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Paris quadrifolia</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q62" t="n">
-        <v>500512</v>
-      </c>
-      <c r="R62" t="n">
-        <v>7003140</v>
-      </c>
-      <c r="S62" t="n">
-        <v>10</v>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF62" t="inlineStr"/>
-      <c r="AG62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849889</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>135849996</v>
-      </c>
-      <c r="B63" t="n">
-        <v>98345</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>500520</v>
-      </c>
-      <c r="R63" t="n">
-        <v>7003324</v>
-      </c>
-      <c r="S63" t="n">
-        <v>10</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF63" t="inlineStr"/>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849996</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>135849997</v>
-      </c>
-      <c r="B64" t="n">
-        <v>98345</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>500533</v>
-      </c>
-      <c r="R64" t="n">
-        <v>7003286</v>
-      </c>
-      <c r="S64" t="n">
-        <v>10</v>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF64" t="inlineStr"/>
-      <c r="AG64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849997</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>135849998</v>
-      </c>
-      <c r="B65" t="n">
-        <v>98345</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>223358</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Hultbräken</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Phegopteris connectilis</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>500474</v>
-      </c>
-      <c r="R65" t="n">
-        <v>7003265</v>
-      </c>
-      <c r="S65" t="n">
-        <v>10</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF65" t="inlineStr"/>
-      <c r="AG65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT65" t="inlineStr"/>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849998</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>135849893</v>
-      </c>
-      <c r="B66" t="n">
-        <v>101394</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>500510</v>
-      </c>
-      <c r="R66" t="n">
-        <v>7003353</v>
-      </c>
-      <c r="S66" t="n">
-        <v>10</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF66" t="inlineStr"/>
-      <c r="AG66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Högörtbarrskog</t>
-        </is>
-      </c>
-      <c r="AT66" t="inlineStr"/>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849893</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>135849894</v>
-      </c>
-      <c r="B67" t="n">
-        <v>101394</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q67" t="n">
-        <v>500470</v>
-      </c>
-      <c r="R67" t="n">
-        <v>7003356</v>
-      </c>
-      <c r="S67" t="n">
-        <v>10</v>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF67" t="inlineStr"/>
-      <c r="AG67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Högörtbarrskog</t>
-        </is>
-      </c>
-      <c r="AT67" t="inlineStr"/>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849894</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>135849895</v>
-      </c>
-      <c r="B68" t="n">
-        <v>101394</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q68" t="n">
-        <v>500496</v>
-      </c>
-      <c r="R68" t="n">
-        <v>7003339</v>
-      </c>
-      <c r="S68" t="n">
-        <v>10</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF68" t="inlineStr"/>
-      <c r="AG68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Högörtbarrskog</t>
-        </is>
-      </c>
-      <c r="AT68" t="inlineStr"/>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849895</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>135849896</v>
-      </c>
-      <c r="B69" t="n">
-        <v>101394</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>500524</v>
-      </c>
-      <c r="R69" t="n">
-        <v>7003325</v>
-      </c>
-      <c r="S69" t="n">
-        <v>10</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF69" t="inlineStr"/>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849896</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>135849897</v>
-      </c>
-      <c r="B70" t="n">
-        <v>101394</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>500461</v>
-      </c>
-      <c r="R70" t="n">
-        <v>7003234</v>
-      </c>
-      <c r="S70" t="n">
-        <v>10</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF70" t="inlineStr"/>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849897</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>135849898</v>
-      </c>
-      <c r="B71" t="n">
-        <v>101394</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>500438</v>
-      </c>
-      <c r="R71" t="n">
-        <v>7003234</v>
-      </c>
-      <c r="S71" t="n">
-        <v>10</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF71" t="inlineStr"/>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849898</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>135849899</v>
-      </c>
-      <c r="B72" t="n">
-        <v>101394</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>500480</v>
-      </c>
-      <c r="R72" t="n">
-        <v>7003325</v>
-      </c>
-      <c r="S72" t="n">
-        <v>10</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF72" t="inlineStr"/>
-      <c r="AG72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT72" t="inlineStr"/>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849899</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>135849900</v>
-      </c>
-      <c r="B73" t="n">
-        <v>101394</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>500469</v>
-      </c>
-      <c r="R73" t="n">
-        <v>7003260</v>
-      </c>
-      <c r="S73" t="n">
-        <v>10</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF73" t="inlineStr"/>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849900</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>135849901</v>
-      </c>
-      <c r="B74" t="n">
-        <v>101394</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>500470</v>
-      </c>
-      <c r="R74" t="n">
-        <v>7003268</v>
-      </c>
-      <c r="S74" t="n">
-        <v>10</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF74" t="inlineStr"/>
-      <c r="AG74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT74" t="inlineStr"/>
-      <c r="AW74" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849901</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>135849902</v>
-      </c>
-      <c r="B75" t="n">
-        <v>101394</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q75" t="n">
-        <v>500443</v>
-      </c>
-      <c r="R75" t="n">
-        <v>7003286</v>
-      </c>
-      <c r="S75" t="n">
-        <v>10</v>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF75" t="inlineStr"/>
-      <c r="AG75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT75" t="inlineStr"/>
-      <c r="AW75" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
-      <c r="AZ75" t="inlineStr">
-        <is>
           <t>https://artportalen.se/Sighting/135849902</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>135849903</v>
-      </c>
-      <c r="B76" t="n">
-        <v>101394</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Lundkälen NV, Jmt</t>
-        </is>
-      </c>
-      <c r="Q76" t="n">
-        <v>500429</v>
-      </c>
-      <c r="R76" t="n">
-        <v>7003294</v>
-      </c>
-      <c r="S76" t="n">
-        <v>10</v>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>Kyrkås</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AD76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF76" t="inlineStr"/>
-      <c r="AG76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT76" t="inlineStr"/>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135849903</t>
         </is>
       </c>
     </row>
@@ -9724,35 +6251,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28050-2026 artfynd.xlsx
+++ b/artfynd/A 28050-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ47"/>
+  <dimension ref="A1:AZ76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>135849953</v>
       </c>
       <c r="B2" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135849954</v>
       </c>
       <c r="B3" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135849955</v>
       </c>
       <c r="B4" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135849956</v>
       </c>
       <c r="B5" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135849957</v>
       </c>
       <c r="B6" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135849958</v>
       </c>
       <c r="B7" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135849959</v>
       </c>
       <c r="B8" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135850018</v>
+        <v>135850014</v>
       </c>
       <c r="B9" t="n">
         <v>79444</v>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>500425</v>
+        <v>500484</v>
       </c>
       <c r="R9" t="n">
-        <v>7003323</v>
+        <v>7003356</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1540,11 +1540,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1557,7 +1552,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1589,63 +1584,54 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135850018</t>
+          <t>https://artportalen.se/Sighting/135850014</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135849842</v>
+        <v>135850015</v>
       </c>
       <c r="B10" t="n">
-        <v>57982</v>
+        <v>79444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>500404</v>
+        <v>500586</v>
       </c>
       <c r="R10" t="n">
-        <v>7003270</v>
+        <v>7003162</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1682,7 +1668,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran med spår av rikligt med kådaflöde.</t>
+          <t>Långväxta bålar på gran i granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,12 +1677,13 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1711,12 +1698,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1733,48 +1720,43 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849842</t>
+          <t>https://artportalen.se/Sighting/135850015</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135849843</v>
+        <v>135850016</v>
       </c>
       <c r="B11" t="n">
-        <v>57982</v>
+        <v>79444</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1782,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>500404</v>
+        <v>500552</v>
       </c>
       <c r="R11" t="n">
-        <v>7003271</v>
+        <v>7003131</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1820,23 +1802,19 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1849,14 +1827,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1873,63 +1846,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849843</t>
+          <t>https://artportalen.se/Sighting/135850016</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135849844</v>
+        <v>135850017</v>
       </c>
       <c r="B12" t="n">
-        <v>57982</v>
+        <v>79444</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>500403</v>
+        <v>500505</v>
       </c>
       <c r="R12" t="n">
-        <v>7003276</v>
+        <v>7003184</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1966,7 +1930,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Långväxta bålar på gran i granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1975,12 +1939,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -1993,14 +1958,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2017,63 +1977,54 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849844</t>
+          <t>https://artportalen.se/Sighting/135850017</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135849845</v>
+        <v>135850018</v>
       </c>
       <c r="B13" t="n">
-        <v>57982</v>
+        <v>79444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>500377</v>
+        <v>500425</v>
       </c>
       <c r="R13" t="n">
-        <v>7003317</v>
+        <v>7003323</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2110,7 +2061,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2119,6 +2070,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2137,14 +2089,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2161,67 +2108,63 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849845</t>
+          <t>https://artportalen.se/Sighting/135850018</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135849841</v>
+        <v>135849842</v>
       </c>
       <c r="B14" t="n">
-        <v>99318</v>
+        <v>57982</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>500424</v>
+        <v>500404</v>
       </c>
       <c r="R14" t="n">
-        <v>7003277</v>
+        <v>7003270</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2258,7 +2201,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Minst 3 plantor som växer i ett örtrikt fältskikt på fuktig mark.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran med spår av rikligt med kådaflöde.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2267,13 +2210,32 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2290,48 +2252,48 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849841</t>
+          <t>https://artportalen.se/Sighting/135849842</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135849936</v>
+        <v>135849843</v>
       </c>
       <c r="B15" t="n">
-        <v>99632</v>
+        <v>57982</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2339,10 +2301,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>500459</v>
+        <v>500404</v>
       </c>
       <c r="R15" t="n">
-        <v>7003232</v>
+        <v>7003271</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2377,19 +2339,43 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2406,59 +2392,63 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849936</t>
+          <t>https://artportalen.se/Sighting/135849843</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135849937</v>
+        <v>135849844</v>
       </c>
       <c r="B16" t="n">
-        <v>99632</v>
+        <v>57982</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219880</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>500481</v>
+        <v>500403</v>
       </c>
       <c r="R16" t="n">
-        <v>7003274</v>
+        <v>7003276</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2493,19 +2483,43 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2522,59 +2536,63 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849937</t>
+          <t>https://artportalen.se/Sighting/135849844</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135849917</v>
+        <v>135849845</v>
       </c>
       <c r="B17" t="n">
-        <v>108389</v>
+        <v>57982</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220102</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>500456</v>
+        <v>500377</v>
       </c>
       <c r="R17" t="n">
-        <v>7003316</v>
+        <v>7003317</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2609,19 +2627,43 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2638,16 +2680,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849917</t>
+          <t>https://artportalen.se/Sighting/135849845</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135849918</v>
+        <v>135850027</v>
       </c>
       <c r="B18" t="n">
-        <v>108389</v>
+        <v>99212</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2655,21 +2697,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220102</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2687,10 +2729,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>500488</v>
+        <v>500425</v>
       </c>
       <c r="R18" t="n">
-        <v>7003344</v>
+        <v>7003277</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2725,6 +2767,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Växer här i ett stort örtrikt fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2737,7 +2784,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2754,16 +2801,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849918</t>
+          <t>https://artportalen.se/Sighting/135850027</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135849919</v>
+        <v>135850012</v>
       </c>
       <c r="B19" t="n">
-        <v>108389</v>
+        <v>99194</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,28 +2818,36 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220102</v>
+        <v>219795</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -2803,10 +2858,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>500511</v>
+        <v>500521</v>
       </c>
       <c r="R19" t="n">
-        <v>7003325</v>
+        <v>7003130</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2870,16 +2925,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849919</t>
+          <t>https://artportalen.se/Sighting/135850012</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135849920</v>
+        <v>135850029</v>
       </c>
       <c r="B20" t="n">
-        <v>108389</v>
+        <v>99297</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,25 +2942,33 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220102</v>
+        <v>219811</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -2919,10 +2982,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>500416</v>
+        <v>500389</v>
       </c>
       <c r="R20" t="n">
-        <v>7003258</v>
+        <v>7003289</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2969,7 +3032,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2986,16 +3049,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849920</t>
+          <t>https://artportalen.se/Sighting/135850029</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135849921</v>
+        <v>135849834</v>
       </c>
       <c r="B21" t="n">
-        <v>108389</v>
+        <v>99319</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3003,28 +3066,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220102</v>
+        <v>219847</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -3035,10 +3098,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>500474</v>
+        <v>500475</v>
       </c>
       <c r="R21" t="n">
-        <v>7003267</v>
+        <v>7003332</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3102,16 +3165,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849921</t>
+          <t>https://artportalen.se/Sighting/135849834</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135849922</v>
+        <v>135849835</v>
       </c>
       <c r="B22" t="n">
-        <v>108389</v>
+        <v>99319</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3119,28 +3182,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220102</v>
+        <v>219847</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -3151,10 +3214,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>500448</v>
+        <v>500456</v>
       </c>
       <c r="R22" t="n">
-        <v>7003286</v>
+        <v>7003229</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3201,7 +3264,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3218,16 +3281,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849922</t>
+          <t>https://artportalen.se/Sighting/135849835</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135849923</v>
+        <v>135849836</v>
       </c>
       <c r="B23" t="n">
-        <v>108389</v>
+        <v>99319</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3235,21 +3298,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220102</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3267,10 +3330,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>500415</v>
+        <v>500435</v>
       </c>
       <c r="R23" t="n">
-        <v>7003291</v>
+        <v>7003231</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3334,16 +3397,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849923</t>
+          <t>https://artportalen.se/Sighting/135849836</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135849909</v>
+        <v>135849837</v>
       </c>
       <c r="B24" t="n">
-        <v>111269</v>
+        <v>99319</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3351,28 +3414,28 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220240</v>
+        <v>219847</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -3383,10 +3446,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>500546</v>
+        <v>500408</v>
       </c>
       <c r="R24" t="n">
-        <v>7003124</v>
+        <v>7003263</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3433,7 +3496,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3450,16 +3513,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849909</t>
+          <t>https://artportalen.se/Sighting/135849837</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135849910</v>
+        <v>135849838</v>
       </c>
       <c r="B25" t="n">
-        <v>111269</v>
+        <v>99319</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3467,28 +3530,28 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220240</v>
+        <v>219847</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -3499,10 +3562,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>500461</v>
+        <v>500394</v>
       </c>
       <c r="R25" t="n">
-        <v>7003351</v>
+        <v>7003275</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3566,50 +3629,42 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849910</t>
+          <t>https://artportalen.se/Sighting/135849838</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135849975</v>
+        <v>135849839</v>
       </c>
       <c r="B26" t="n">
-        <v>99294</v>
+        <v>99319</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -3623,10 +3678,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>500529</v>
+        <v>500397</v>
       </c>
       <c r="R26" t="n">
-        <v>7003306</v>
+        <v>7003280</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3661,11 +3716,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Minst 30 plantor och 7 överblommade blomställningar inom ca 3 m2 yta i granskog.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3678,7 +3728,12 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Örtrik barrskog på stor del fuktig mark.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3695,71 +3750,59 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849975</t>
+          <t>https://artportalen.se/Sighting/135849839</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135849976</v>
+        <v>135849840</v>
       </c>
       <c r="B27" t="n">
-        <v>99294</v>
+        <v>99319</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>överblommad</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>500652</v>
+        <v>500478</v>
       </c>
       <c r="R27" t="n">
-        <v>7003184</v>
+        <v>7003263</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3794,11 +3837,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Minst 120 plantor varav 30 med överblommade blomställningar inom ca 8 m2 yta i granskog.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3811,7 +3849,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3828,43 +3866,43 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849976</t>
+          <t>https://artportalen.se/Sighting/135849840</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135849977</v>
+        <v>135849841</v>
       </c>
       <c r="B28" t="n">
-        <v>99294</v>
+        <v>99319</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3878,21 +3916,17 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>500570</v>
+        <v>500424</v>
       </c>
       <c r="R28" t="n">
-        <v>7003141</v>
+        <v>7003277</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3929,7 +3963,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Minst 70 plantor och 13 överblommade blomställningar inom ca 1,5 m2 yta i granskog.</t>
+          <t>Minst 3 plantor som växer i ett örtrikt fältskikt på fuktig mark.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3944,7 +3978,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3961,71 +3995,59 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849977</t>
+          <t>https://artportalen.se/Sighting/135849841</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135849978</v>
+        <v>135849936</v>
       </c>
       <c r="B29" t="n">
-        <v>99294</v>
+        <v>99633</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>500507</v>
+        <v>500459</v>
       </c>
       <c r="R29" t="n">
-        <v>7003191</v>
+        <v>7003232</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4060,11 +4082,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst 30 plantor och 15 överblommade blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4077,7 +4094,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4094,71 +4111,59 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849978</t>
+          <t>https://artportalen.se/Sighting/135849936</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135849979</v>
+        <v>135849937</v>
       </c>
       <c r="B30" t="n">
-        <v>99294</v>
+        <v>99633</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>219880</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lundkälen NV, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>500400</v>
+        <v>500481</v>
       </c>
       <c r="R30" t="n">
-        <v>7003285</v>
+        <v>7003274</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4193,11 +4198,6 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 120 plantor och 20 mestadels överblommade blomställningar inom ca 2 m2 yta på ett moss- och granöverväxt block.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4227,16 +4227,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849979</t>
+          <t>https://artportalen.se/Sighting/135849937</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135849862</v>
+        <v>135850030</v>
       </c>
       <c r="B31" t="n">
-        <v>110039</v>
+        <v>108320</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4244,28 +4244,28 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221184</v>
+        <v>220083</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -4276,10 +4276,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>500497</v>
+        <v>500467</v>
       </c>
       <c r="R31" t="n">
-        <v>7003367</v>
+        <v>7003353</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4343,16 +4343,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849862</t>
+          <t>https://artportalen.se/Sighting/135850030</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135849863</v>
+        <v>135850031</v>
       </c>
       <c r="B32" t="n">
-        <v>110039</v>
+        <v>108320</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4360,21 +4360,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221184</v>
+        <v>220083</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>500524</v>
+        <v>500476</v>
       </c>
       <c r="R32" t="n">
-        <v>7003318</v>
+        <v>7003332</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4442,7 +4442,12 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Örtrik barrskog på kalkrik fuktig mark.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4459,16 +4464,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849863</t>
+          <t>https://artportalen.se/Sighting/135850031</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135849864</v>
+        <v>135850032</v>
       </c>
       <c r="B33" t="n">
-        <v>110039</v>
+        <v>108320</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4476,21 +4481,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221184</v>
+        <v>220083</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4508,10 +4513,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>500480</v>
+        <v>500513</v>
       </c>
       <c r="R33" t="n">
-        <v>7003262</v>
+        <v>7003327</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4575,16 +4580,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849864</t>
+          <t>https://artportalen.se/Sighting/135850032</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135849915</v>
+        <v>135850033</v>
       </c>
       <c r="B34" t="n">
-        <v>99571</v>
+        <v>108320</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4592,28 +4597,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222812</v>
+        <v>220083</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -4624,7 +4629,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>500491</v>
+        <v>500572</v>
       </c>
       <c r="R34" t="n">
         <v>7003234</v>
@@ -4691,16 +4696,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849915</t>
+          <t>https://artportalen.se/Sighting/135850033</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135849996</v>
+        <v>135850034</v>
       </c>
       <c r="B35" t="n">
-        <v>98345</v>
+        <v>108320</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4708,21 +4713,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>223358</v>
+        <v>220083</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4740,10 +4745,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>500520</v>
+        <v>500399</v>
       </c>
       <c r="R35" t="n">
-        <v>7003324</v>
+        <v>7003277</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4790,7 +4795,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4807,16 +4812,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849996</t>
+          <t>https://artportalen.se/Sighting/135850034</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135849997</v>
+        <v>135850035</v>
       </c>
       <c r="B36" t="n">
-        <v>98345</v>
+        <v>108320</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4824,28 +4829,28 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>223358</v>
+        <v>220083</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -4856,10 +4861,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>500533</v>
+        <v>500389</v>
       </c>
       <c r="R36" t="n">
-        <v>7003286</v>
+        <v>7003293</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4906,7 +4911,12 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Örtrik barrskog på fuktig mark.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4923,16 +4933,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849997</t>
+          <t>https://artportalen.se/Sighting/135850035</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135849998</v>
+        <v>135849917</v>
       </c>
       <c r="B37" t="n">
-        <v>98345</v>
+        <v>108390</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4940,28 +4950,28 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>223358</v>
+        <v>220102</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -4972,10 +4982,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>500474</v>
+        <v>500456</v>
       </c>
       <c r="R37" t="n">
-        <v>7003265</v>
+        <v>7003316</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5022,7 +5032,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5039,16 +5049,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849998</t>
+          <t>https://artportalen.se/Sighting/135849917</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135849893</v>
+        <v>135849918</v>
       </c>
       <c r="B38" t="n">
-        <v>101394</v>
+        <v>108390</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5056,28 +5066,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>224885</v>
+        <v>220102</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5088,10 +5098,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>500510</v>
+        <v>500488</v>
       </c>
       <c r="R38" t="n">
-        <v>7003353</v>
+        <v>7003344</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5155,16 +5165,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849893</t>
+          <t>https://artportalen.se/Sighting/135849918</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135849894</v>
+        <v>135849919</v>
       </c>
       <c r="B39" t="n">
-        <v>101394</v>
+        <v>108390</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5172,21 +5182,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>224885</v>
+        <v>220102</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5204,10 +5214,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>500470</v>
+        <v>500511</v>
       </c>
       <c r="R39" t="n">
-        <v>7003356</v>
+        <v>7003325</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5254,7 +5264,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Högörtbarrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5271,16 +5281,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849894</t>
+          <t>https://artportalen.se/Sighting/135849919</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135849895</v>
+        <v>135849920</v>
       </c>
       <c r="B40" t="n">
-        <v>101394</v>
+        <v>108390</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5288,28 +5298,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>224885</v>
+        <v>220102</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -5320,10 +5330,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>500496</v>
+        <v>500416</v>
       </c>
       <c r="R40" t="n">
-        <v>7003339</v>
+        <v>7003258</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5387,16 +5397,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849895</t>
+          <t>https://artportalen.se/Sighting/135849920</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135849896</v>
+        <v>135849921</v>
       </c>
       <c r="B41" t="n">
-        <v>101394</v>
+        <v>108390</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5404,28 +5414,28 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>224885</v>
+        <v>220102</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -5436,10 +5446,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>500524</v>
+        <v>500474</v>
       </c>
       <c r="R41" t="n">
-        <v>7003325</v>
+        <v>7003267</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5486,7 +5496,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5503,16 +5513,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849896</t>
+          <t>https://artportalen.se/Sighting/135849921</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135849897</v>
+        <v>135849922</v>
       </c>
       <c r="B42" t="n">
-        <v>101394</v>
+        <v>108390</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5520,28 +5530,28 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>224885</v>
+        <v>220102</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -5552,10 +5562,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>500461</v>
+        <v>500448</v>
       </c>
       <c r="R42" t="n">
-        <v>7003234</v>
+        <v>7003286</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5602,7 +5612,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Högörtbarrskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5619,16 +5629,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849897</t>
+          <t>https://artportalen.se/Sighting/135849922</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135849898</v>
+        <v>135849923</v>
       </c>
       <c r="B43" t="n">
-        <v>101394</v>
+        <v>108390</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5636,28 +5646,28 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>224885</v>
+        <v>220102</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -5668,10 +5678,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>500438</v>
+        <v>500415</v>
       </c>
       <c r="R43" t="n">
-        <v>7003234</v>
+        <v>7003291</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5735,16 +5745,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849898</t>
+          <t>https://artportalen.se/Sighting/135849923</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135849899</v>
+        <v>135849909</v>
       </c>
       <c r="B44" t="n">
-        <v>101394</v>
+        <v>111270</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5752,21 +5762,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>224885</v>
+        <v>220240</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5784,10 +5794,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>500480</v>
+        <v>500546</v>
       </c>
       <c r="R44" t="n">
-        <v>7003325</v>
+        <v>7003124</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5834,7 +5844,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5851,16 +5861,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849899</t>
+          <t>https://artportalen.se/Sighting/135849909</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135849900</v>
+        <v>135849910</v>
       </c>
       <c r="B45" t="n">
-        <v>101394</v>
+        <v>111270</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5868,21 +5878,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>224885</v>
+        <v>220240</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5900,10 +5910,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>500469</v>
+        <v>500461</v>
       </c>
       <c r="R45" t="n">
-        <v>7003260</v>
+        <v>7003351</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5967,45 +5977,53 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849900</t>
+          <t>https://artportalen.se/Sighting/135849910</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135849901</v>
+        <v>135849974</v>
       </c>
       <c r="B46" t="n">
-        <v>101394</v>
+        <v>99295</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>224885</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -6016,10 +6034,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>500470</v>
+        <v>500511</v>
       </c>
       <c r="R46" t="n">
-        <v>7003268</v>
+        <v>7003332</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6054,6 +6072,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor och 10 överblommade blomställningar inom ca 2 x 2 m2 yta i granskog.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6083,45 +6106,53 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135849901</t>
+          <t>https://artportalen.se/Sighting/135849974</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135849902</v>
+        <v>135849975</v>
       </c>
       <c r="B47" t="n">
-        <v>101394</v>
+        <v>99295</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>224885</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -6132,10 +6163,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>500443</v>
+        <v>500529</v>
       </c>
       <c r="R47" t="n">
-        <v>7003286</v>
+        <v>7003306</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6170,6 +6201,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Minst 30 plantor och 7 överblommade blomställningar inom ca 3 m2 yta i granskog.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6182,7 +6218,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6199,7 +6235,3444 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135849975</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135849976</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99295</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>500652</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7003184</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Minst 120 plantor varav 30 med överblommade blomställningar inom ca 8 m2 yta i granskog.</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849976</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135849977</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99295</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>500570</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7003141</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst 70 plantor och 13 överblommade blomställningar inom ca 1,5 m2 yta i granskog.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849977</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135849978</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99295</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>500507</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7003191</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Minst 30 plantor och 15 överblommade blomställningar inom ca 2 x 1 m2 yta i granskog.</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849978</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135849979</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99295</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>500400</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7003285</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Minst 120 plantor och 20 mestadels överblommade blomställningar inom ca 2 m2 yta på ett moss- och granöverväxt block.</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849979</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135849862</v>
+      </c>
+      <c r="B52" t="n">
+        <v>110040</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>500497</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7003367</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849862</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135849863</v>
+      </c>
+      <c r="B53" t="n">
+        <v>110040</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>500524</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7003318</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849863</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135849864</v>
+      </c>
+      <c r="B54" t="n">
+        <v>110040</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>500480</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7003262</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849864</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135849876</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99317</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>500545</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7003269</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849876</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135850039</v>
+      </c>
+      <c r="B56" t="n">
+        <v>101505</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>500509</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7003354</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850039</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135850040</v>
+      </c>
+      <c r="B57" t="n">
+        <v>101505</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>500494</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7003341</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850040</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135850042</v>
+      </c>
+      <c r="B58" t="n">
+        <v>101505</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>500509</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7003330</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850042</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135850043</v>
+      </c>
+      <c r="B59" t="n">
+        <v>101505</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>500523</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7003129</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850043</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135850044</v>
+      </c>
+      <c r="B60" t="n">
+        <v>101505</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>500450</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7003243</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135850044</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135849915</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99572</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>500491</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7003234</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849915</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135849889</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99101</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>500512</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7003140</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849889</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135849996</v>
+      </c>
+      <c r="B63" t="n">
+        <v>98346</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>500520</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7003324</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849996</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135849997</v>
+      </c>
+      <c r="B64" t="n">
+        <v>98346</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>500533</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7003286</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849997</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135849998</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98346</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>500474</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7003265</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849998</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135849893</v>
+      </c>
+      <c r="B66" t="n">
+        <v>101395</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>500510</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7003353</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Högörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849893</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135849894</v>
+      </c>
+      <c r="B67" t="n">
+        <v>101395</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>500470</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7003356</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Högörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849894</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>135849895</v>
+      </c>
+      <c r="B68" t="n">
+        <v>101395</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>500496</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7003339</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Högörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849895</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135849896</v>
+      </c>
+      <c r="B69" t="n">
+        <v>101395</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>500524</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7003325</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849896</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135849897</v>
+      </c>
+      <c r="B70" t="n">
+        <v>101395</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>500461</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7003234</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849897</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135849898</v>
+      </c>
+      <c r="B71" t="n">
+        <v>101395</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>500438</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7003234</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849898</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135849899</v>
+      </c>
+      <c r="B72" t="n">
+        <v>101395</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>500480</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7003325</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849899</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135849900</v>
+      </c>
+      <c r="B73" t="n">
+        <v>101395</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>500469</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7003260</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849900</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135849901</v>
+      </c>
+      <c r="B74" t="n">
+        <v>101395</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>500470</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7003268</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849901</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135849902</v>
+      </c>
+      <c r="B75" t="n">
+        <v>101395</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>500443</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7003286</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135849902</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135849903</v>
+      </c>
+      <c r="B76" t="n">
+        <v>101395</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Lundkälen NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>500429</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7003294</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135849903</t>
         </is>
       </c>
     </row>
@@ -6251,6 +9724,35 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28050-2026 artfynd.xlsx
+++ b/artfynd/A 28050-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135849953</v>
       </c>
       <c r="B2" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135849954</v>
       </c>
       <c r="B3" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135849955</v>
       </c>
       <c r="B4" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135849956</v>
       </c>
       <c r="B5" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135849957</v>
       </c>
       <c r="B6" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135849958</v>
       </c>
       <c r="B7" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135849959</v>
       </c>
       <c r="B8" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135850014</v>
       </c>
       <c r="B9" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>135850015</v>
       </c>
       <c r="B10" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>135850016</v>
       </c>
       <c r="B11" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>135850017</v>
       </c>
       <c r="B12" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>135850018</v>
       </c>
       <c r="B13" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>135849842</v>
       </c>
       <c r="B14" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>135849843</v>
       </c>
       <c r="B15" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>135849844</v>
       </c>
       <c r="B16" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>135849845</v>
       </c>
       <c r="B17" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135850027</v>
       </c>
       <c r="B18" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>135850012</v>
       </c>
       <c r="B19" t="n">
-        <v>99194</v>
+        <v>99195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>135850029</v>
       </c>
       <c r="B20" t="n">
-        <v>99297</v>
+        <v>99298</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135849834</v>
       </c>
       <c r="B21" t="n">
-        <v>99319</v>
+        <v>99320</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>135849835</v>
       </c>
       <c r="B22" t="n">
-        <v>99319</v>
+        <v>99320</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>135849836</v>
       </c>
       <c r="B23" t="n">
-        <v>99319</v>
+        <v>99320</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>135849837</v>
       </c>
       <c r="B24" t="n">
-        <v>99319</v>
+        <v>99320</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>135849838</v>
       </c>
       <c r="B25" t="n">
-        <v>99319</v>
+        <v>99320</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>135849839</v>
       </c>
       <c r="B26" t="n">
-        <v>99319</v>
+        <v>99320</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>135849840</v>
       </c>
       <c r="B27" t="n">
-        <v>99319</v>
+        <v>99320</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>135849841</v>
       </c>
       <c r="B28" t="n">
-        <v>99319</v>
+        <v>99320</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>135849936</v>
       </c>
       <c r="B29" t="n">
-        <v>99633</v>
+        <v>99634</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>135849937</v>
       </c>
       <c r="B30" t="n">
-        <v>99633</v>
+        <v>99634</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>135850030</v>
       </c>
       <c r="B31" t="n">
-        <v>108320</v>
+        <v>108321</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>135850031</v>
       </c>
       <c r="B32" t="n">
-        <v>108320</v>
+        <v>108321</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>135850032</v>
       </c>
       <c r="B33" t="n">
-        <v>108320</v>
+        <v>108321</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>135850033</v>
       </c>
       <c r="B34" t="n">
-        <v>108320</v>
+        <v>108321</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>135850034</v>
       </c>
       <c r="B35" t="n">
-        <v>108320</v>
+        <v>108321</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>135850035</v>
       </c>
       <c r="B36" t="n">
-        <v>108320</v>
+        <v>108321</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>135849917</v>
       </c>
       <c r="B37" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>135849918</v>
       </c>
       <c r="B38" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>135849919</v>
       </c>
       <c r="B39" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>135849920</v>
       </c>
       <c r="B40" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>135849921</v>
       </c>
       <c r="B41" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>135849922</v>
       </c>
       <c r="B42" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>135849923</v>
       </c>
       <c r="B43" t="n">
-        <v>108390</v>
+        <v>108391</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>135849909</v>
       </c>
       <c r="B44" t="n">
-        <v>111270</v>
+        <v>111271</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>135849910</v>
       </c>
       <c r="B45" t="n">
-        <v>111270</v>
+        <v>111271</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>135849974</v>
       </c>
       <c r="B46" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>135849975</v>
       </c>
       <c r="B47" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>135849976</v>
       </c>
       <c r="B48" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>135849977</v>
       </c>
       <c r="B49" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>135849978</v>
       </c>
       <c r="B50" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>135849979</v>
       </c>
       <c r="B51" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>135849862</v>
       </c>
       <c r="B52" t="n">
-        <v>110040</v>
+        <v>110041</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>135849863</v>
       </c>
       <c r="B53" t="n">
-        <v>110040</v>
+        <v>110041</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>135849864</v>
       </c>
       <c r="B54" t="n">
-        <v>110040</v>
+        <v>110041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>135849876</v>
       </c>
       <c r="B55" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>135850039</v>
       </c>
       <c r="B56" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>135850040</v>
       </c>
       <c r="B57" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>135850042</v>
       </c>
       <c r="B58" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>135850043</v>
       </c>
       <c r="B59" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>135850044</v>
       </c>
       <c r="B60" t="n">
-        <v>101505</v>
+        <v>101506</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>135849915</v>
       </c>
       <c r="B61" t="n">
-        <v>99572</v>
+        <v>99573</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>135849889</v>
       </c>
       <c r="B62" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>135849996</v>
       </c>
       <c r="B63" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>135849997</v>
       </c>
       <c r="B64" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>135849998</v>
       </c>
       <c r="B65" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>135849893</v>
       </c>
       <c r="B66" t="n">
-        <v>101395</v>
+        <v>101396</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>135849894</v>
       </c>
       <c r="B67" t="n">
-        <v>101395</v>
+        <v>101396</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>135849895</v>
       </c>
       <c r="B68" t="n">
-        <v>101395</v>
+        <v>101396</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>135849896</v>
       </c>
       <c r="B69" t="n">
-        <v>101395</v>
+        <v>101396</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>135849897</v>
       </c>
       <c r="B70" t="n">
-        <v>101395</v>
+        <v>101396</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>135849898</v>
       </c>
       <c r="B71" t="n">
-        <v>101395</v>
+        <v>101396</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>135849899</v>
       </c>
       <c r="B72" t="n">
-        <v>101395</v>
+        <v>101396</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>135849900</v>
       </c>
       <c r="B73" t="n">
-        <v>101395</v>
+        <v>101396</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>135849901</v>
       </c>
       <c r="B74" t="n">
-        <v>101395</v>
+        <v>101396</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>135849902</v>
       </c>
       <c r="B75" t="n">
-        <v>101395</v>
+        <v>101396</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>135849903</v>
       </c>
       <c r="B76" t="n">
-        <v>101395</v>
+        <v>101396</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 28050-2026 artfynd.xlsx
+++ b/artfynd/A 28050-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135849953</v>
       </c>
       <c r="B2" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135849954</v>
       </c>
       <c r="B3" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135849955</v>
       </c>
       <c r="B4" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135849956</v>
       </c>
       <c r="B5" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135849957</v>
       </c>
       <c r="B6" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135849958</v>
       </c>
       <c r="B7" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135849959</v>
       </c>
       <c r="B8" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135850014</v>
       </c>
       <c r="B9" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>135850015</v>
       </c>
       <c r="B10" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>135850016</v>
       </c>
       <c r="B11" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>135850017</v>
       </c>
       <c r="B12" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>135850018</v>
       </c>
       <c r="B13" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>135849842</v>
       </c>
       <c r="B14" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>135849843</v>
       </c>
       <c r="B15" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>135849844</v>
       </c>
       <c r="B16" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>135849845</v>
       </c>
       <c r="B17" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135850027</v>
       </c>
       <c r="B18" t="n">
-        <v>99213</v>
+        <v>99219</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>135850012</v>
       </c>
       <c r="B19" t="n">
-        <v>99195</v>
+        <v>99201</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>135850029</v>
       </c>
       <c r="B20" t="n">
-        <v>99298</v>
+        <v>99304</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135849834</v>
       </c>
       <c r="B21" t="n">
-        <v>99320</v>
+        <v>99326</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>135849835</v>
       </c>
       <c r="B22" t="n">
-        <v>99320</v>
+        <v>99326</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>135849836</v>
       </c>
       <c r="B23" t="n">
-        <v>99320</v>
+        <v>99326</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>135849837</v>
       </c>
       <c r="B24" t="n">
-        <v>99320</v>
+        <v>99326</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>135849838</v>
       </c>
       <c r="B25" t="n">
-        <v>99320</v>
+        <v>99326</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>135849839</v>
       </c>
       <c r="B26" t="n">
-        <v>99320</v>
+        <v>99326</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>135849840</v>
       </c>
       <c r="B27" t="n">
-        <v>99320</v>
+        <v>99326</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>135849841</v>
       </c>
       <c r="B28" t="n">
-        <v>99320</v>
+        <v>99326</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>135849936</v>
       </c>
       <c r="B29" t="n">
-        <v>99634</v>
+        <v>99640</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>135849937</v>
       </c>
       <c r="B30" t="n">
-        <v>99634</v>
+        <v>99640</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>135850030</v>
       </c>
       <c r="B31" t="n">
-        <v>108321</v>
+        <v>108327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>135850031</v>
       </c>
       <c r="B32" t="n">
-        <v>108321</v>
+        <v>108327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>135850032</v>
       </c>
       <c r="B33" t="n">
-        <v>108321</v>
+        <v>108327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>135850033</v>
       </c>
       <c r="B34" t="n">
-        <v>108321</v>
+        <v>108327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>135850034</v>
       </c>
       <c r="B35" t="n">
-        <v>108321</v>
+        <v>108327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>135850035</v>
       </c>
       <c r="B36" t="n">
-        <v>108321</v>
+        <v>108327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>135849917</v>
       </c>
       <c r="B37" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>135849918</v>
       </c>
       <c r="B38" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>135849919</v>
       </c>
       <c r="B39" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>135849920</v>
       </c>
       <c r="B40" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>135849921</v>
       </c>
       <c r="B41" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>135849922</v>
       </c>
       <c r="B42" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>135849923</v>
       </c>
       <c r="B43" t="n">
-        <v>108391</v>
+        <v>108397</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>135849909</v>
       </c>
       <c r="B44" t="n">
-        <v>111271</v>
+        <v>111277</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>135849910</v>
       </c>
       <c r="B45" t="n">
-        <v>111271</v>
+        <v>111277</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>135849974</v>
       </c>
       <c r="B46" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>135849975</v>
       </c>
       <c r="B47" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>135849976</v>
       </c>
       <c r="B48" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>135849977</v>
       </c>
       <c r="B49" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>135849978</v>
       </c>
       <c r="B50" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>135849979</v>
       </c>
       <c r="B51" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>135849862</v>
       </c>
       <c r="B52" t="n">
-        <v>110041</v>
+        <v>110047</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>135849863</v>
       </c>
       <c r="B53" t="n">
-        <v>110041</v>
+        <v>110047</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>135849864</v>
       </c>
       <c r="B54" t="n">
-        <v>110041</v>
+        <v>110047</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>135849876</v>
       </c>
       <c r="B55" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>135850039</v>
       </c>
       <c r="B56" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>135850040</v>
       </c>
       <c r="B57" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>135850042</v>
       </c>
       <c r="B58" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>135850043</v>
       </c>
       <c r="B59" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>135850044</v>
       </c>
       <c r="B60" t="n">
-        <v>101506</v>
+        <v>101512</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>135849915</v>
       </c>
       <c r="B61" t="n">
-        <v>99573</v>
+        <v>99579</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>135849889</v>
       </c>
       <c r="B62" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>135849996</v>
       </c>
       <c r="B63" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>135849997</v>
       </c>
       <c r="B64" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>135849998</v>
       </c>
       <c r="B65" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>135849893</v>
       </c>
       <c r="B66" t="n">
-        <v>101396</v>
+        <v>101402</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>135849894</v>
       </c>
       <c r="B67" t="n">
-        <v>101396</v>
+        <v>101402</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>135849895</v>
       </c>
       <c r="B68" t="n">
-        <v>101396</v>
+        <v>101402</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>135849896</v>
       </c>
       <c r="B69" t="n">
-        <v>101396</v>
+        <v>101402</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>135849897</v>
       </c>
       <c r="B70" t="n">
-        <v>101396</v>
+        <v>101402</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>135849898</v>
       </c>
       <c r="B71" t="n">
-        <v>101396</v>
+        <v>101402</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>135849899</v>
       </c>
       <c r="B72" t="n">
-        <v>101396</v>
+        <v>101402</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>135849900</v>
       </c>
       <c r="B73" t="n">
-        <v>101396</v>
+        <v>101402</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>135849901</v>
       </c>
       <c r="B74" t="n">
-        <v>101396</v>
+        <v>101402</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>135849902</v>
       </c>
       <c r="B75" t="n">
-        <v>101396</v>
+        <v>101402</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>135849903</v>
       </c>
       <c r="B76" t="n">
-        <v>101396</v>
+        <v>101402</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 28050-2026 artfynd.xlsx
+++ b/artfynd/A 28050-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135849953</v>
       </c>
       <c r="B2" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135849954</v>
       </c>
       <c r="B3" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135849955</v>
       </c>
       <c r="B4" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135849956</v>
       </c>
       <c r="B5" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135849957</v>
       </c>
       <c r="B6" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135849958</v>
       </c>
       <c r="B7" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135849959</v>
       </c>
       <c r="B8" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135850014</v>
       </c>
       <c r="B9" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>135850015</v>
       </c>
       <c r="B10" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>135850016</v>
       </c>
       <c r="B11" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>135850017</v>
       </c>
       <c r="B12" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>135850018</v>
       </c>
       <c r="B13" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>135849842</v>
       </c>
       <c r="B14" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>135849843</v>
       </c>
       <c r="B15" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>135849844</v>
       </c>
       <c r="B16" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>135849845</v>
       </c>
       <c r="B17" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135850027</v>
       </c>
       <c r="B18" t="n">
-        <v>99219</v>
+        <v>99220</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>135850012</v>
       </c>
       <c r="B19" t="n">
-        <v>99201</v>
+        <v>99202</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>135850029</v>
       </c>
       <c r="B20" t="n">
-        <v>99304</v>
+        <v>99305</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135849834</v>
       </c>
       <c r="B21" t="n">
-        <v>99326</v>
+        <v>99327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>135849835</v>
       </c>
       <c r="B22" t="n">
-        <v>99326</v>
+        <v>99327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>135849836</v>
       </c>
       <c r="B23" t="n">
-        <v>99326</v>
+        <v>99327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>135849837</v>
       </c>
       <c r="B24" t="n">
-        <v>99326</v>
+        <v>99327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>135849838</v>
       </c>
       <c r="B25" t="n">
-        <v>99326</v>
+        <v>99327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>135849839</v>
       </c>
       <c r="B26" t="n">
-        <v>99326</v>
+        <v>99327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>135849840</v>
       </c>
       <c r="B27" t="n">
-        <v>99326</v>
+        <v>99327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>135849841</v>
       </c>
       <c r="B28" t="n">
-        <v>99326</v>
+        <v>99327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>135849936</v>
       </c>
       <c r="B29" t="n">
-        <v>99640</v>
+        <v>99641</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>135849937</v>
       </c>
       <c r="B30" t="n">
-        <v>99640</v>
+        <v>99641</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>135850030</v>
       </c>
       <c r="B31" t="n">
-        <v>108327</v>
+        <v>108328</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>135850031</v>
       </c>
       <c r="B32" t="n">
-        <v>108327</v>
+        <v>108328</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>135850032</v>
       </c>
       <c r="B33" t="n">
-        <v>108327</v>
+        <v>108328</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>135850033</v>
       </c>
       <c r="B34" t="n">
-        <v>108327</v>
+        <v>108328</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>135850034</v>
       </c>
       <c r="B35" t="n">
-        <v>108327</v>
+        <v>108328</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>135850035</v>
       </c>
       <c r="B36" t="n">
-        <v>108327</v>
+        <v>108328</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>135849917</v>
       </c>
       <c r="B37" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>135849918</v>
       </c>
       <c r="B38" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>135849919</v>
       </c>
       <c r="B39" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>135849920</v>
       </c>
       <c r="B40" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>135849921</v>
       </c>
       <c r="B41" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>135849922</v>
       </c>
       <c r="B42" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>135849923</v>
       </c>
       <c r="B43" t="n">
-        <v>108397</v>
+        <v>108398</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>135849909</v>
       </c>
       <c r="B44" t="n">
-        <v>111277</v>
+        <v>111278</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>135849910</v>
       </c>
       <c r="B45" t="n">
-        <v>111277</v>
+        <v>111278</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>135849974</v>
       </c>
       <c r="B46" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>135849975</v>
       </c>
       <c r="B47" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>135849976</v>
       </c>
       <c r="B48" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>135849977</v>
       </c>
       <c r="B49" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>135849978</v>
       </c>
       <c r="B50" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>135849979</v>
       </c>
       <c r="B51" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>135849862</v>
       </c>
       <c r="B52" t="n">
-        <v>110047</v>
+        <v>110048</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>135849863</v>
       </c>
       <c r="B53" t="n">
-        <v>110047</v>
+        <v>110048</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>135849864</v>
       </c>
       <c r="B54" t="n">
-        <v>110047</v>
+        <v>110048</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>135849876</v>
       </c>
       <c r="B55" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>135850039</v>
       </c>
       <c r="B56" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>135850040</v>
       </c>
       <c r="B57" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>135850042</v>
       </c>
       <c r="B58" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>135850043</v>
       </c>
       <c r="B59" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>135850044</v>
       </c>
       <c r="B60" t="n">
-        <v>101512</v>
+        <v>101513</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>135849915</v>
       </c>
       <c r="B61" t="n">
-        <v>99579</v>
+        <v>99580</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>135849889</v>
       </c>
       <c r="B62" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>135849996</v>
       </c>
       <c r="B63" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>135849997</v>
       </c>
       <c r="B64" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>135849998</v>
       </c>
       <c r="B65" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>135849893</v>
       </c>
       <c r="B66" t="n">
-        <v>101402</v>
+        <v>101403</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>135849894</v>
       </c>
       <c r="B67" t="n">
-        <v>101402</v>
+        <v>101403</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>135849895</v>
       </c>
       <c r="B68" t="n">
-        <v>101402</v>
+        <v>101403</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>135849896</v>
       </c>
       <c r="B69" t="n">
-        <v>101402</v>
+        <v>101403</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>135849897</v>
       </c>
       <c r="B70" t="n">
-        <v>101402</v>
+        <v>101403</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>135849898</v>
       </c>
       <c r="B71" t="n">
-        <v>101402</v>
+        <v>101403</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>135849899</v>
       </c>
       <c r="B72" t="n">
-        <v>101402</v>
+        <v>101403</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>135849900</v>
       </c>
       <c r="B73" t="n">
-        <v>101402</v>
+        <v>101403</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>135849901</v>
       </c>
       <c r="B74" t="n">
-        <v>101402</v>
+        <v>101403</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>135849902</v>
       </c>
       <c r="B75" t="n">
-        <v>101402</v>
+        <v>101403</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>135849903</v>
       </c>
       <c r="B76" t="n">
-        <v>101402</v>
+        <v>101403</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 28050-2026 artfynd.xlsx
+++ b/artfynd/A 28050-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135849953</v>
       </c>
       <c r="B2" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135849954</v>
       </c>
       <c r="B3" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135849955</v>
       </c>
       <c r="B4" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135849956</v>
       </c>
       <c r="B5" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135849957</v>
       </c>
       <c r="B6" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135849958</v>
       </c>
       <c r="B7" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135849959</v>
       </c>
       <c r="B8" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135850014</v>
       </c>
       <c r="B9" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>135850015</v>
       </c>
       <c r="B10" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>135850016</v>
       </c>
       <c r="B11" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>135850017</v>
       </c>
       <c r="B12" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>135850018</v>
       </c>
       <c r="B13" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135850027</v>
       </c>
       <c r="B18" t="n">
-        <v>99220</v>
+        <v>99231</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>135850012</v>
       </c>
       <c r="B19" t="n">
-        <v>99202</v>
+        <v>99213</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>135850029</v>
       </c>
       <c r="B20" t="n">
-        <v>99305</v>
+        <v>99316</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135849834</v>
       </c>
       <c r="B21" t="n">
-        <v>99327</v>
+        <v>99338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>135849835</v>
       </c>
       <c r="B22" t="n">
-        <v>99327</v>
+        <v>99338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>135849836</v>
       </c>
       <c r="B23" t="n">
-        <v>99327</v>
+        <v>99338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>135849837</v>
       </c>
       <c r="B24" t="n">
-        <v>99327</v>
+        <v>99338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>135849838</v>
       </c>
       <c r="B25" t="n">
-        <v>99327</v>
+        <v>99338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>135849839</v>
       </c>
       <c r="B26" t="n">
-        <v>99327</v>
+        <v>99338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>135849840</v>
       </c>
       <c r="B27" t="n">
-        <v>99327</v>
+        <v>99338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>135849841</v>
       </c>
       <c r="B28" t="n">
-        <v>99327</v>
+        <v>99338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>135849936</v>
       </c>
       <c r="B29" t="n">
-        <v>99641</v>
+        <v>99652</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>135849937</v>
       </c>
       <c r="B30" t="n">
-        <v>99641</v>
+        <v>99652</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>135850030</v>
       </c>
       <c r="B31" t="n">
-        <v>108328</v>
+        <v>108339</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>135850031</v>
       </c>
       <c r="B32" t="n">
-        <v>108328</v>
+        <v>108339</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>135850032</v>
       </c>
       <c r="B33" t="n">
-        <v>108328</v>
+        <v>108339</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>135850033</v>
       </c>
       <c r="B34" t="n">
-        <v>108328</v>
+        <v>108339</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>135850034</v>
       </c>
       <c r="B35" t="n">
-        <v>108328</v>
+        <v>108339</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>135850035</v>
       </c>
       <c r="B36" t="n">
-        <v>108328</v>
+        <v>108339</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>135849917</v>
       </c>
       <c r="B37" t="n">
-        <v>108398</v>
+        <v>108409</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>135849918</v>
       </c>
       <c r="B38" t="n">
-        <v>108398</v>
+        <v>108409</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>135849919</v>
       </c>
       <c r="B39" t="n">
-        <v>108398</v>
+        <v>108409</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>135849920</v>
       </c>
       <c r="B40" t="n">
-        <v>108398</v>
+        <v>108409</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>135849921</v>
       </c>
       <c r="B41" t="n">
-        <v>108398</v>
+        <v>108409</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>135849922</v>
       </c>
       <c r="B42" t="n">
-        <v>108398</v>
+        <v>108409</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>135849923</v>
       </c>
       <c r="B43" t="n">
-        <v>108398</v>
+        <v>108409</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>135849909</v>
       </c>
       <c r="B44" t="n">
-        <v>111278</v>
+        <v>111289</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>135849910</v>
       </c>
       <c r="B45" t="n">
-        <v>111278</v>
+        <v>111289</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>135849974</v>
       </c>
       <c r="B46" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>135849975</v>
       </c>
       <c r="B47" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>135849976</v>
       </c>
       <c r="B48" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>135849977</v>
       </c>
       <c r="B49" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>135849978</v>
       </c>
       <c r="B50" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>135849979</v>
       </c>
       <c r="B51" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>135849862</v>
       </c>
       <c r="B52" t="n">
-        <v>110048</v>
+        <v>110059</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>135849863</v>
       </c>
       <c r="B53" t="n">
-        <v>110048</v>
+        <v>110059</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>135849864</v>
       </c>
       <c r="B54" t="n">
-        <v>110048</v>
+        <v>110059</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>135849876</v>
       </c>
       <c r="B55" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>135850039</v>
       </c>
       <c r="B56" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>135850040</v>
       </c>
       <c r="B57" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>135850042</v>
       </c>
       <c r="B58" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>135850043</v>
       </c>
       <c r="B59" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>135850044</v>
       </c>
       <c r="B60" t="n">
-        <v>101513</v>
+        <v>101524</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>135849915</v>
       </c>
       <c r="B61" t="n">
-        <v>99580</v>
+        <v>99591</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>135849889</v>
       </c>
       <c r="B62" t="n">
-        <v>99109</v>
+        <v>99120</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>135849996</v>
       </c>
       <c r="B63" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>135849997</v>
       </c>
       <c r="B64" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>135849998</v>
       </c>
       <c r="B65" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>135849893</v>
       </c>
       <c r="B66" t="n">
-        <v>101403</v>
+        <v>101414</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>135849894</v>
       </c>
       <c r="B67" t="n">
-        <v>101403</v>
+        <v>101414</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>135849895</v>
       </c>
       <c r="B68" t="n">
-        <v>101403</v>
+        <v>101414</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>135849896</v>
       </c>
       <c r="B69" t="n">
-        <v>101403</v>
+        <v>101414</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>135849897</v>
       </c>
       <c r="B70" t="n">
-        <v>101403</v>
+        <v>101414</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>135849898</v>
       </c>
       <c r="B71" t="n">
-        <v>101403</v>
+        <v>101414</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>135849899</v>
       </c>
       <c r="B72" t="n">
-        <v>101403</v>
+        <v>101414</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>135849900</v>
       </c>
       <c r="B73" t="n">
-        <v>101403</v>
+        <v>101414</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>135849901</v>
       </c>
       <c r="B74" t="n">
-        <v>101403</v>
+        <v>101414</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>135849902</v>
       </c>
       <c r="B75" t="n">
-        <v>101403</v>
+        <v>101414</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>135849903</v>
       </c>
       <c r="B76" t="n">
-        <v>101403</v>
+        <v>101414</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 28050-2026 artfynd.xlsx
+++ b/artfynd/A 28050-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135849953</v>
       </c>
       <c r="B2" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135849954</v>
       </c>
       <c r="B3" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135849955</v>
       </c>
       <c r="B4" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135849956</v>
       </c>
       <c r="B5" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135849957</v>
       </c>
       <c r="B6" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135849958</v>
       </c>
       <c r="B7" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135849959</v>
       </c>
       <c r="B8" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135850014</v>
       </c>
       <c r="B9" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>135850015</v>
       </c>
       <c r="B10" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>135850016</v>
       </c>
       <c r="B11" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>135850017</v>
       </c>
       <c r="B12" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>135850018</v>
       </c>
       <c r="B13" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>135849842</v>
       </c>
       <c r="B14" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>135849843</v>
       </c>
       <c r="B15" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>135849844</v>
       </c>
       <c r="B16" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>135849845</v>
       </c>
       <c r="B17" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135850027</v>
       </c>
       <c r="B18" t="n">
-        <v>99231</v>
+        <v>99244</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>135850012</v>
       </c>
       <c r="B19" t="n">
-        <v>99213</v>
+        <v>99226</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>135850029</v>
       </c>
       <c r="B20" t="n">
-        <v>99316</v>
+        <v>99329</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135849834</v>
       </c>
       <c r="B21" t="n">
-        <v>99338</v>
+        <v>99351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>135849835</v>
       </c>
       <c r="B22" t="n">
-        <v>99338</v>
+        <v>99351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>135849836</v>
       </c>
       <c r="B23" t="n">
-        <v>99338</v>
+        <v>99351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>135849837</v>
       </c>
       <c r="B24" t="n">
-        <v>99338</v>
+        <v>99351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>135849838</v>
       </c>
       <c r="B25" t="n">
-        <v>99338</v>
+        <v>99351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>135849839</v>
       </c>
       <c r="B26" t="n">
-        <v>99338</v>
+        <v>99351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>135849840</v>
       </c>
       <c r="B27" t="n">
-        <v>99338</v>
+        <v>99351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>135849841</v>
       </c>
       <c r="B28" t="n">
-        <v>99338</v>
+        <v>99351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>135849936</v>
       </c>
       <c r="B29" t="n">
-        <v>99652</v>
+        <v>99665</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>135849937</v>
       </c>
       <c r="B30" t="n">
-        <v>99652</v>
+        <v>99665</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>135850030</v>
       </c>
       <c r="B31" t="n">
-        <v>108339</v>
+        <v>108352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>135850031</v>
       </c>
       <c r="B32" t="n">
-        <v>108339</v>
+        <v>108352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>135850032</v>
       </c>
       <c r="B33" t="n">
-        <v>108339</v>
+        <v>108352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>135850033</v>
       </c>
       <c r="B34" t="n">
-        <v>108339</v>
+        <v>108352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>135850034</v>
       </c>
       <c r="B35" t="n">
-        <v>108339</v>
+        <v>108352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>135850035</v>
       </c>
       <c r="B36" t="n">
-        <v>108339</v>
+        <v>108352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>135849917</v>
       </c>
       <c r="B37" t="n">
-        <v>108409</v>
+        <v>108422</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>135849918</v>
       </c>
       <c r="B38" t="n">
-        <v>108409</v>
+        <v>108422</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>135849919</v>
       </c>
       <c r="B39" t="n">
-        <v>108409</v>
+        <v>108422</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>135849920</v>
       </c>
       <c r="B40" t="n">
-        <v>108409</v>
+        <v>108422</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>135849921</v>
       </c>
       <c r="B41" t="n">
-        <v>108409</v>
+        <v>108422</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>135849922</v>
       </c>
       <c r="B42" t="n">
-        <v>108409</v>
+        <v>108422</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>135849923</v>
       </c>
       <c r="B43" t="n">
-        <v>108409</v>
+        <v>108422</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>135849909</v>
       </c>
       <c r="B44" t="n">
-        <v>111289</v>
+        <v>111302</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>135849910</v>
       </c>
       <c r="B45" t="n">
-        <v>111289</v>
+        <v>111302</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>135849974</v>
       </c>
       <c r="B46" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>135849975</v>
       </c>
       <c r="B47" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>135849976</v>
       </c>
       <c r="B48" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>135849977</v>
       </c>
       <c r="B49" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>135849978</v>
       </c>
       <c r="B50" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>135849979</v>
       </c>
       <c r="B51" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>135849862</v>
       </c>
       <c r="B52" t="n">
-        <v>110059</v>
+        <v>110072</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>135849863</v>
       </c>
       <c r="B53" t="n">
-        <v>110059</v>
+        <v>110072</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>135849864</v>
       </c>
       <c r="B54" t="n">
-        <v>110059</v>
+        <v>110072</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>135849876</v>
       </c>
       <c r="B55" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>135850039</v>
       </c>
       <c r="B56" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>135850040</v>
       </c>
       <c r="B57" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>135850042</v>
       </c>
       <c r="B58" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>135850043</v>
       </c>
       <c r="B59" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>135850044</v>
       </c>
       <c r="B60" t="n">
-        <v>101524</v>
+        <v>101537</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>135849915</v>
       </c>
       <c r="B61" t="n">
-        <v>99591</v>
+        <v>99604</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>135849889</v>
       </c>
       <c r="B62" t="n">
-        <v>99120</v>
+        <v>99133</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>135849996</v>
       </c>
       <c r="B63" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>135849997</v>
       </c>
       <c r="B64" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>135849998</v>
       </c>
       <c r="B65" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>135849893</v>
       </c>
       <c r="B66" t="n">
-        <v>101414</v>
+        <v>101427</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>135849894</v>
       </c>
       <c r="B67" t="n">
-        <v>101414</v>
+        <v>101427</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>135849895</v>
       </c>
       <c r="B68" t="n">
-        <v>101414</v>
+        <v>101427</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>135849896</v>
       </c>
       <c r="B69" t="n">
-        <v>101414</v>
+        <v>101427</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>135849897</v>
       </c>
       <c r="B70" t="n">
-        <v>101414</v>
+        <v>101427</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>135849898</v>
       </c>
       <c r="B71" t="n">
-        <v>101414</v>
+        <v>101427</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>135849899</v>
       </c>
       <c r="B72" t="n">
-        <v>101414</v>
+        <v>101427</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>135849900</v>
       </c>
       <c r="B73" t="n">
-        <v>101414</v>
+        <v>101427</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>135849901</v>
       </c>
       <c r="B74" t="n">
-        <v>101414</v>
+        <v>101427</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>135849902</v>
       </c>
       <c r="B75" t="n">
-        <v>101414</v>
+        <v>101427</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>135849903</v>
       </c>
       <c r="B76" t="n">
-        <v>101414</v>
+        <v>101427</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 28050-2026 artfynd.xlsx
+++ b/artfynd/A 28050-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135849953</v>
       </c>
       <c r="B2" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135849954</v>
       </c>
       <c r="B3" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135849955</v>
       </c>
       <c r="B4" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135849956</v>
       </c>
       <c r="B5" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135849957</v>
       </c>
       <c r="B6" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135849958</v>
       </c>
       <c r="B7" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135849959</v>
       </c>
       <c r="B8" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135850027</v>
       </c>
       <c r="B18" t="n">
-        <v>99244</v>
+        <v>99245</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>135850012</v>
       </c>
       <c r="B19" t="n">
-        <v>99226</v>
+        <v>99227</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>135850029</v>
       </c>
       <c r="B20" t="n">
-        <v>99329</v>
+        <v>99330</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135849834</v>
       </c>
       <c r="B21" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>135849835</v>
       </c>
       <c r="B22" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>135849836</v>
       </c>
       <c r="B23" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>135849837</v>
       </c>
       <c r="B24" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>135849838</v>
       </c>
       <c r="B25" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>135849839</v>
       </c>
       <c r="B26" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>135849840</v>
       </c>
       <c r="B27" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>135849841</v>
       </c>
       <c r="B28" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>135849936</v>
       </c>
       <c r="B29" t="n">
-        <v>99665</v>
+        <v>99666</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>135849937</v>
       </c>
       <c r="B30" t="n">
-        <v>99665</v>
+        <v>99666</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>135850030</v>
       </c>
       <c r="B31" t="n">
-        <v>108352</v>
+        <v>108353</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>135850031</v>
       </c>
       <c r="B32" t="n">
-        <v>108352</v>
+        <v>108353</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>135850032</v>
       </c>
       <c r="B33" t="n">
-        <v>108352</v>
+        <v>108353</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>135850033</v>
       </c>
       <c r="B34" t="n">
-        <v>108352</v>
+        <v>108353</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>135850034</v>
       </c>
       <c r="B35" t="n">
-        <v>108352</v>
+        <v>108353</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>135850035</v>
       </c>
       <c r="B36" t="n">
-        <v>108352</v>
+        <v>108353</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>135849917</v>
       </c>
       <c r="B37" t="n">
-        <v>108422</v>
+        <v>108423</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>135849918</v>
       </c>
       <c r="B38" t="n">
-        <v>108422</v>
+        <v>108423</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>135849919</v>
       </c>
       <c r="B39" t="n">
-        <v>108422</v>
+        <v>108423</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>135849920</v>
       </c>
       <c r="B40" t="n">
-        <v>108422</v>
+        <v>108423</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>135849921</v>
       </c>
       <c r="B41" t="n">
-        <v>108422</v>
+        <v>108423</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>135849922</v>
       </c>
       <c r="B42" t="n">
-        <v>108422</v>
+        <v>108423</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>135849923</v>
       </c>
       <c r="B43" t="n">
-        <v>108422</v>
+        <v>108423</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>135849909</v>
       </c>
       <c r="B44" t="n">
-        <v>111302</v>
+        <v>111303</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>135849910</v>
       </c>
       <c r="B45" t="n">
-        <v>111302</v>
+        <v>111303</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>135849974</v>
       </c>
       <c r="B46" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>135849975</v>
       </c>
       <c r="B47" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>135849976</v>
       </c>
       <c r="B48" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>135849977</v>
       </c>
       <c r="B49" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>135849978</v>
       </c>
       <c r="B50" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>135849979</v>
       </c>
       <c r="B51" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>135849862</v>
       </c>
       <c r="B52" t="n">
-        <v>110072</v>
+        <v>110073</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>135849863</v>
       </c>
       <c r="B53" t="n">
-        <v>110072</v>
+        <v>110073</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>135849864</v>
       </c>
       <c r="B54" t="n">
-        <v>110072</v>
+        <v>110073</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>135849876</v>
       </c>
       <c r="B55" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>135850039</v>
       </c>
       <c r="B56" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>135850040</v>
       </c>
       <c r="B57" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>135850042</v>
       </c>
       <c r="B58" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>135850043</v>
       </c>
       <c r="B59" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>135850044</v>
       </c>
       <c r="B60" t="n">
-        <v>101537</v>
+        <v>101538</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>135849915</v>
       </c>
       <c r="B61" t="n">
-        <v>99604</v>
+        <v>99605</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>135849889</v>
       </c>
       <c r="B62" t="n">
-        <v>99133</v>
+        <v>99134</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>135849996</v>
       </c>
       <c r="B63" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>135849997</v>
       </c>
       <c r="B64" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>135849998</v>
       </c>
       <c r="B65" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>135849893</v>
       </c>
       <c r="B66" t="n">
-        <v>101427</v>
+        <v>101428</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>135849894</v>
       </c>
       <c r="B67" t="n">
-        <v>101427</v>
+        <v>101428</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>135849895</v>
       </c>
       <c r="B68" t="n">
-        <v>101427</v>
+        <v>101428</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>135849896</v>
       </c>
       <c r="B69" t="n">
-        <v>101427</v>
+        <v>101428</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>135849897</v>
       </c>
       <c r="B70" t="n">
-        <v>101427</v>
+        <v>101428</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>135849898</v>
       </c>
       <c r="B71" t="n">
-        <v>101427</v>
+        <v>101428</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>135849899</v>
       </c>
       <c r="B72" t="n">
-        <v>101427</v>
+        <v>101428</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>135849900</v>
       </c>
       <c r="B73" t="n">
-        <v>101427</v>
+        <v>101428</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>135849901</v>
       </c>
       <c r="B74" t="n">
-        <v>101427</v>
+        <v>101428</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>135849902</v>
       </c>
       <c r="B75" t="n">
-        <v>101427</v>
+        <v>101428</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>135849903</v>
       </c>
       <c r="B76" t="n">
-        <v>101427</v>
+        <v>101428</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 28050-2026 artfynd.xlsx
+++ b/artfynd/A 28050-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135849953</v>
       </c>
       <c r="B2" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135849954</v>
       </c>
       <c r="B3" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135849955</v>
       </c>
       <c r="B4" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135849956</v>
       </c>
       <c r="B5" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135849957</v>
       </c>
       <c r="B6" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135849958</v>
       </c>
       <c r="B7" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135849959</v>
       </c>
       <c r="B8" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135850014</v>
       </c>
       <c r="B9" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>135850015</v>
       </c>
       <c r="B10" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>135850016</v>
       </c>
       <c r="B11" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>135850017</v>
       </c>
       <c r="B12" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>135850018</v>
       </c>
       <c r="B13" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>135849842</v>
       </c>
       <c r="B14" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>135849843</v>
       </c>
       <c r="B15" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>135849844</v>
       </c>
       <c r="B16" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>135849845</v>
       </c>
       <c r="B17" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135850027</v>
       </c>
       <c r="B18" t="n">
-        <v>99245</v>
+        <v>99258</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>135850012</v>
       </c>
       <c r="B19" t="n">
-        <v>99227</v>
+        <v>99240</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>135850029</v>
       </c>
       <c r="B20" t="n">
-        <v>99330</v>
+        <v>99343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135849834</v>
       </c>
       <c r="B21" t="n">
-        <v>99352</v>
+        <v>99365</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>135849835</v>
       </c>
       <c r="B22" t="n">
-        <v>99352</v>
+        <v>99365</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>135849836</v>
       </c>
       <c r="B23" t="n">
-        <v>99352</v>
+        <v>99365</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>135849837</v>
       </c>
       <c r="B24" t="n">
-        <v>99352</v>
+        <v>99365</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>135849838</v>
       </c>
       <c r="B25" t="n">
-        <v>99352</v>
+        <v>99365</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>135849839</v>
       </c>
       <c r="B26" t="n">
-        <v>99352</v>
+        <v>99365</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>135849840</v>
       </c>
       <c r="B27" t="n">
-        <v>99352</v>
+        <v>99365</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>135849841</v>
       </c>
       <c r="B28" t="n">
-        <v>99352</v>
+        <v>99365</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>135849936</v>
       </c>
       <c r="B29" t="n">
-        <v>99666</v>
+        <v>99679</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>135849937</v>
       </c>
       <c r="B30" t="n">
-        <v>99666</v>
+        <v>99679</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>135850030</v>
       </c>
       <c r="B31" t="n">
-        <v>108353</v>
+        <v>108366</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>135850031</v>
       </c>
       <c r="B32" t="n">
-        <v>108353</v>
+        <v>108366</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>135850032</v>
       </c>
       <c r="B33" t="n">
-        <v>108353</v>
+        <v>108366</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>135850033</v>
       </c>
       <c r="B34" t="n">
-        <v>108353</v>
+        <v>108366</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>135850034</v>
       </c>
       <c r="B35" t="n">
-        <v>108353</v>
+        <v>108366</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>135850035</v>
       </c>
       <c r="B36" t="n">
-        <v>108353</v>
+        <v>108366</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>135849917</v>
       </c>
       <c r="B37" t="n">
-        <v>108423</v>
+        <v>108436</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>135849918</v>
       </c>
       <c r="B38" t="n">
-        <v>108423</v>
+        <v>108436</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>135849919</v>
       </c>
       <c r="B39" t="n">
-        <v>108423</v>
+        <v>108436</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>135849920</v>
       </c>
       <c r="B40" t="n">
-        <v>108423</v>
+        <v>108436</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>135849921</v>
       </c>
       <c r="B41" t="n">
-        <v>108423</v>
+        <v>108436</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>135849922</v>
       </c>
       <c r="B42" t="n">
-        <v>108423</v>
+        <v>108436</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>135849923</v>
       </c>
       <c r="B43" t="n">
-        <v>108423</v>
+        <v>108436</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>135849909</v>
       </c>
       <c r="B44" t="n">
-        <v>111303</v>
+        <v>111316</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>135849910</v>
       </c>
       <c r="B45" t="n">
-        <v>111303</v>
+        <v>111316</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>135849974</v>
       </c>
       <c r="B46" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>135849975</v>
       </c>
       <c r="B47" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>135849976</v>
       </c>
       <c r="B48" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>135849977</v>
       </c>
       <c r="B49" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>135849978</v>
       </c>
       <c r="B50" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>135849979</v>
       </c>
       <c r="B51" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>135849862</v>
       </c>
       <c r="B52" t="n">
-        <v>110073</v>
+        <v>110086</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>135849863</v>
       </c>
       <c r="B53" t="n">
-        <v>110073</v>
+        <v>110086</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>135849864</v>
       </c>
       <c r="B54" t="n">
-        <v>110073</v>
+        <v>110086</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>135849876</v>
       </c>
       <c r="B55" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>135850039</v>
       </c>
       <c r="B56" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>135850040</v>
       </c>
       <c r="B57" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>135850042</v>
       </c>
       <c r="B58" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>135850043</v>
       </c>
       <c r="B59" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>135850044</v>
       </c>
       <c r="B60" t="n">
-        <v>101538</v>
+        <v>101551</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>135849915</v>
       </c>
       <c r="B61" t="n">
-        <v>99605</v>
+        <v>99618</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>135849889</v>
       </c>
       <c r="B62" t="n">
-        <v>99134</v>
+        <v>99147</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>135849996</v>
       </c>
       <c r="B63" t="n">
-        <v>98379</v>
+        <v>98392</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>135849997</v>
       </c>
       <c r="B64" t="n">
-        <v>98379</v>
+        <v>98392</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>135849998</v>
       </c>
       <c r="B65" t="n">
-        <v>98379</v>
+        <v>98392</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>135849893</v>
       </c>
       <c r="B66" t="n">
-        <v>101428</v>
+        <v>101441</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>135849894</v>
       </c>
       <c r="B67" t="n">
-        <v>101428</v>
+        <v>101441</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>135849895</v>
       </c>
       <c r="B68" t="n">
-        <v>101428</v>
+        <v>101441</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>135849896</v>
       </c>
       <c r="B69" t="n">
-        <v>101428</v>
+        <v>101441</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>135849897</v>
       </c>
       <c r="B70" t="n">
-        <v>101428</v>
+        <v>101441</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>135849898</v>
       </c>
       <c r="B71" t="n">
-        <v>101428</v>
+        <v>101441</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>135849899</v>
       </c>
       <c r="B72" t="n">
-        <v>101428</v>
+        <v>101441</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>135849900</v>
       </c>
       <c r="B73" t="n">
-        <v>101428</v>
+        <v>101441</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>135849901</v>
       </c>
       <c r="B74" t="n">
-        <v>101428</v>
+        <v>101441</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>135849902</v>
       </c>
       <c r="B75" t="n">
-        <v>101428</v>
+        <v>101441</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>135849903</v>
       </c>
       <c r="B76" t="n">
-        <v>101428</v>
+        <v>101441</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 28050-2026 artfynd.xlsx
+++ b/artfynd/A 28050-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135849953</v>
       </c>
       <c r="B2" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135849954</v>
       </c>
       <c r="B3" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135849955</v>
       </c>
       <c r="B4" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135849956</v>
       </c>
       <c r="B5" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135849957</v>
       </c>
       <c r="B6" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135849958</v>
       </c>
       <c r="B7" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135849959</v>
       </c>
       <c r="B8" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135850014</v>
       </c>
       <c r="B9" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>135850015</v>
       </c>
       <c r="B10" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>135850016</v>
       </c>
       <c r="B11" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>135850017</v>
       </c>
       <c r="B12" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>135850018</v>
       </c>
       <c r="B13" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135850027</v>
       </c>
       <c r="B18" t="n">
-        <v>99258</v>
+        <v>99259</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>135850012</v>
       </c>
       <c r="B19" t="n">
-        <v>99240</v>
+        <v>99241</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>135850029</v>
       </c>
       <c r="B20" t="n">
-        <v>99343</v>
+        <v>99344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135849834</v>
       </c>
       <c r="B21" t="n">
-        <v>99365</v>
+        <v>99366</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>135849835</v>
       </c>
       <c r="B22" t="n">
-        <v>99365</v>
+        <v>99366</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>135849836</v>
       </c>
       <c r="B23" t="n">
-        <v>99365</v>
+        <v>99366</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>135849837</v>
       </c>
       <c r="B24" t="n">
-        <v>99365</v>
+        <v>99366</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>135849838</v>
       </c>
       <c r="B25" t="n">
-        <v>99365</v>
+        <v>99366</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>135849839</v>
       </c>
       <c r="B26" t="n">
-        <v>99365</v>
+        <v>99366</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         <v>135849840</v>
       </c>
       <c r="B27" t="n">
-        <v>99365</v>
+        <v>99366</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>135849841</v>
       </c>
       <c r="B28" t="n">
-        <v>99365</v>
+        <v>99366</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>135849936</v>
       </c>
       <c r="B29" t="n">
-        <v>99679</v>
+        <v>99680</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>135849937</v>
       </c>
       <c r="B30" t="n">
-        <v>99679</v>
+        <v>99680</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>135850030</v>
       </c>
       <c r="B31" t="n">
-        <v>108366</v>
+        <v>108367</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>135850031</v>
       </c>
       <c r="B32" t="n">
-        <v>108366</v>
+        <v>108367</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>135850032</v>
       </c>
       <c r="B33" t="n">
-        <v>108366</v>
+        <v>108367</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>135850033</v>
       </c>
       <c r="B34" t="n">
-        <v>108366</v>
+        <v>108367</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>135850034</v>
       </c>
       <c r="B35" t="n">
-        <v>108366</v>
+        <v>108367</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>135850035</v>
       </c>
       <c r="B36" t="n">
-        <v>108366</v>
+        <v>108367</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>135849917</v>
       </c>
       <c r="B37" t="n">
-        <v>108436</v>
+        <v>108437</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>135849918</v>
       </c>
       <c r="B38" t="n">
-        <v>108436</v>
+        <v>108437</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>135849919</v>
       </c>
       <c r="B39" t="n">
-        <v>108436</v>
+        <v>108437</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>135849920</v>
       </c>
       <c r="B40" t="n">
-        <v>108436</v>
+        <v>108437</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         <v>135849921</v>
       </c>
       <c r="B41" t="n">
-        <v>108436</v>
+        <v>108437</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>135849922</v>
       </c>
       <c r="B42" t="n">
-        <v>108436</v>
+        <v>108437</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>135849923</v>
       </c>
       <c r="B43" t="n">
-        <v>108436</v>
+        <v>108437</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>135849909</v>
       </c>
       <c r="B44" t="n">
-        <v>111316</v>
+        <v>111317</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>135849910</v>
       </c>
       <c r="B45" t="n">
-        <v>111316</v>
+        <v>111317</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         <v>135849974</v>
       </c>
       <c r="B46" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>135849975</v>
       </c>
       <c r="B47" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>135849976</v>
       </c>
       <c r="B48" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>135849977</v>
       </c>
       <c r="B49" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>135849978</v>
       </c>
       <c r="B50" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>135849979</v>
       </c>
       <c r="B51" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>135849862</v>
       </c>
       <c r="B52" t="n">
-        <v>110086</v>
+        <v>110087</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>135849863</v>
       </c>
       <c r="B53" t="n">
-        <v>110086</v>
+        <v>110087</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>135849864</v>
       </c>
       <c r="B54" t="n">
-        <v>110086</v>
+        <v>110087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>135849876</v>
       </c>
       <c r="B55" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>135850039</v>
       </c>
       <c r="B56" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>135850040</v>
       </c>
       <c r="B57" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>135850042</v>
       </c>
       <c r="B58" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>135850043</v>
       </c>
       <c r="B59" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>135850044</v>
       </c>
       <c r="B60" t="n">
-        <v>101551</v>
+        <v>101552</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>135849915</v>
       </c>
       <c r="B61" t="n">
-        <v>99618</v>
+        <v>99619</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>135849889</v>
       </c>
       <c r="B62" t="n">
-        <v>99147</v>
+        <v>99148</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>135849996</v>
       </c>
       <c r="B63" t="n">
-        <v>98392</v>
+        <v>98393</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>135849997</v>
       </c>
       <c r="B64" t="n">
-        <v>98392</v>
+        <v>98393</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>135849998</v>
       </c>
       <c r="B65" t="n">
-        <v>98392</v>
+        <v>98393</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>135849893</v>
       </c>
       <c r="B66" t="n">
-        <v>101441</v>
+        <v>101442</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>135849894</v>
       </c>
       <c r="B67" t="n">
-        <v>101441</v>
+        <v>101442</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>135849895</v>
       </c>
       <c r="B68" t="n">
-        <v>101441</v>
+        <v>101442</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>135849896</v>
       </c>
       <c r="B69" t="n">
-        <v>101441</v>
+        <v>101442</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>135849897</v>
       </c>
       <c r="B70" t="n">
-        <v>101441</v>
+        <v>101442</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>135849898</v>
       </c>
       <c r="B71" t="n">
-        <v>101441</v>
+        <v>101442</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>135849899</v>
       </c>
       <c r="B72" t="n">
-        <v>101441</v>
+        <v>101442</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>135849900</v>
       </c>
       <c r="B73" t="n">
-        <v>101441</v>
+        <v>101442</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>135849901</v>
       </c>
       <c r="B74" t="n">
-        <v>101441</v>
+        <v>101442</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>135849902</v>
       </c>
       <c r="B75" t="n">
-        <v>101441</v>
+        <v>101442</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         <v>135849903</v>
       </c>
       <c r="B76" t="n">
-        <v>101441</v>
+        <v>101442</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
